--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetInfoRegist.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetInfoRegist.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\tamsDoubleBranch\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
   </bookViews>
@@ -7264,7 +7269,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -7532,9 +7537,6 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="18" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7614,12 +7616,8 @@
     <xf numFmtId="49" fontId="13" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="18" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="18" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -7632,6 +7630,13 @@
     <xf numFmtId="179" fontId="18" fillId="8" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="18" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7828,13 +7833,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -7848,6 +7846,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -8165,1387 +8166,1368 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:JV11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:JM11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="44.5" style="75" customWidth="1"/>
-    <col min="2" max="2" width="15.375" style="76"/>
-    <col min="3" max="3" width="22.75" style="76" customWidth="1"/>
-    <col min="4" max="4" width="18.5" style="76" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="77" customWidth="1"/>
-    <col min="6" max="6" width="14.125" style="75"/>
-    <col min="7" max="7" width="10.75" style="78" customWidth="1"/>
-    <col min="8" max="8" width="10.375" style="79" customWidth="1"/>
-    <col min="9" max="9" width="9.5" style="79"/>
-    <col min="10" max="10" width="11.25" style="80" customWidth="1"/>
-    <col min="11" max="11" width="11.625" style="76" customWidth="1"/>
-    <col min="12" max="12" width="19.75" style="76"/>
-    <col min="13" max="13" width="25.25" style="76"/>
-    <col min="14" max="14" width="20.75" style="77"/>
-    <col min="15" max="15" width="12.75" style="81" customWidth="1"/>
-    <col min="16" max="17" width="12.25" style="82" customWidth="1"/>
-    <col min="18" max="18" width="15.375" style="82"/>
-    <col min="19" max="19" width="10.875" style="82"/>
-    <col min="20" max="20" width="30.875" style="82"/>
-    <col min="21" max="22" width="35.375" style="82"/>
-    <col min="23" max="23" width="22.25" style="82" customWidth="1"/>
-    <col min="24" max="24" width="22.375" style="82" customWidth="1"/>
-    <col min="25" max="25" width="19.875" style="82" customWidth="1"/>
-    <col min="26" max="26" width="9.5" style="75"/>
-    <col min="27" max="27" width="9.5" style="76"/>
+    <col min="1" max="1" width="44.453125" style="75" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" style="76"/>
+    <col min="3" max="3" width="22.7265625" style="76" customWidth="1"/>
+    <col min="4" max="4" width="18.453125" style="76" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="77" customWidth="1"/>
+    <col min="6" max="6" width="14.08984375" style="75"/>
+    <col min="7" max="7" width="10.7265625" style="78" customWidth="1"/>
+    <col min="8" max="8" width="10.36328125" style="79" customWidth="1"/>
+    <col min="9" max="9" width="9.453125" style="79"/>
+    <col min="10" max="10" width="11.26953125" style="80" customWidth="1"/>
+    <col min="11" max="11" width="11.6328125" style="76" customWidth="1"/>
+    <col min="12" max="12" width="19.7265625" style="76"/>
+    <col min="13" max="13" width="25.26953125" style="76"/>
+    <col min="14" max="14" width="20.7265625" style="77"/>
+    <col min="15" max="15" width="12.7265625" style="81" customWidth="1"/>
+    <col min="16" max="17" width="12.26953125" style="82" customWidth="1"/>
+    <col min="18" max="18" width="15.36328125" style="82"/>
+    <col min="19" max="19" width="10.90625" style="82"/>
+    <col min="20" max="20" width="30.90625" style="82"/>
+    <col min="21" max="22" width="35.36328125" style="82"/>
+    <col min="23" max="23" width="22.26953125" style="82" customWidth="1"/>
+    <col min="24" max="24" width="22.36328125" style="82" customWidth="1"/>
+    <col min="25" max="25" width="19.90625" style="82" customWidth="1"/>
+    <col min="26" max="26" width="9.453125" style="75"/>
+    <col min="27" max="27" width="9.453125" style="76"/>
     <col min="28" max="28" width="9" style="76"/>
-    <col min="29" max="29" width="22.875" style="76" customWidth="1"/>
-    <col min="30" max="30" width="11.625" style="80" customWidth="1"/>
-    <col min="31" max="31" width="11.625" style="76" customWidth="1"/>
-    <col min="32" max="32" width="14.125" style="76"/>
+    <col min="29" max="29" width="22.90625" style="76" customWidth="1"/>
+    <col min="30" max="30" width="11.6328125" style="80" customWidth="1"/>
+    <col min="31" max="31" width="11.6328125" style="76" customWidth="1"/>
+    <col min="32" max="32" width="14.08984375" style="76"/>
     <col min="33" max="33" width="56" style="83"/>
-    <col min="34" max="34" width="18.125" style="75" customWidth="1"/>
-    <col min="35" max="35" width="19.75" style="76"/>
-    <col min="36" max="36" width="13.625" style="76" customWidth="1"/>
-    <col min="37" max="37" width="15.375" style="78" customWidth="1"/>
-    <col min="38" max="38" width="15.375" style="79" customWidth="1"/>
-    <col min="39" max="39" width="9.125" style="76" customWidth="1"/>
-    <col min="40" max="40" width="9.375" style="76" customWidth="1"/>
-    <col min="41" max="41" width="11.5" style="76" customWidth="1"/>
-    <col min="42" max="42" width="19.875" style="76" customWidth="1"/>
-    <col min="43" max="45" width="20.125" style="80"/>
-    <col min="46" max="47" width="21.875" style="84" customWidth="1"/>
-    <col min="48" max="48" width="18.875" style="76" customWidth="1"/>
-    <col min="49" max="49" width="11.875" style="76" customWidth="1"/>
-    <col min="50" max="51" width="24.25" style="76" customWidth="1"/>
-    <col min="52" max="52" width="15.5" style="80" customWidth="1"/>
-    <col min="53" max="55" width="13.25" style="80" customWidth="1"/>
-    <col min="56" max="57" width="19.5" style="80" customWidth="1"/>
-    <col min="58" max="58" width="23.875" style="80" customWidth="1"/>
+    <col min="34" max="34" width="18.08984375" style="75" customWidth="1"/>
+    <col min="35" max="35" width="19.7265625" style="76"/>
+    <col min="36" max="36" width="13.6328125" style="76" customWidth="1"/>
+    <col min="37" max="37" width="15.36328125" style="78" customWidth="1"/>
+    <col min="38" max="38" width="15.36328125" style="79" customWidth="1"/>
+    <col min="39" max="39" width="9.08984375" style="76" customWidth="1"/>
+    <col min="40" max="40" width="9.36328125" style="76" customWidth="1"/>
+    <col min="41" max="41" width="11.453125" style="76" customWidth="1"/>
+    <col min="42" max="42" width="19.90625" style="76" customWidth="1"/>
+    <col min="43" max="45" width="20.08984375" style="80"/>
+    <col min="46" max="47" width="21.90625" style="84" customWidth="1"/>
+    <col min="48" max="48" width="18.90625" style="76" customWidth="1"/>
+    <col min="49" max="49" width="11.90625" style="76" customWidth="1"/>
+    <col min="50" max="51" width="24.26953125" style="76" customWidth="1"/>
+    <col min="52" max="52" width="15.453125" style="80" customWidth="1"/>
+    <col min="53" max="55" width="13.26953125" style="80" customWidth="1"/>
+    <col min="56" max="57" width="19.453125" style="80" customWidth="1"/>
+    <col min="58" max="58" width="23.90625" style="80" customWidth="1"/>
     <col min="59" max="59" width="9" style="76"/>
-    <col min="60" max="60" width="22.75" style="76" customWidth="1"/>
-    <col min="61" max="61" width="36.125" style="76" customWidth="1"/>
-    <col min="62" max="62" width="28.625" style="76"/>
-    <col min="63" max="64" width="33.125" style="76"/>
-    <col min="65" max="65" width="12.375" style="76" customWidth="1"/>
-    <col min="66" max="66" width="22.875" style="76" customWidth="1"/>
-    <col min="67" max="67" width="35.375" style="76"/>
-    <col min="68" max="68" width="25.25" style="76"/>
-    <col min="69" max="69" width="29.625" style="76"/>
-    <col min="70" max="71" width="15.375" style="76" customWidth="1"/>
-    <col min="72" max="72" width="20.875" style="76" customWidth="1"/>
-    <col min="73" max="73" width="15.375" style="76" customWidth="1"/>
-    <col min="74" max="74" width="20.75" style="76" customWidth="1"/>
-    <col min="75" max="75" width="16.625" style="76" customWidth="1"/>
-    <col min="76" max="76" width="15.75" style="76" customWidth="1"/>
-    <col min="77" max="77" width="19.375" style="76" customWidth="1"/>
-    <col min="78" max="79" width="14.5" style="76" customWidth="1"/>
-    <col min="80" max="85" width="16.625" style="76" customWidth="1"/>
-    <col min="86" max="90" width="19.5" style="76" customWidth="1"/>
-    <col min="91" max="91" width="19.5" style="85" customWidth="1"/>
+    <col min="60" max="60" width="22.7265625" style="76" customWidth="1"/>
+    <col min="61" max="61" width="36.08984375" style="76" customWidth="1"/>
+    <col min="62" max="62" width="28.6328125" style="76"/>
+    <col min="63" max="64" width="33.08984375" style="76"/>
+    <col min="65" max="65" width="12.36328125" style="76" customWidth="1"/>
+    <col min="66" max="66" width="22.90625" style="76" customWidth="1"/>
+    <col min="67" max="67" width="35.36328125" style="76"/>
+    <col min="68" max="68" width="25.26953125" style="76"/>
+    <col min="69" max="69" width="29.6328125" style="76"/>
+    <col min="70" max="71" width="15.36328125" style="76" customWidth="1"/>
+    <col min="72" max="72" width="20.90625" style="76" customWidth="1"/>
+    <col min="73" max="73" width="15.36328125" style="76" customWidth="1"/>
+    <col min="74" max="74" width="20.7265625" style="76" customWidth="1"/>
+    <col min="75" max="75" width="16.6328125" style="76" customWidth="1"/>
+    <col min="76" max="76" width="15.7265625" style="76" customWidth="1"/>
+    <col min="77" max="77" width="19.36328125" style="76" customWidth="1"/>
+    <col min="78" max="79" width="14.453125" style="76" customWidth="1"/>
+    <col min="80" max="85" width="16.6328125" style="76" customWidth="1"/>
+    <col min="86" max="90" width="19.453125" style="76" customWidth="1"/>
+    <col min="91" max="91" width="19.453125" style="85" customWidth="1"/>
     <col min="92" max="92" width="14" style="76" customWidth="1"/>
-    <col min="93" max="93" width="14.375" style="76" customWidth="1"/>
+    <col min="93" max="93" width="14.36328125" style="76" customWidth="1"/>
     <col min="94" max="97" width="19" style="76" customWidth="1"/>
-    <col min="98" max="98" width="14.875" style="80" customWidth="1"/>
-    <col min="99" max="99" width="19.75" style="77"/>
-    <col min="100" max="100" width="17.625" style="76" customWidth="1"/>
-    <col min="101" max="101" width="19.75" style="76"/>
-    <col min="102" max="102" width="16.375" style="76" customWidth="1"/>
-    <col min="103" max="103" width="13.5" style="84" customWidth="1"/>
-    <col min="104" max="104" width="14.625" style="78" customWidth="1"/>
-    <col min="105" max="105" width="22" style="192"/>
+    <col min="98" max="98" width="14.90625" style="80" customWidth="1"/>
+    <col min="99" max="99" width="19.7265625" style="77"/>
+    <col min="100" max="100" width="17.6328125" style="76" customWidth="1"/>
+    <col min="101" max="101" width="19.7265625" style="76"/>
+    <col min="102" max="102" width="16.36328125" style="76" customWidth="1"/>
+    <col min="103" max="103" width="13.453125" style="84" customWidth="1"/>
+    <col min="104" max="104" width="14.6328125" style="78" customWidth="1"/>
+    <col min="105" max="105" width="22" style="124"/>
     <col min="106" max="106" width="22" style="84"/>
     <col min="107" max="107" width="22" style="84" customWidth="1"/>
     <col min="108" max="108" width="22" style="79" customWidth="1"/>
-    <col min="109" max="109" width="13.875" style="79" customWidth="1"/>
-    <col min="110" max="110" width="16.5" style="76" customWidth="1"/>
-    <col min="111" max="111" width="16.125" style="80" customWidth="1"/>
-    <col min="112" max="112" width="16.875" style="75" customWidth="1"/>
-    <col min="113" max="113" width="17.875" style="76"/>
-    <col min="114" max="114" width="9.75" style="76"/>
-    <col min="115" max="117" width="17.875" style="76" customWidth="1"/>
-    <col min="118" max="118" width="26.5" style="76"/>
-    <col min="119" max="120" width="30.875" style="76"/>
-    <col min="121" max="122" width="26.5" style="76" customWidth="1"/>
+    <col min="109" max="109" width="13.90625" style="79" customWidth="1"/>
+    <col min="110" max="110" width="16.453125" style="76" customWidth="1"/>
+    <col min="111" max="111" width="16.08984375" style="80" customWidth="1"/>
+    <col min="112" max="112" width="16.90625" style="75" customWidth="1"/>
+    <col min="113" max="113" width="17.90625" style="76"/>
+    <col min="114" max="114" width="9.7265625" style="76"/>
+    <col min="115" max="117" width="17.90625" style="76" customWidth="1"/>
+    <col min="118" max="118" width="26.453125" style="76"/>
+    <col min="119" max="120" width="30.90625" style="76"/>
+    <col min="121" max="122" width="26.453125" style="76" customWidth="1"/>
     <col min="123" max="123" width="9" style="75"/>
-    <col min="124" max="124" width="13.875" style="78"/>
-    <col min="125" max="126" width="11.5" style="76" customWidth="1"/>
-    <col min="127" max="127" width="19.375" style="75" customWidth="1"/>
-    <col min="128" max="128" width="10.625" style="76" customWidth="1"/>
-    <col min="129" max="129" width="10.125" style="82" customWidth="1"/>
+    <col min="124" max="124" width="13.90625" style="78"/>
+    <col min="125" max="126" width="11.453125" style="76" customWidth="1"/>
+    <col min="127" max="127" width="19.36328125" style="75" customWidth="1"/>
+    <col min="128" max="128" width="10.6328125" style="76" customWidth="1"/>
+    <col min="129" max="129" width="10.08984375" style="82" customWidth="1"/>
     <col min="130" max="130" width="11" style="82" customWidth="1"/>
-    <col min="131" max="131" width="21.5" style="82" customWidth="1"/>
+    <col min="131" max="131" width="21.453125" style="82" customWidth="1"/>
     <col min="132" max="133" width="10" style="82" customWidth="1"/>
-    <col min="134" max="134" width="11.875" style="86" customWidth="1"/>
-    <col min="135" max="135" width="21.75" style="82" customWidth="1"/>
-    <col min="136" max="136" width="14.375" style="82" customWidth="1"/>
-    <col min="137" max="137" width="11.875" style="87" customWidth="1"/>
-    <col min="138" max="138" width="21.125" style="86" customWidth="1"/>
-    <col min="139" max="139" width="14.625" style="82" customWidth="1"/>
-    <col min="140" max="140" width="28.5" style="76" customWidth="1"/>
-    <col min="141" max="141" width="16.875" style="75" customWidth="1"/>
-    <col min="142" max="143" width="9.5" style="76"/>
+    <col min="134" max="134" width="11.90625" style="86" customWidth="1"/>
+    <col min="135" max="135" width="21.7265625" style="82" customWidth="1"/>
+    <col min="136" max="136" width="14.36328125" style="82" customWidth="1"/>
+    <col min="137" max="137" width="11.90625" style="87" customWidth="1"/>
+    <col min="138" max="138" width="21.08984375" style="86" customWidth="1"/>
+    <col min="139" max="139" width="14.6328125" style="82" customWidth="1"/>
+    <col min="140" max="140" width="28.453125" style="76" customWidth="1"/>
+    <col min="141" max="141" width="16.90625" style="75" customWidth="1"/>
+    <col min="142" max="143" width="9.453125" style="76"/>
     <col min="144" max="144" width="9" style="76"/>
-    <col min="145" max="145" width="12.625" style="80" customWidth="1"/>
-    <col min="146" max="146" width="11.375" style="77" customWidth="1"/>
-    <col min="147" max="147" width="16.25" style="75" customWidth="1"/>
-    <col min="148" max="148" width="16.125" style="76" customWidth="1"/>
-    <col min="149" max="149" width="15.875" style="76" customWidth="1"/>
-    <col min="150" max="150" width="11.25" style="76" customWidth="1"/>
-    <col min="151" max="151" width="23.75" style="77"/>
-    <col min="152" max="152" width="16.25" style="75" customWidth="1"/>
-    <col min="153" max="155" width="10.25" style="76" customWidth="1"/>
-    <col min="156" max="156" width="10.875" style="80" customWidth="1"/>
-    <col min="157" max="157" width="20.75" style="84" customWidth="1"/>
+    <col min="145" max="145" width="12.6328125" style="80" customWidth="1"/>
+    <col min="146" max="146" width="11.36328125" style="77" customWidth="1"/>
+    <col min="147" max="147" width="16.26953125" style="75" customWidth="1"/>
+    <col min="148" max="148" width="16.08984375" style="76" customWidth="1"/>
+    <col min="149" max="149" width="15.90625" style="76" customWidth="1"/>
+    <col min="150" max="150" width="11.26953125" style="76" customWidth="1"/>
+    <col min="151" max="151" width="23.7265625" style="77"/>
+    <col min="152" max="152" width="16.26953125" style="75" customWidth="1"/>
+    <col min="153" max="155" width="10.26953125" style="76" customWidth="1"/>
+    <col min="156" max="156" width="10.90625" style="80" customWidth="1"/>
+    <col min="157" max="157" width="20.7265625" style="84" customWidth="1"/>
     <col min="158" max="159" width="28" style="80"/>
-    <col min="160" max="160" width="26.5" style="76" customWidth="1"/>
-    <col min="161" max="161" width="29.125" style="76" customWidth="1"/>
-    <col min="162" max="162" width="14.75" style="76" customWidth="1"/>
+    <col min="160" max="160" width="26.453125" style="76" customWidth="1"/>
+    <col min="161" max="161" width="29.08984375" style="76" customWidth="1"/>
+    <col min="162" max="162" width="14.7265625" style="76" customWidth="1"/>
     <col min="163" max="163" width="15" style="76" customWidth="1"/>
-    <col min="164" max="164" width="22.875" style="80" customWidth="1"/>
-    <col min="165" max="165" width="23.625" style="80" customWidth="1"/>
-    <col min="166" max="166" width="21.625" style="78" customWidth="1"/>
-    <col min="167" max="167" width="24.75" style="78" customWidth="1"/>
-    <col min="168" max="168" width="12.25" style="124" customWidth="1"/>
-    <col min="169" max="169" width="15.25" style="82" customWidth="1"/>
-    <col min="170" max="170" width="28.375" style="82" customWidth="1"/>
-    <col min="171" max="171" width="25.25" style="82" customWidth="1"/>
-    <col min="172" max="172" width="17.75" style="82" customWidth="1"/>
-    <col min="173" max="173" width="9.75" style="82" customWidth="1"/>
+    <col min="164" max="164" width="22.90625" style="80" customWidth="1"/>
+    <col min="165" max="165" width="23.6328125" style="80" customWidth="1"/>
+    <col min="166" max="166" width="21.6328125" style="78" customWidth="1"/>
+    <col min="167" max="167" width="24.7265625" style="78" customWidth="1"/>
+    <col min="168" max="168" width="12.26953125" style="121" customWidth="1"/>
+    <col min="169" max="169" width="15.26953125" style="82" customWidth="1"/>
+    <col min="170" max="170" width="28.36328125" style="82" customWidth="1"/>
+    <col min="171" max="171" width="25.26953125" style="82" customWidth="1"/>
+    <col min="172" max="172" width="17.7265625" style="82" customWidth="1"/>
+    <col min="173" max="173" width="9.7265625" style="82" customWidth="1"/>
     <col min="174" max="174" width="11" style="82" customWidth="1"/>
-    <col min="175" max="175" width="19.375" style="88"/>
-    <col min="176" max="176" width="17.5" style="82" customWidth="1"/>
-    <col min="177" max="177" width="17.625" style="82" customWidth="1"/>
-    <col min="178" max="178" width="17.5" style="82" customWidth="1"/>
-    <col min="179" max="179" width="18.5" style="82" customWidth="1"/>
-    <col min="180" max="180" width="18.25" style="82" customWidth="1"/>
-    <col min="181" max="181" width="15.375" style="82"/>
-    <col min="182" max="182" width="17.5" style="82" customWidth="1"/>
-    <col min="183" max="183" width="17.125" style="87" customWidth="1"/>
-    <col min="184" max="184" width="16.5" style="87" customWidth="1"/>
-    <col min="185" max="185" width="12.75" style="82" customWidth="1"/>
-    <col min="186" max="186" width="12.875" style="82" customWidth="1"/>
-    <col min="187" max="188" width="14.25" style="87" customWidth="1"/>
+    <col min="175" max="175" width="19.36328125" style="88"/>
+    <col min="176" max="176" width="17.453125" style="82" customWidth="1"/>
+    <col min="177" max="177" width="17.6328125" style="82" customWidth="1"/>
+    <col min="178" max="178" width="17.453125" style="82" customWidth="1"/>
+    <col min="179" max="179" width="18.453125" style="82" customWidth="1"/>
+    <col min="180" max="180" width="18.26953125" style="82" customWidth="1"/>
+    <col min="181" max="181" width="15.36328125" style="82"/>
+    <col min="182" max="182" width="17.453125" style="82" customWidth="1"/>
+    <col min="183" max="183" width="17.08984375" style="87" customWidth="1"/>
+    <col min="184" max="184" width="16.453125" style="87" customWidth="1"/>
+    <col min="185" max="185" width="12.7265625" style="82" customWidth="1"/>
+    <col min="186" max="186" width="12.90625" style="82" customWidth="1"/>
+    <col min="187" max="188" width="14.26953125" style="87" customWidth="1"/>
     <col min="189" max="189" width="21" style="87"/>
-    <col min="190" max="190" width="25.5" style="87"/>
-    <col min="191" max="191" width="17.875" style="87"/>
-    <col min="192" max="192" width="16.25" style="75" customWidth="1"/>
+    <col min="190" max="190" width="25.453125" style="87"/>
+    <col min="191" max="191" width="17.90625" style="87"/>
+    <col min="192" max="192" width="16.26953125" style="75" customWidth="1"/>
     <col min="193" max="193" width="9" style="76"/>
-    <col min="194" max="194" width="12.5" style="84" customWidth="1"/>
+    <col min="194" max="194" width="12.453125" style="84" customWidth="1"/>
     <col min="195" max="195" width="11" style="78" customWidth="1"/>
-    <col min="196" max="196" width="13.125" style="89" customWidth="1"/>
+    <col min="196" max="196" width="13.08984375" style="89" customWidth="1"/>
     <col min="197" max="197" width="20" style="76" customWidth="1"/>
-    <col min="198" max="198" width="15.375" style="76"/>
-    <col min="199" max="199" width="17.5" style="76"/>
-    <col min="200" max="200" width="11.625" style="78" customWidth="1"/>
-    <col min="201" max="202" width="11.625" style="76" customWidth="1"/>
-    <col min="203" max="203" width="17.625" style="76"/>
-    <col min="204" max="204" width="19.75" style="76"/>
-    <col min="205" max="205" width="23.25" style="80"/>
-    <col min="206" max="206" width="23.25" style="90"/>
-    <col min="207" max="207" width="11.625" style="76" customWidth="1"/>
-    <col min="208" max="208" width="35.375" style="76"/>
-    <col min="209" max="209" width="38.5" style="76"/>
-    <col min="210" max="210" width="28.625" style="76"/>
-    <col min="211" max="212" width="33.125" style="76"/>
-    <col min="213" max="213" width="11.625" style="76" customWidth="1"/>
-    <col min="214" max="214" width="16.375" style="76"/>
-    <col min="215" max="215" width="19.75" style="76"/>
-    <col min="216" max="216" width="35.375" style="76"/>
-    <col min="217" max="217" width="25.25" style="76"/>
-    <col min="218" max="218" width="29.625" style="76"/>
-    <col min="219" max="224" width="18.625" style="76"/>
-    <col min="225" max="225" width="16.625" style="76" customWidth="1"/>
-    <col min="226" max="226" width="18.625" style="76"/>
-    <col min="227" max="227" width="17.625" style="75"/>
-    <col min="228" max="230" width="13.125" style="76" customWidth="1"/>
-    <col min="231" max="231" width="13.125" style="78" customWidth="1"/>
-    <col min="232" max="232" width="14.75" style="89" customWidth="1"/>
-    <col min="233" max="233" width="16.125" style="75" customWidth="1"/>
-    <col min="234" max="236" width="16.125" style="76" customWidth="1"/>
-    <col min="237" max="237" width="21.75" style="76"/>
-    <col min="238" max="238" width="17.5" style="76"/>
-    <col min="239" max="239" width="27.625" style="76" customWidth="1"/>
+    <col min="198" max="198" width="15.36328125" style="76"/>
+    <col min="199" max="199" width="17.453125" style="76"/>
+    <col min="200" max="200" width="11.6328125" style="78" customWidth="1"/>
+    <col min="201" max="202" width="11.6328125" style="76" customWidth="1"/>
+    <col min="203" max="203" width="17.6328125" style="76"/>
+    <col min="204" max="204" width="19.7265625" style="76"/>
+    <col min="205" max="205" width="23.26953125" style="80"/>
+    <col min="206" max="206" width="23.26953125" style="90"/>
+    <col min="207" max="207" width="11.6328125" style="76" customWidth="1"/>
+    <col min="208" max="208" width="35.36328125" style="76"/>
+    <col min="209" max="209" width="38.453125" style="76"/>
+    <col min="210" max="210" width="28.6328125" style="76"/>
+    <col min="211" max="212" width="33.08984375" style="76"/>
+    <col min="213" max="213" width="11.6328125" style="76" customWidth="1"/>
+    <col min="214" max="214" width="16.36328125" style="76"/>
+    <col min="215" max="215" width="19.7265625" style="76"/>
+    <col min="216" max="216" width="35.36328125" style="76"/>
+    <col min="217" max="217" width="25.26953125" style="76"/>
+    <col min="218" max="218" width="29.6328125" style="76"/>
+    <col min="219" max="224" width="18.6328125" style="76"/>
+    <col min="225" max="225" width="16.6328125" style="76" customWidth="1"/>
+    <col min="226" max="226" width="18.6328125" style="76"/>
+    <col min="227" max="227" width="17.6328125" style="75"/>
+    <col min="228" max="230" width="13.08984375" style="76" customWidth="1"/>
+    <col min="231" max="231" width="13.08984375" style="78" customWidth="1"/>
+    <col min="232" max="232" width="14.7265625" style="89" customWidth="1"/>
+    <col min="233" max="233" width="16.08984375" style="75" customWidth="1"/>
+    <col min="234" max="236" width="16.08984375" style="76" customWidth="1"/>
+    <col min="237" max="237" width="21.7265625" style="76"/>
+    <col min="238" max="238" width="17.453125" style="76"/>
+    <col min="239" max="239" width="27.6328125" style="76" customWidth="1"/>
     <col min="240" max="240" width="23" style="76"/>
-    <col min="241" max="242" width="19.75" style="76"/>
-    <col min="243" max="243" width="19.75" style="76" customWidth="1"/>
-    <col min="244" max="244" width="29.625" style="76"/>
-    <col min="245" max="245" width="34.125" style="76"/>
-    <col min="246" max="246" width="34.125" style="76" customWidth="1"/>
-    <col min="247" max="247" width="34.125" style="77" customWidth="1"/>
-    <col min="248" max="252" width="34.125" style="76" customWidth="1"/>
-    <col min="253" max="253" width="34.125" style="91" customWidth="1"/>
-    <col min="254" max="260" width="34.125" style="76" customWidth="1"/>
-    <col min="261" max="261" width="34.125" style="92" customWidth="1"/>
-    <col min="262" max="267" width="34.125" style="74" customWidth="1"/>
-    <col min="268" max="268" width="15.75" style="82" customWidth="1"/>
+    <col min="241" max="242" width="19.7265625" style="76"/>
+    <col min="243" max="243" width="19.7265625" style="76" customWidth="1"/>
+    <col min="244" max="244" width="29.6328125" style="76"/>
+    <col min="245" max="245" width="34.08984375" style="76"/>
+    <col min="246" max="246" width="34.08984375" style="76" customWidth="1"/>
+    <col min="247" max="247" width="34.08984375" style="77" customWidth="1"/>
+    <col min="248" max="252" width="34.08984375" style="76" customWidth="1"/>
+    <col min="253" max="253" width="34.08984375" style="91" customWidth="1"/>
+    <col min="254" max="260" width="34.08984375" style="76" customWidth="1"/>
+    <col min="261" max="261" width="34.08984375" style="92" customWidth="1"/>
+    <col min="262" max="267" width="34.08984375" style="74" customWidth="1"/>
+    <col min="268" max="268" width="15.7265625" style="82" customWidth="1"/>
     <col min="269" max="269" width="9" style="82"/>
-    <col min="270" max="270" width="12.5" style="86" customWidth="1"/>
+    <col min="270" max="270" width="12.453125" style="86" customWidth="1"/>
     <col min="271" max="271" width="11" style="88" customWidth="1"/>
-    <col min="272" max="272" width="13.125" style="87" customWidth="1"/>
-    <col min="273" max="273" width="16.5" style="75" customWidth="1"/>
-    <col min="274" max="282" width="9" style="93"/>
-    <col min="283" max="16384" width="9" style="1"/>
+    <col min="272" max="272" width="13.08984375" style="87" customWidth="1"/>
+    <col min="273" max="273" width="16.453125" style="75" customWidth="1"/>
+    <col min="274" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:282" s="72" customFormat="1">
-      <c r="A1" s="126" t="s">
+    <row r="1" spans="1:273" s="72" customFormat="1">
+      <c r="A1" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="128" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="130"/>
-      <c r="H1" s="130"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="130"/>
-      <c r="M1" s="130"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="133" t="s">
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="132" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
-      <c r="R1" s="133"/>
-      <c r="S1" s="133"/>
-      <c r="T1" s="133"/>
-      <c r="U1" s="133"/>
-      <c r="V1" s="133"/>
-      <c r="W1" s="133"/>
-      <c r="X1" s="133"/>
-      <c r="Y1" s="133"/>
-      <c r="Z1" s="129" t="s">
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="132"/>
+      <c r="T1" s="132"/>
+      <c r="U1" s="132"/>
+      <c r="V1" s="132"/>
+      <c r="W1" s="132"/>
+      <c r="X1" s="132"/>
+      <c r="Y1" s="132"/>
+      <c r="Z1" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="130"/>
-      <c r="AB1" s="130"/>
-      <c r="AC1" s="130"/>
-      <c r="AD1" s="130"/>
-      <c r="AE1" s="130"/>
-      <c r="AF1" s="130"/>
-      <c r="AG1" s="132"/>
-      <c r="AH1" s="126" t="s">
+      <c r="AA1" s="129"/>
+      <c r="AB1" s="129"/>
+      <c r="AC1" s="129"/>
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="129"/>
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="131"/>
+      <c r="AH1" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="127"/>
-      <c r="AJ1" s="127"/>
-      <c r="AK1" s="127"/>
-      <c r="AL1" s="127"/>
-      <c r="AM1" s="127"/>
-      <c r="AN1" s="127"/>
-      <c r="AO1" s="127"/>
-      <c r="AP1" s="127"/>
-      <c r="AQ1" s="127"/>
-      <c r="AR1" s="127"/>
-      <c r="AS1" s="127"/>
-      <c r="AT1" s="127"/>
-      <c r="AU1" s="127"/>
-      <c r="AV1" s="127"/>
-      <c r="AW1" s="127"/>
-      <c r="AX1" s="127"/>
-      <c r="AY1" s="127"/>
-      <c r="AZ1" s="127"/>
-      <c r="BA1" s="127"/>
-      <c r="BB1" s="127"/>
-      <c r="BC1" s="127"/>
-      <c r="BD1" s="127"/>
-      <c r="BE1" s="127"/>
-      <c r="BF1" s="127"/>
-      <c r="BG1" s="127"/>
-      <c r="BH1" s="127"/>
-      <c r="BI1" s="127"/>
-      <c r="BJ1" s="127"/>
-      <c r="BK1" s="127"/>
-      <c r="BL1" s="127"/>
-      <c r="BM1" s="127"/>
-      <c r="BN1" s="127"/>
-      <c r="BO1" s="127"/>
-      <c r="BP1" s="127"/>
-      <c r="BQ1" s="127"/>
-      <c r="BR1" s="127"/>
-      <c r="BS1" s="127"/>
-      <c r="BT1" s="127"/>
-      <c r="BU1" s="127"/>
-      <c r="BV1" s="127"/>
-      <c r="BW1" s="127"/>
-      <c r="BX1" s="127"/>
-      <c r="BY1" s="127"/>
-      <c r="BZ1" s="127"/>
-      <c r="CA1" s="127"/>
-      <c r="CB1" s="134"/>
-      <c r="CC1" s="134"/>
-      <c r="CD1" s="134"/>
-      <c r="CE1" s="134"/>
-      <c r="CF1" s="134"/>
-      <c r="CG1" s="134"/>
-      <c r="CH1" s="134"/>
-      <c r="CI1" s="134"/>
-      <c r="CJ1" s="134"/>
-      <c r="CK1" s="134"/>
-      <c r="CL1" s="134"/>
-      <c r="CM1" s="135"/>
-      <c r="CN1" s="127"/>
-      <c r="CO1" s="127"/>
-      <c r="CP1" s="127"/>
-      <c r="CQ1" s="127"/>
-      <c r="CR1" s="127"/>
-      <c r="CS1" s="127"/>
-      <c r="CT1" s="127"/>
-      <c r="CU1" s="128"/>
-      <c r="CV1" s="136" t="s">
+      <c r="AI1" s="126"/>
+      <c r="AJ1" s="126"/>
+      <c r="AK1" s="126"/>
+      <c r="AL1" s="126"/>
+      <c r="AM1" s="126"/>
+      <c r="AN1" s="126"/>
+      <c r="AO1" s="126"/>
+      <c r="AP1" s="126"/>
+      <c r="AQ1" s="126"/>
+      <c r="AR1" s="126"/>
+      <c r="AS1" s="126"/>
+      <c r="AT1" s="126"/>
+      <c r="AU1" s="126"/>
+      <c r="AV1" s="126"/>
+      <c r="AW1" s="126"/>
+      <c r="AX1" s="126"/>
+      <c r="AY1" s="126"/>
+      <c r="AZ1" s="126"/>
+      <c r="BA1" s="126"/>
+      <c r="BB1" s="126"/>
+      <c r="BC1" s="126"/>
+      <c r="BD1" s="126"/>
+      <c r="BE1" s="126"/>
+      <c r="BF1" s="126"/>
+      <c r="BG1" s="126"/>
+      <c r="BH1" s="126"/>
+      <c r="BI1" s="126"/>
+      <c r="BJ1" s="126"/>
+      <c r="BK1" s="126"/>
+      <c r="BL1" s="126"/>
+      <c r="BM1" s="126"/>
+      <c r="BN1" s="126"/>
+      <c r="BO1" s="126"/>
+      <c r="BP1" s="126"/>
+      <c r="BQ1" s="126"/>
+      <c r="BR1" s="126"/>
+      <c r="BS1" s="126"/>
+      <c r="BT1" s="126"/>
+      <c r="BU1" s="126"/>
+      <c r="BV1" s="126"/>
+      <c r="BW1" s="126"/>
+      <c r="BX1" s="126"/>
+      <c r="BY1" s="126"/>
+      <c r="BZ1" s="126"/>
+      <c r="CA1" s="126"/>
+      <c r="CB1" s="133"/>
+      <c r="CC1" s="133"/>
+      <c r="CD1" s="133"/>
+      <c r="CE1" s="133"/>
+      <c r="CF1" s="133"/>
+      <c r="CG1" s="133"/>
+      <c r="CH1" s="133"/>
+      <c r="CI1" s="133"/>
+      <c r="CJ1" s="133"/>
+      <c r="CK1" s="133"/>
+      <c r="CL1" s="133"/>
+      <c r="CM1" s="134"/>
+      <c r="CN1" s="126"/>
+      <c r="CO1" s="126"/>
+      <c r="CP1" s="126"/>
+      <c r="CQ1" s="126"/>
+      <c r="CR1" s="126"/>
+      <c r="CS1" s="126"/>
+      <c r="CT1" s="126"/>
+      <c r="CU1" s="127"/>
+      <c r="CV1" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="CW1" s="133"/>
-      <c r="CX1" s="133"/>
-      <c r="CY1" s="133"/>
-      <c r="CZ1" s="133"/>
-      <c r="DA1" s="133"/>
-      <c r="DB1" s="133"/>
-      <c r="DC1" s="133"/>
-      <c r="DD1" s="133"/>
-      <c r="DE1" s="133"/>
-      <c r="DF1" s="133"/>
-      <c r="DG1" s="137"/>
-      <c r="DH1" s="138" t="s">
+      <c r="CW1" s="132"/>
+      <c r="CX1" s="132"/>
+      <c r="CY1" s="132"/>
+      <c r="CZ1" s="132"/>
+      <c r="DA1" s="132"/>
+      <c r="DB1" s="132"/>
+      <c r="DC1" s="132"/>
+      <c r="DD1" s="132"/>
+      <c r="DE1" s="132"/>
+      <c r="DF1" s="132"/>
+      <c r="DG1" s="136"/>
+      <c r="DH1" s="137" t="s">
         <v>6</v>
       </c>
-      <c r="DI1" s="139"/>
-      <c r="DJ1" s="139"/>
-      <c r="DK1" s="139"/>
-      <c r="DL1" s="139"/>
-      <c r="DM1" s="139"/>
-      <c r="DN1" s="139"/>
-      <c r="DO1" s="139"/>
-      <c r="DP1" s="139"/>
-      <c r="DQ1" s="139"/>
-      <c r="DR1" s="139"/>
-      <c r="DS1" s="140" t="s">
+      <c r="DI1" s="138"/>
+      <c r="DJ1" s="138"/>
+      <c r="DK1" s="138"/>
+      <c r="DL1" s="138"/>
+      <c r="DM1" s="138"/>
+      <c r="DN1" s="138"/>
+      <c r="DO1" s="138"/>
+      <c r="DP1" s="138"/>
+      <c r="DQ1" s="138"/>
+      <c r="DR1" s="138"/>
+      <c r="DS1" s="139" t="s">
         <v>7</v>
       </c>
-      <c r="DT1" s="141"/>
-      <c r="DU1" s="141"/>
-      <c r="DV1" s="141"/>
-      <c r="DW1" s="142" t="s">
+      <c r="DT1" s="140"/>
+      <c r="DU1" s="140"/>
+      <c r="DV1" s="140"/>
+      <c r="DW1" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="DX1" s="131"/>
-      <c r="DY1" s="143"/>
-      <c r="DZ1" s="143"/>
-      <c r="EA1" s="143"/>
-      <c r="EB1" s="143"/>
-      <c r="EC1" s="143"/>
-      <c r="ED1" s="143"/>
-      <c r="EE1" s="143"/>
-      <c r="EF1" s="143"/>
-      <c r="EG1" s="143"/>
-      <c r="EH1" s="143"/>
-      <c r="EI1" s="143"/>
-      <c r="EJ1" s="144"/>
-      <c r="EK1" s="138" t="s">
+      <c r="DX1" s="130"/>
+      <c r="DY1" s="142"/>
+      <c r="DZ1" s="142"/>
+      <c r="EA1" s="142"/>
+      <c r="EB1" s="142"/>
+      <c r="EC1" s="142"/>
+      <c r="ED1" s="142"/>
+      <c r="EE1" s="142"/>
+      <c r="EF1" s="142"/>
+      <c r="EG1" s="142"/>
+      <c r="EH1" s="142"/>
+      <c r="EI1" s="142"/>
+      <c r="EJ1" s="143"/>
+      <c r="EK1" s="137" t="s">
         <v>9</v>
       </c>
-      <c r="EL1" s="139"/>
-      <c r="EM1" s="139"/>
-      <c r="EN1" s="139"/>
-      <c r="EO1" s="139"/>
-      <c r="EP1" s="145"/>
-      <c r="EQ1" s="138" t="s">
+      <c r="EL1" s="138"/>
+      <c r="EM1" s="138"/>
+      <c r="EN1" s="138"/>
+      <c r="EO1" s="138"/>
+      <c r="EP1" s="144"/>
+      <c r="EQ1" s="137" t="s">
         <v>10</v>
       </c>
-      <c r="ER1" s="139"/>
-      <c r="ES1" s="139"/>
-      <c r="ET1" s="139"/>
-      <c r="EU1" s="145"/>
-      <c r="EV1" s="138" t="s">
+      <c r="ER1" s="138"/>
+      <c r="ES1" s="138"/>
+      <c r="ET1" s="138"/>
+      <c r="EU1" s="144"/>
+      <c r="EV1" s="137" t="s">
         <v>11</v>
       </c>
-      <c r="EW1" s="139"/>
-      <c r="EX1" s="139"/>
-      <c r="EY1" s="139"/>
-      <c r="EZ1" s="139"/>
-      <c r="FA1" s="139"/>
-      <c r="FB1" s="139"/>
-      <c r="FC1" s="139"/>
-      <c r="FD1" s="139"/>
-      <c r="FE1" s="139"/>
-      <c r="FF1" s="139"/>
-      <c r="FG1" s="139"/>
-      <c r="FH1" s="139"/>
-      <c r="FI1" s="139"/>
-      <c r="FJ1" s="139"/>
-      <c r="FK1" s="139"/>
-      <c r="FL1" s="145"/>
-      <c r="FM1" s="131" t="s">
+      <c r="EW1" s="138"/>
+      <c r="EX1" s="138"/>
+      <c r="EY1" s="138"/>
+      <c r="EZ1" s="138"/>
+      <c r="FA1" s="138"/>
+      <c r="FB1" s="138"/>
+      <c r="FC1" s="138"/>
+      <c r="FD1" s="138"/>
+      <c r="FE1" s="138"/>
+      <c r="FF1" s="138"/>
+      <c r="FG1" s="138"/>
+      <c r="FH1" s="138"/>
+      <c r="FI1" s="138"/>
+      <c r="FJ1" s="138"/>
+      <c r="FK1" s="138"/>
+      <c r="FL1" s="144"/>
+      <c r="FM1" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="FN1" s="131"/>
-      <c r="FO1" s="131"/>
-      <c r="FP1" s="131"/>
-      <c r="FQ1" s="131"/>
-      <c r="FR1" s="131"/>
-      <c r="FS1" s="131"/>
-      <c r="FT1" s="131"/>
-      <c r="FU1" s="131"/>
-      <c r="FV1" s="131"/>
-      <c r="FW1" s="131"/>
-      <c r="FX1" s="131"/>
-      <c r="FY1" s="131"/>
-      <c r="FZ1" s="131"/>
-      <c r="GA1" s="131"/>
-      <c r="GB1" s="131"/>
-      <c r="GC1" s="131"/>
-      <c r="GD1" s="131"/>
-      <c r="GE1" s="131"/>
-      <c r="GF1" s="131"/>
-      <c r="GG1" s="131"/>
-      <c r="GH1" s="131"/>
-      <c r="GI1" s="131"/>
-      <c r="GJ1" s="138" t="s">
+      <c r="FN1" s="130"/>
+      <c r="FO1" s="130"/>
+      <c r="FP1" s="130"/>
+      <c r="FQ1" s="130"/>
+      <c r="FR1" s="130"/>
+      <c r="FS1" s="130"/>
+      <c r="FT1" s="130"/>
+      <c r="FU1" s="130"/>
+      <c r="FV1" s="130"/>
+      <c r="FW1" s="130"/>
+      <c r="FX1" s="130"/>
+      <c r="FY1" s="130"/>
+      <c r="FZ1" s="130"/>
+      <c r="GA1" s="130"/>
+      <c r="GB1" s="130"/>
+      <c r="GC1" s="130"/>
+      <c r="GD1" s="130"/>
+      <c r="GE1" s="130"/>
+      <c r="GF1" s="130"/>
+      <c r="GG1" s="130"/>
+      <c r="GH1" s="130"/>
+      <c r="GI1" s="130"/>
+      <c r="GJ1" s="137" t="s">
         <v>13</v>
       </c>
-      <c r="GK1" s="139"/>
-      <c r="GL1" s="139"/>
-      <c r="GM1" s="139"/>
-      <c r="GN1" s="145"/>
-      <c r="GO1" s="129" t="s">
+      <c r="GK1" s="138"/>
+      <c r="GL1" s="138"/>
+      <c r="GM1" s="138"/>
+      <c r="GN1" s="144"/>
+      <c r="GO1" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="GP1" s="130"/>
-      <c r="GQ1" s="130"/>
-      <c r="GR1" s="130"/>
-      <c r="GS1" s="130"/>
-      <c r="GT1" s="130"/>
-      <c r="GU1" s="130"/>
-      <c r="GV1" s="130"/>
-      <c r="GW1" s="130"/>
-      <c r="GX1" s="130"/>
-      <c r="GY1" s="130"/>
-      <c r="GZ1" s="130"/>
-      <c r="HA1" s="130"/>
-      <c r="HB1" s="130"/>
-      <c r="HC1" s="130"/>
-      <c r="HD1" s="130"/>
-      <c r="HE1" s="130"/>
-      <c r="HF1" s="130"/>
-      <c r="HG1" s="130"/>
-      <c r="HH1" s="130"/>
-      <c r="HI1" s="130"/>
-      <c r="HJ1" s="130"/>
-      <c r="HK1" s="130"/>
-      <c r="HL1" s="130"/>
-      <c r="HM1" s="130"/>
-      <c r="HN1" s="130"/>
-      <c r="HO1" s="130"/>
-      <c r="HP1" s="130"/>
-      <c r="HQ1" s="127"/>
-      <c r="HR1" s="130"/>
-      <c r="HS1" s="129" t="s">
+      <c r="GP1" s="129"/>
+      <c r="GQ1" s="129"/>
+      <c r="GR1" s="129"/>
+      <c r="GS1" s="129"/>
+      <c r="GT1" s="129"/>
+      <c r="GU1" s="129"/>
+      <c r="GV1" s="129"/>
+      <c r="GW1" s="129"/>
+      <c r="GX1" s="129"/>
+      <c r="GY1" s="129"/>
+      <c r="GZ1" s="129"/>
+      <c r="HA1" s="129"/>
+      <c r="HB1" s="129"/>
+      <c r="HC1" s="129"/>
+      <c r="HD1" s="129"/>
+      <c r="HE1" s="129"/>
+      <c r="HF1" s="129"/>
+      <c r="HG1" s="129"/>
+      <c r="HH1" s="129"/>
+      <c r="HI1" s="129"/>
+      <c r="HJ1" s="129"/>
+      <c r="HK1" s="129"/>
+      <c r="HL1" s="129"/>
+      <c r="HM1" s="129"/>
+      <c r="HN1" s="129"/>
+      <c r="HO1" s="129"/>
+      <c r="HP1" s="129"/>
+      <c r="HQ1" s="126"/>
+      <c r="HR1" s="129"/>
+      <c r="HS1" s="128" t="s">
         <v>15</v>
       </c>
-      <c r="HT1" s="130"/>
-      <c r="HU1" s="130"/>
-      <c r="HV1" s="130"/>
-      <c r="HW1" s="130"/>
-      <c r="HX1" s="132"/>
-      <c r="HY1" s="129" t="s">
+      <c r="HT1" s="129"/>
+      <c r="HU1" s="129"/>
+      <c r="HV1" s="129"/>
+      <c r="HW1" s="129"/>
+      <c r="HX1" s="131"/>
+      <c r="HY1" s="128" t="s">
         <v>16</v>
       </c>
-      <c r="HZ1" s="130"/>
-      <c r="IA1" s="130"/>
-      <c r="IB1" s="130"/>
-      <c r="IC1" s="130"/>
-      <c r="ID1" s="130"/>
-      <c r="IE1" s="130"/>
-      <c r="IF1" s="130"/>
-      <c r="IG1" s="130"/>
-      <c r="IH1" s="130"/>
-      <c r="II1" s="130"/>
-      <c r="IJ1" s="130"/>
-      <c r="IK1" s="130"/>
-      <c r="IL1" s="130"/>
-      <c r="IM1" s="132"/>
-      <c r="IN1" s="142" t="s">
+      <c r="HZ1" s="129"/>
+      <c r="IA1" s="129"/>
+      <c r="IB1" s="129"/>
+      <c r="IC1" s="129"/>
+      <c r="ID1" s="129"/>
+      <c r="IE1" s="129"/>
+      <c r="IF1" s="129"/>
+      <c r="IG1" s="129"/>
+      <c r="IH1" s="129"/>
+      <c r="II1" s="129"/>
+      <c r="IJ1" s="129"/>
+      <c r="IK1" s="129"/>
+      <c r="IL1" s="129"/>
+      <c r="IM1" s="131"/>
+      <c r="IN1" s="141" t="s">
         <v>17</v>
       </c>
-      <c r="IO1" s="143"/>
-      <c r="IP1" s="143"/>
-      <c r="IQ1" s="143"/>
-      <c r="IR1" s="143"/>
-      <c r="IS1" s="143"/>
-      <c r="IT1" s="143"/>
-      <c r="IU1" s="143"/>
-      <c r="IV1" s="143"/>
-      <c r="IW1" s="143"/>
-      <c r="IX1" s="143"/>
-      <c r="IY1" s="143"/>
-      <c r="IZ1" s="143"/>
-      <c r="JA1" s="143"/>
-      <c r="JB1" s="143"/>
-      <c r="JC1" s="143"/>
-      <c r="JD1" s="143"/>
-      <c r="JE1" s="143"/>
-      <c r="JF1" s="143"/>
-      <c r="JG1" s="144"/>
-      <c r="JH1" s="142" t="s">
+      <c r="IO1" s="142"/>
+      <c r="IP1" s="142"/>
+      <c r="IQ1" s="142"/>
+      <c r="IR1" s="142"/>
+      <c r="IS1" s="142"/>
+      <c r="IT1" s="142"/>
+      <c r="IU1" s="142"/>
+      <c r="IV1" s="142"/>
+      <c r="IW1" s="142"/>
+      <c r="IX1" s="142"/>
+      <c r="IY1" s="142"/>
+      <c r="IZ1" s="142"/>
+      <c r="JA1" s="142"/>
+      <c r="JB1" s="142"/>
+      <c r="JC1" s="142"/>
+      <c r="JD1" s="142"/>
+      <c r="JE1" s="142"/>
+      <c r="JF1" s="142"/>
+      <c r="JG1" s="143"/>
+      <c r="JH1" s="141" t="s">
         <v>18</v>
       </c>
-      <c r="JI1" s="143"/>
-      <c r="JJ1" s="143"/>
-      <c r="JK1" s="143"/>
-      <c r="JL1" s="143"/>
-      <c r="JM1" s="118"/>
-      <c r="JN1" s="119"/>
-      <c r="JO1" s="119"/>
-      <c r="JP1" s="119"/>
-      <c r="JQ1" s="119"/>
-      <c r="JR1" s="119"/>
-      <c r="JS1" s="119"/>
-      <c r="JT1" s="119"/>
-      <c r="JU1" s="119"/>
-      <c r="JV1" s="119"/>
-    </row>
-    <row r="2" spans="1:282" s="73" customFormat="1">
-      <c r="A2" s="94" t="s">
+      <c r="JI1" s="142"/>
+      <c r="JJ1" s="142"/>
+      <c r="JK1" s="142"/>
+      <c r="JL1" s="142"/>
+      <c r="JM1" s="117"/>
+    </row>
+    <row r="2" spans="1:273" s="73" customFormat="1">
+      <c r="A2" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="95" t="s">
+      <c r="C2" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="95" t="s">
+      <c r="D2" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="96" t="s">
+      <c r="E2" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="97" t="s">
+      <c r="F2" s="96" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="97" t="s">
+      <c r="G2" s="96" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="97" t="s">
+      <c r="H2" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="97" t="s">
+      <c r="I2" s="96" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="100" t="s">
+      <c r="J2" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="101" t="s">
+      <c r="K2" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="102" t="s">
+      <c r="L2" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="97" t="s">
+      <c r="M2" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="97" t="s">
+      <c r="N2" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="O2" s="103" t="s">
+      <c r="O2" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="P2" s="103" t="s">
+      <c r="P2" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="Q2" s="103" t="s">
+      <c r="Q2" s="102" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="103" t="s">
+      <c r="R2" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="103" t="s">
+      <c r="S2" s="102" t="s">
         <v>37</v>
       </c>
-      <c r="T2" s="103" t="s">
+      <c r="T2" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="U2" s="103" t="s">
+      <c r="U2" s="102" t="s">
         <v>39</v>
       </c>
-      <c r="V2" s="103" t="s">
+      <c r="V2" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="W2" s="103" t="s">
+      <c r="W2" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="X2" s="103" t="s">
+      <c r="X2" s="102" t="s">
         <v>42</v>
       </c>
-      <c r="Y2" s="103" t="s">
+      <c r="Y2" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="Z2" s="97" t="s">
+      <c r="Z2" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="97" t="s">
+      <c r="AA2" s="96" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="97" t="s">
+      <c r="AB2" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="AC2" s="97" t="s">
+      <c r="AC2" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="AD2" s="97" t="s">
+      <c r="AD2" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="AE2" s="97" t="s">
+      <c r="AE2" s="96" t="s">
         <v>29</v>
       </c>
-      <c r="AF2" s="97" t="s">
+      <c r="AF2" s="96" t="s">
         <v>46</v>
       </c>
-      <c r="AG2" s="97" t="s">
+      <c r="AG2" s="96" t="s">
         <v>47</v>
       </c>
-      <c r="AH2" s="103" t="s">
+      <c r="AH2" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="AI2" s="103" t="s">
+      <c r="AI2" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="AJ2" s="103" t="s">
+      <c r="AJ2" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="AK2" s="103" t="s">
+      <c r="AK2" s="102" t="s">
         <v>50</v>
       </c>
-      <c r="AL2" s="104" t="s">
+      <c r="AL2" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="AM2" s="103" t="s">
+      <c r="AM2" s="102" t="s">
         <v>52</v>
       </c>
-      <c r="AN2" s="103" t="s">
+      <c r="AN2" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="AO2" s="103" t="s">
+      <c r="AO2" s="102" t="s">
         <v>53</v>
       </c>
-      <c r="AP2" s="103" t="s">
+      <c r="AP2" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="AQ2" s="103" t="s">
+      <c r="AQ2" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="AR2" s="103" t="s">
+      <c r="AR2" s="102" t="s">
         <v>56</v>
       </c>
-      <c r="AS2" s="103" t="s">
+      <c r="AS2" s="102" t="s">
         <v>57</v>
       </c>
-      <c r="AT2" s="103" t="s">
+      <c r="AT2" s="102" t="s">
         <v>58</v>
       </c>
-      <c r="AU2" s="103" t="s">
+      <c r="AU2" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="AV2" s="103" t="s">
+      <c r="AV2" s="102" t="s">
         <v>60</v>
       </c>
-      <c r="AW2" s="103" t="s">
+      <c r="AW2" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="AX2" s="103" t="s">
+      <c r="AX2" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="AY2" s="103" t="s">
+      <c r="AY2" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="AZ2" s="103" t="s">
+      <c r="AZ2" s="102" t="s">
         <v>63</v>
       </c>
-      <c r="BA2" s="103" t="s">
+      <c r="BA2" s="102" t="s">
         <v>64</v>
       </c>
-      <c r="BB2" s="103" t="s">
+      <c r="BB2" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="BC2" s="103" t="s">
+      <c r="BC2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="BD2" s="103" t="s">
+      <c r="BD2" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="BE2" s="103" t="s">
+      <c r="BE2" s="102" t="s">
         <v>68</v>
       </c>
-      <c r="BF2" s="103" t="s">
+      <c r="BF2" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="BG2" s="103" t="s">
+      <c r="BG2" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="BH2" s="103" t="s">
+      <c r="BH2" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="BI2" s="103" t="s">
+      <c r="BI2" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="BJ2" s="103" t="s">
+      <c r="BJ2" s="102" t="s">
         <v>73</v>
       </c>
-      <c r="BK2" s="103" t="s">
+      <c r="BK2" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="BL2" s="103" t="s">
+      <c r="BL2" s="102" t="s">
         <v>75</v>
       </c>
-      <c r="BM2" s="103" t="s">
+      <c r="BM2" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="BN2" s="103" t="s">
+      <c r="BN2" s="102" t="s">
         <v>77</v>
       </c>
-      <c r="BO2" s="103" t="s">
+      <c r="BO2" s="102" t="s">
         <v>78</v>
       </c>
-      <c r="BP2" s="103" t="s">
+      <c r="BP2" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="BQ2" s="103" t="s">
+      <c r="BQ2" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="BR2" s="103" t="s">
+      <c r="BR2" s="102" t="s">
         <v>81</v>
       </c>
-      <c r="BS2" s="103" t="s">
+      <c r="BS2" s="102" t="s">
         <v>82</v>
       </c>
-      <c r="BT2" s="103" t="s">
+      <c r="BT2" s="102" t="s">
         <v>83</v>
       </c>
-      <c r="BU2" s="103" t="s">
+      <c r="BU2" s="102" t="s">
         <v>84</v>
       </c>
-      <c r="BV2" s="103" t="s">
+      <c r="BV2" s="102" t="s">
         <v>85</v>
       </c>
-      <c r="BW2" s="103" t="s">
+      <c r="BW2" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="BX2" s="103" t="s">
+      <c r="BX2" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="BY2" s="103" t="s">
+      <c r="BY2" s="102" t="s">
         <v>88</v>
       </c>
-      <c r="BZ2" s="103" t="s">
+      <c r="BZ2" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="CA2" s="103" t="s">
+      <c r="CA2" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="CB2" s="106" t="s">
+      <c r="CB2" s="105" t="s">
         <v>91</v>
       </c>
-      <c r="CC2" s="106" t="s">
+      <c r="CC2" s="105" t="s">
         <v>92</v>
       </c>
-      <c r="CD2" s="106" t="s">
+      <c r="CD2" s="105" t="s">
         <v>93</v>
       </c>
-      <c r="CE2" s="106" t="s">
+      <c r="CE2" s="105" t="s">
         <v>94</v>
       </c>
-      <c r="CF2" s="106" t="s">
+      <c r="CF2" s="105" t="s">
         <v>95</v>
       </c>
-      <c r="CG2" s="106" t="s">
+      <c r="CG2" s="105" t="s">
         <v>96</v>
       </c>
-      <c r="CH2" s="106" t="s">
+      <c r="CH2" s="105" t="s">
         <v>97</v>
       </c>
-      <c r="CI2" s="106" t="s">
+      <c r="CI2" s="105" t="s">
         <v>98</v>
       </c>
-      <c r="CJ2" s="106" t="s">
+      <c r="CJ2" s="105" t="s">
         <v>99</v>
       </c>
-      <c r="CK2" s="106" t="s">
+      <c r="CK2" s="105" t="s">
         <v>100</v>
       </c>
-      <c r="CL2" s="106" t="s">
+      <c r="CL2" s="105" t="s">
         <v>101</v>
       </c>
-      <c r="CM2" s="107" t="s">
+      <c r="CM2" s="106" t="s">
         <v>102</v>
       </c>
-      <c r="CN2" s="103" t="s">
+      <c r="CN2" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="CO2" s="103" t="s">
+      <c r="CO2" s="102" t="s">
         <v>104</v>
       </c>
-      <c r="CP2" s="103" t="s">
+      <c r="CP2" s="102" t="s">
         <v>105</v>
       </c>
-      <c r="CQ2" s="103" t="s">
+      <c r="CQ2" s="102" t="s">
         <v>106</v>
       </c>
-      <c r="CR2" s="103" t="s">
+      <c r="CR2" s="102" t="s">
         <v>107</v>
       </c>
-      <c r="CS2" s="103" t="s">
+      <c r="CS2" s="102" t="s">
         <v>108</v>
       </c>
-      <c r="CT2" s="103" t="s">
+      <c r="CT2" s="102" t="s">
         <v>109</v>
       </c>
-      <c r="CU2" s="103" t="s">
+      <c r="CU2" s="102" t="s">
         <v>110</v>
       </c>
-      <c r="CV2" s="97" t="s">
+      <c r="CV2" s="96" t="s">
         <v>111</v>
       </c>
-      <c r="CW2" s="97" t="s">
+      <c r="CW2" s="96" t="s">
         <v>49</v>
       </c>
-      <c r="CX2" s="97" t="s">
+      <c r="CX2" s="96" t="s">
         <v>112</v>
       </c>
-      <c r="CY2" s="97" t="s">
+      <c r="CY2" s="96" t="s">
         <v>113</v>
       </c>
-      <c r="CZ2" s="97" t="s">
+      <c r="CZ2" s="96" t="s">
         <v>114</v>
       </c>
-      <c r="DA2" s="191" t="s">
+      <c r="DA2" s="123" t="s">
         <v>115</v>
       </c>
-      <c r="DB2" s="97" t="s">
+      <c r="DB2" s="96" t="s">
         <v>116</v>
       </c>
-      <c r="DC2" s="97" t="s">
+      <c r="DC2" s="96" t="s">
         <v>117</v>
       </c>
-      <c r="DD2" s="97" t="s">
+      <c r="DD2" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="DE2" s="97" t="s">
+      <c r="DE2" s="96" t="s">
         <v>27</v>
       </c>
-      <c r="DF2" s="97" t="s">
+      <c r="DF2" s="96" t="s">
         <v>118</v>
       </c>
-      <c r="DG2" s="97" t="s">
+      <c r="DG2" s="96" t="s">
         <v>119</v>
       </c>
-      <c r="DH2" s="108" t="s">
+      <c r="DH2" s="107" t="s">
         <v>120</v>
       </c>
-      <c r="DI2" s="108" t="s">
+      <c r="DI2" s="107" t="s">
         <v>121</v>
       </c>
-      <c r="DJ2" s="108" t="s">
+      <c r="DJ2" s="107" t="s">
         <v>122</v>
       </c>
-      <c r="DK2" s="108" t="s">
+      <c r="DK2" s="107" t="s">
         <v>118</v>
       </c>
-      <c r="DL2" s="108" t="s">
+      <c r="DL2" s="107" t="s">
         <v>123</v>
       </c>
-      <c r="DM2" s="108" t="s">
+      <c r="DM2" s="107" t="s">
         <v>124</v>
       </c>
-      <c r="DN2" s="108" t="s">
+      <c r="DN2" s="107" t="s">
         <v>125</v>
       </c>
-      <c r="DO2" s="108" t="s">
+      <c r="DO2" s="107" t="s">
         <v>126</v>
       </c>
-      <c r="DP2" s="109" t="s">
+      <c r="DP2" s="108" t="s">
         <v>127</v>
       </c>
-      <c r="DQ2" s="109" t="s">
+      <c r="DQ2" s="108" t="s">
         <v>128</v>
       </c>
-      <c r="DR2" s="110" t="s">
+      <c r="DR2" s="109" t="s">
         <v>129</v>
       </c>
-      <c r="DS2" s="102" t="s">
+      <c r="DS2" s="101" t="s">
         <v>34</v>
       </c>
-      <c r="DT2" s="123" t="s">
+      <c r="DT2" s="120" t="s">
         <v>130</v>
       </c>
-      <c r="DU2" s="100" t="s">
+      <c r="DU2" s="99" t="s">
         <v>131</v>
       </c>
-      <c r="DV2" s="101" t="s">
+      <c r="DV2" s="100" t="s">
         <v>132</v>
       </c>
-      <c r="DW2" s="111" t="s">
+      <c r="DW2" s="110" t="s">
         <v>133</v>
       </c>
-      <c r="DX2" s="110" t="s">
+      <c r="DX2" s="109" t="s">
         <v>134</v>
       </c>
-      <c r="DY2" s="112" t="s">
+      <c r="DY2" s="111" t="s">
         <v>135</v>
       </c>
-      <c r="DZ2" s="103" t="s">
+      <c r="DZ2" s="102" t="s">
         <v>136</v>
       </c>
-      <c r="EA2" s="103" t="s">
+      <c r="EA2" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="EB2" s="103" t="s">
+      <c r="EB2" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="EC2" s="103" t="s">
+      <c r="EC2" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="ED2" s="103" t="s">
+      <c r="ED2" s="102" t="s">
         <v>137</v>
       </c>
-      <c r="EE2" s="103" t="s">
+      <c r="EE2" s="102" t="s">
         <v>138</v>
       </c>
-      <c r="EF2" s="103" t="s">
+      <c r="EF2" s="102" t="s">
         <v>139</v>
       </c>
-      <c r="EG2" s="103" t="s">
+      <c r="EG2" s="102" t="s">
         <v>140</v>
       </c>
-      <c r="EH2" s="103" t="s">
+      <c r="EH2" s="102" t="s">
         <v>58</v>
       </c>
-      <c r="EI2" s="103" t="s">
+      <c r="EI2" s="102" t="s">
         <v>141</v>
       </c>
-      <c r="EJ2" s="103" t="s">
+      <c r="EJ2" s="102" t="s">
         <v>142</v>
       </c>
-      <c r="EK2" s="97" t="s">
+      <c r="EK2" s="96" t="s">
         <v>133</v>
       </c>
-      <c r="EL2" s="97" t="s">
+      <c r="EL2" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="EM2" s="97" t="s">
+      <c r="EM2" s="96" t="s">
         <v>27</v>
       </c>
-      <c r="EN2" s="97" t="s">
+      <c r="EN2" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="EO2" s="97" t="s">
+      <c r="EO2" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="EP2" s="97" t="s">
+      <c r="EP2" s="96" t="s">
         <v>29</v>
       </c>
-      <c r="EQ2" s="113" t="s">
+      <c r="EQ2" s="112" t="s">
         <v>133</v>
       </c>
-      <c r="ER2" s="110" t="s">
+      <c r="ER2" s="109" t="s">
         <v>143</v>
       </c>
-      <c r="ES2" s="110" t="s">
+      <c r="ES2" s="109" t="s">
         <v>144</v>
       </c>
-      <c r="ET2" s="110" t="s">
+      <c r="ET2" s="109" t="s">
         <v>136</v>
       </c>
-      <c r="EU2" s="103" t="s">
+      <c r="EU2" s="102" t="s">
         <v>118</v>
       </c>
-      <c r="EV2" s="97" t="s">
+      <c r="EV2" s="96" t="s">
         <v>133</v>
       </c>
-      <c r="EW2" s="97" t="s">
+      <c r="EW2" s="96" t="s">
         <v>145</v>
       </c>
-      <c r="EX2" s="97" t="s">
+      <c r="EX2" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="EY2" s="97" t="s">
+      <c r="EY2" s="96" t="s">
         <v>27</v>
       </c>
-      <c r="EZ2" s="97" t="s">
+      <c r="EZ2" s="96" t="s">
         <v>146</v>
       </c>
-      <c r="FA2" s="97" t="s">
+      <c r="FA2" s="96" t="s">
         <v>147</v>
       </c>
-      <c r="FB2" s="97" t="s">
+      <c r="FB2" s="96" t="s">
         <v>148</v>
       </c>
-      <c r="FC2" s="97" t="s">
+      <c r="FC2" s="96" t="s">
         <v>149</v>
       </c>
-      <c r="FD2" s="97" t="s">
+      <c r="FD2" s="96" t="s">
         <v>150</v>
       </c>
-      <c r="FE2" s="97" t="s">
+      <c r="FE2" s="96" t="s">
         <v>151</v>
       </c>
-      <c r="FF2" s="97" t="s">
+      <c r="FF2" s="96" t="s">
         <v>152</v>
       </c>
-      <c r="FG2" s="97" t="s">
+      <c r="FG2" s="96" t="s">
         <v>153</v>
       </c>
-      <c r="FH2" s="97" t="s">
+      <c r="FH2" s="96" t="s">
         <v>154</v>
       </c>
-      <c r="FI2" s="97" t="s">
+      <c r="FI2" s="96" t="s">
         <v>155</v>
       </c>
-      <c r="FJ2" s="123" t="s">
+      <c r="FJ2" s="120" t="s">
         <v>156</v>
       </c>
-      <c r="FK2" s="123" t="s">
+      <c r="FK2" s="120" t="s">
         <v>157</v>
       </c>
-      <c r="FL2" s="123" t="s">
+      <c r="FL2" s="120" t="s">
         <v>158</v>
       </c>
-      <c r="FM2" s="103" t="s">
+      <c r="FM2" s="102" t="s">
         <v>159</v>
       </c>
-      <c r="FN2" s="103" t="s">
+      <c r="FN2" s="102" t="s">
         <v>160</v>
       </c>
-      <c r="FO2" s="103" t="s">
+      <c r="FO2" s="102" t="s">
         <v>161</v>
       </c>
-      <c r="FP2" s="103" t="s">
+      <c r="FP2" s="102" t="s">
         <v>162</v>
       </c>
-      <c r="FQ2" s="103" t="s">
+      <c r="FQ2" s="102" t="s">
         <v>163</v>
       </c>
-      <c r="FR2" s="103" t="s">
+      <c r="FR2" s="102" t="s">
         <v>164</v>
       </c>
-      <c r="FS2" s="103" t="s">
+      <c r="FS2" s="102" t="s">
         <v>50</v>
       </c>
-      <c r="FT2" s="103" t="s">
+      <c r="FT2" s="102" t="s">
         <v>165</v>
       </c>
-      <c r="FU2" s="103" t="s">
+      <c r="FU2" s="102" t="s">
         <v>166</v>
       </c>
-      <c r="FV2" s="103" t="s">
+      <c r="FV2" s="102" t="s">
         <v>167</v>
       </c>
-      <c r="FW2" s="103" t="s">
+      <c r="FW2" s="102" t="s">
         <v>168</v>
       </c>
-      <c r="FX2" s="103" t="s">
+      <c r="FX2" s="102" t="s">
         <v>169</v>
       </c>
-      <c r="FY2" s="103" t="s">
+      <c r="FY2" s="102" t="s">
         <v>170</v>
       </c>
-      <c r="FZ2" s="103" t="s">
+      <c r="FZ2" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="GA2" s="103" t="s">
+      <c r="GA2" s="102" t="s">
         <v>171</v>
       </c>
-      <c r="GB2" s="103" t="s">
+      <c r="GB2" s="102" t="s">
         <v>172</v>
       </c>
-      <c r="GC2" s="103" t="s">
+      <c r="GC2" s="102" t="s">
         <v>173</v>
       </c>
-      <c r="GD2" s="103" t="s">
+      <c r="GD2" s="102" t="s">
         <v>174</v>
       </c>
-      <c r="GE2" s="103" t="s">
+      <c r="GE2" s="102" t="s">
         <v>175</v>
       </c>
-      <c r="GF2" s="103" t="s">
+      <c r="GF2" s="102" t="s">
         <v>176</v>
       </c>
-      <c r="GG2" s="103" t="s">
+      <c r="GG2" s="102" t="s">
         <v>177</v>
       </c>
-      <c r="GH2" s="103" t="s">
+      <c r="GH2" s="102" t="s">
         <v>178</v>
       </c>
-      <c r="GI2" s="103" t="s">
+      <c r="GI2" s="102" t="s">
         <v>179</v>
       </c>
-      <c r="GJ2" s="97" t="s">
+      <c r="GJ2" s="96" t="s">
         <v>133</v>
       </c>
-      <c r="GK2" s="97" t="s">
+      <c r="GK2" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="GL2" s="97" t="s">
+      <c r="GL2" s="96" t="s">
         <v>180</v>
       </c>
-      <c r="GM2" s="123" t="s">
+      <c r="GM2" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="GN2" s="97" t="s">
+      <c r="GN2" s="96" t="s">
         <v>182</v>
       </c>
-      <c r="GO2" s="103" t="s">
+      <c r="GO2" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="GP2" s="103" t="s">
+      <c r="GP2" s="102" t="s">
         <v>183</v>
       </c>
-      <c r="GQ2" s="103" t="s">
+      <c r="GQ2" s="102" t="s">
         <v>184</v>
       </c>
-      <c r="GR2" s="125" t="s">
+      <c r="GR2" s="122" t="s">
         <v>50</v>
       </c>
-      <c r="GS2" s="103" t="s">
+      <c r="GS2" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="GT2" s="103" t="s">
+      <c r="GT2" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="GU2" s="103" t="s">
+      <c r="GU2" s="102" t="s">
         <v>133</v>
       </c>
-      <c r="GV2" s="103" t="s">
+      <c r="GV2" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="GW2" s="103" t="s">
+      <c r="GW2" s="102" t="s">
         <v>185</v>
       </c>
-      <c r="GX2" s="103" t="s">
+      <c r="GX2" s="102" t="s">
         <v>186</v>
       </c>
-      <c r="GY2" s="103" t="s">
+      <c r="GY2" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="GZ2" s="103" t="s">
+      <c r="GZ2" s="102" t="s">
         <v>106</v>
       </c>
-      <c r="HA2" s="103" t="s">
+      <c r="HA2" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="HB2" s="103" t="s">
+      <c r="HB2" s="102" t="s">
         <v>73</v>
       </c>
-      <c r="HC2" s="103" t="s">
+      <c r="HC2" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="HD2" s="103" t="s">
+      <c r="HD2" s="102" t="s">
         <v>75</v>
       </c>
-      <c r="HE2" s="103" t="s">
+      <c r="HE2" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="HF2" s="103" t="s">
+      <c r="HF2" s="102" t="s">
         <v>77</v>
       </c>
-      <c r="HG2" s="103" t="s">
+      <c r="HG2" s="102" t="s">
         <v>110</v>
       </c>
-      <c r="HH2" s="103" t="s">
+      <c r="HH2" s="102" t="s">
         <v>78</v>
       </c>
-      <c r="HI2" s="103" t="s">
+      <c r="HI2" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="HJ2" s="103" t="s">
+      <c r="HJ2" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="HK2" s="103" t="s">
+      <c r="HK2" s="102" t="s">
         <v>187</v>
       </c>
-      <c r="HL2" s="114" t="s">
+      <c r="HL2" s="113" t="s">
         <v>81</v>
       </c>
-      <c r="HM2" s="114" t="s">
+      <c r="HM2" s="113" t="s">
         <v>82</v>
       </c>
-      <c r="HN2" s="114" t="s">
+      <c r="HN2" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="HO2" s="114" t="s">
+      <c r="HO2" s="113" t="s">
         <v>84</v>
       </c>
-      <c r="HP2" s="114" t="s">
+      <c r="HP2" s="113" t="s">
         <v>85</v>
       </c>
-      <c r="HQ2" s="103" t="s">
+      <c r="HQ2" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="HR2" s="114" t="s">
+      <c r="HR2" s="113" t="s">
         <v>188</v>
       </c>
-      <c r="HS2" s="101" t="s">
+      <c r="HS2" s="100" t="s">
         <v>133</v>
       </c>
-      <c r="HT2" s="101" t="s">
+      <c r="HT2" s="100" t="s">
         <v>34</v>
       </c>
-      <c r="HU2" s="101" t="s">
+      <c r="HU2" s="100" t="s">
         <v>26</v>
       </c>
-      <c r="HV2" s="101" t="s">
+      <c r="HV2" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="HW2" s="115" t="s">
+      <c r="HW2" s="114" t="s">
         <v>181</v>
       </c>
-      <c r="HX2" s="116" t="s">
+      <c r="HX2" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="HY2" s="103" t="s">
+      <c r="HY2" s="102" t="s">
         <v>190</v>
       </c>
-      <c r="HZ2" s="103" t="s">
+      <c r="HZ2" s="102" t="s">
         <v>191</v>
       </c>
-      <c r="IA2" s="103" t="s">
+      <c r="IA2" s="102" t="s">
         <v>118</v>
       </c>
-      <c r="IB2" s="103" t="s">
+      <c r="IB2" s="102" t="s">
         <v>192</v>
       </c>
-      <c r="IC2" s="103" t="s">
+      <c r="IC2" s="102" t="s">
         <v>193</v>
       </c>
-      <c r="ID2" s="103" t="s">
+      <c r="ID2" s="102" t="s">
         <v>194</v>
       </c>
-      <c r="IE2" s="103" t="s">
+      <c r="IE2" s="102" t="s">
         <v>160</v>
       </c>
-      <c r="IF2" s="103" t="s">
+      <c r="IF2" s="102" t="s">
         <v>195</v>
       </c>
-      <c r="IG2" s="103" t="s">
+      <c r="IG2" s="102" t="s">
         <v>196</v>
       </c>
-      <c r="IH2" s="103" t="s">
+      <c r="IH2" s="102" t="s">
         <v>197</v>
       </c>
-      <c r="II2" s="103" t="s">
+      <c r="II2" s="102" t="s">
         <v>123</v>
       </c>
-      <c r="IJ2" s="103" t="s">
+      <c r="IJ2" s="102" t="s">
         <v>198</v>
       </c>
-      <c r="IK2" s="103" t="s">
+      <c r="IK2" s="102" t="s">
         <v>199</v>
       </c>
-      <c r="IL2" s="103" t="s">
+      <c r="IL2" s="102" t="s">
         <v>200</v>
       </c>
-      <c r="IM2" s="103" t="s">
+      <c r="IM2" s="102" t="s">
         <v>201</v>
       </c>
-      <c r="IN2" s="117" t="s">
+      <c r="IN2" s="116" t="s">
         <v>202</v>
       </c>
-      <c r="IO2" s="117" t="s">
+      <c r="IO2" s="116" t="s">
         <v>203</v>
       </c>
-      <c r="IP2" s="117" t="s">
+      <c r="IP2" s="116" t="s">
         <v>204</v>
       </c>
-      <c r="IQ2" s="117" t="s">
+      <c r="IQ2" s="116" t="s">
         <v>205</v>
       </c>
-      <c r="IR2" s="117" t="s">
+      <c r="IR2" s="116" t="s">
         <v>206</v>
       </c>
-      <c r="IS2" s="117" t="s">
+      <c r="IS2" s="116" t="s">
         <v>207</v>
       </c>
-      <c r="IT2" s="117" t="s">
+      <c r="IT2" s="116" t="s">
         <v>208</v>
       </c>
-      <c r="IU2" s="117" t="s">
+      <c r="IU2" s="116" t="s">
         <v>209</v>
       </c>
-      <c r="IV2" s="117" t="s">
+      <c r="IV2" s="116" t="s">
         <v>210</v>
       </c>
-      <c r="IW2" s="117" t="s">
+      <c r="IW2" s="116" t="s">
         <v>211</v>
       </c>
-      <c r="IX2" s="117" t="s">
+      <c r="IX2" s="116" t="s">
         <v>212</v>
       </c>
-      <c r="IY2" s="117" t="s">
+      <c r="IY2" s="116" t="s">
         <v>213</v>
       </c>
-      <c r="IZ2" s="117" t="s">
+      <c r="IZ2" s="116" t="s">
         <v>214</v>
       </c>
-      <c r="JA2" s="117" t="s">
+      <c r="JA2" s="116" t="s">
         <v>215</v>
       </c>
-      <c r="JB2" s="117" t="s">
+      <c r="JB2" s="116" t="s">
         <v>216</v>
       </c>
-      <c r="JC2" s="117" t="s">
+      <c r="JC2" s="116" t="s">
         <v>217</v>
       </c>
-      <c r="JD2" s="117" t="s">
+      <c r="JD2" s="116" t="s">
         <v>218</v>
       </c>
-      <c r="JE2" s="117" t="s">
+      <c r="JE2" s="116" t="s">
         <v>219</v>
       </c>
-      <c r="JF2" s="117" t="s">
+      <c r="JF2" s="116" t="s">
         <v>220</v>
       </c>
-      <c r="JG2" s="117" t="s">
+      <c r="JG2" s="116" t="s">
         <v>221</v>
       </c>
-      <c r="JH2" s="97" t="s">
+      <c r="JH2" s="96" t="s">
         <v>133</v>
       </c>
-      <c r="JI2" s="97" t="s">
+      <c r="JI2" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="JJ2" s="97" t="s">
+      <c r="JJ2" s="96" t="s">
         <v>180</v>
       </c>
-      <c r="JK2" s="97" t="s">
+      <c r="JK2" s="96" t="s">
         <v>222</v>
       </c>
-      <c r="JL2" s="100" t="s">
+      <c r="JL2" s="99" t="s">
         <v>223</v>
       </c>
-      <c r="JM2" s="120" t="s">
+      <c r="JM2" s="118" t="s">
         <v>224</v>
       </c>
-      <c r="JN2" s="121"/>
-      <c r="JO2" s="121"/>
-      <c r="JP2" s="121"/>
-      <c r="JQ2" s="121"/>
-      <c r="JR2" s="121"/>
-      <c r="JS2" s="121"/>
-      <c r="JT2" s="121"/>
-      <c r="JU2" s="121"/>
-      <c r="JV2" s="121"/>
-    </row>
-    <row r="3" spans="1:282">
+    </row>
+    <row r="3" spans="1:273">
       <c r="C3" s="33"/>
-      <c r="D3" s="98"/>
+      <c r="D3" s="97"/>
       <c r="M3" s="64"/>
-      <c r="AG3" s="105"/>
-    </row>
-    <row r="4" spans="1:282" s="74" customFormat="1">
+      <c r="AG3" s="104"/>
+    </row>
+    <row r="4" spans="1:273" s="74" customFormat="1">
       <c r="A4" s="75"/>
       <c r="B4" s="76"/>
       <c r="C4" s="33"/>
-      <c r="D4" s="98"/>
+      <c r="D4" s="97"/>
       <c r="E4" s="77"/>
       <c r="F4" s="75"/>
       <c r="G4" s="78"/>
@@ -9574,7 +9556,7 @@
       <c r="AD4" s="80"/>
       <c r="AE4" s="76"/>
       <c r="AF4" s="76"/>
-      <c r="AG4" s="105"/>
+      <c r="AG4" s="104"/>
       <c r="AH4" s="75"/>
       <c r="AI4" s="76"/>
       <c r="AJ4" s="76"/>
@@ -9646,7 +9628,7 @@
       <c r="CX4" s="76"/>
       <c r="CY4" s="84"/>
       <c r="CZ4" s="78"/>
-      <c r="DA4" s="192"/>
+      <c r="DA4" s="124"/>
       <c r="DB4" s="84"/>
       <c r="DC4" s="84"/>
       <c r="DD4" s="79"/>
@@ -9709,7 +9691,7 @@
       <c r="FI4" s="80"/>
       <c r="FJ4" s="78"/>
       <c r="FK4" s="78"/>
-      <c r="FL4" s="124"/>
+      <c r="FL4" s="121"/>
       <c r="FM4" s="82"/>
       <c r="FN4" s="82"/>
       <c r="FO4" s="82"/>
@@ -9809,21 +9791,12 @@
       <c r="JK4" s="88"/>
       <c r="JL4" s="87"/>
       <c r="JM4" s="75"/>
-      <c r="JN4" s="93"/>
-      <c r="JO4" s="93"/>
-      <c r="JP4" s="93"/>
-      <c r="JQ4" s="93"/>
-      <c r="JR4" s="93"/>
-      <c r="JS4" s="93"/>
-      <c r="JT4" s="93"/>
-      <c r="JU4" s="93"/>
-      <c r="JV4" s="93"/>
-    </row>
-    <row r="5" spans="1:282" s="74" customFormat="1">
+    </row>
+    <row r="5" spans="1:273" s="74" customFormat="1">
       <c r="A5" s="75"/>
       <c r="B5" s="76"/>
       <c r="C5" s="33"/>
-      <c r="D5" s="98"/>
+      <c r="D5" s="97"/>
       <c r="E5" s="77"/>
       <c r="F5" s="75"/>
       <c r="G5" s="78"/>
@@ -9852,7 +9825,7 @@
       <c r="AD5" s="80"/>
       <c r="AE5" s="76"/>
       <c r="AF5" s="76"/>
-      <c r="AG5" s="105"/>
+      <c r="AG5" s="104"/>
       <c r="AH5" s="75"/>
       <c r="AI5" s="76"/>
       <c r="AJ5" s="76"/>
@@ -9924,7 +9897,7 @@
       <c r="CX5" s="76"/>
       <c r="CY5" s="84"/>
       <c r="CZ5" s="78"/>
-      <c r="DA5" s="192"/>
+      <c r="DA5" s="124"/>
       <c r="DB5" s="84"/>
       <c r="DC5" s="84"/>
       <c r="DD5" s="79"/>
@@ -9987,7 +9960,7 @@
       <c r="FI5" s="80"/>
       <c r="FJ5" s="78"/>
       <c r="FK5" s="78"/>
-      <c r="FL5" s="124"/>
+      <c r="FL5" s="121"/>
       <c r="FM5" s="82"/>
       <c r="FN5" s="82"/>
       <c r="FO5" s="82"/>
@@ -10087,46 +10060,37 @@
       <c r="JK5" s="88"/>
       <c r="JL5" s="87"/>
       <c r="JM5" s="75"/>
-      <c r="JN5" s="93"/>
-      <c r="JO5" s="93"/>
-      <c r="JP5" s="93"/>
-      <c r="JQ5" s="93"/>
-      <c r="JR5" s="93"/>
-      <c r="JS5" s="93"/>
-      <c r="JT5" s="93"/>
-      <c r="JU5" s="93"/>
-      <c r="JV5" s="93"/>
-    </row>
-    <row r="6" spans="1:282">
-      <c r="C6" s="99"/>
-      <c r="D6" s="98"/>
+    </row>
+    <row r="6" spans="1:273">
+      <c r="C6" s="98"/>
+      <c r="D6" s="97"/>
       <c r="M6" s="64"/>
-      <c r="AG6" s="105"/>
-    </row>
-    <row r="7" spans="1:282">
-      <c r="D7" s="98"/>
+      <c r="AG6" s="104"/>
+    </row>
+    <row r="7" spans="1:273">
+      <c r="D7" s="97"/>
       <c r="M7" s="64"/>
-      <c r="AG7" s="105"/>
-    </row>
-    <row r="8" spans="1:282">
-      <c r="D8" s="98"/>
+      <c r="AG7" s="104"/>
+    </row>
+    <row r="8" spans="1:273">
+      <c r="D8" s="97"/>
       <c r="M8" s="64"/>
-      <c r="AG8" s="105"/>
-    </row>
-    <row r="9" spans="1:282">
-      <c r="D9" s="98"/>
-      <c r="AG9" s="105"/>
-    </row>
-    <row r="10" spans="1:282">
+      <c r="AG8" s="104"/>
+    </row>
+    <row r="9" spans="1:273">
+      <c r="D9" s="97"/>
+      <c r="AG9" s="104"/>
+    </row>
+    <row r="10" spans="1:273">
       <c r="C10" s="34"/>
-      <c r="D10" s="98"/>
+      <c r="D10" s="97"/>
       <c r="M10" s="64"/>
-      <c r="AG10" s="105"/>
-    </row>
-    <row r="11" spans="1:282">
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="AG11" s="105"/>
+      <c r="AG10" s="104"/>
+    </row>
+    <row r="11" spans="1:273">
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="AG11" s="104"/>
     </row>
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -10152,7 +10116,7 @@
     <mergeCell ref="AH1:CU1"/>
   </mergeCells>
   <phoneticPr fontId="36" type="noConversion"/>
-  <dataValidations count="131">
+  <dataValidations count="130">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DJ3 DJ4 DJ5 DJ6:DJ9 DJ10:DJ65536">
       <formula1>"01 普通股,02 优先股,99 其他"</formula1>
     </dataValidation>
@@ -10231,7 +10195,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="GD1">
       <formula1>"01 主动,02 被动,99 其他"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="金额输入值必须大于等于0且必须为n(15,2)格式。" sqref="AK3 AK4 AK5 AK6:AK9 AK10:AK65536">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="金额输入值必须大于等于0且必须为n(15,2)格式。" sqref="AK3:AK65536 FS3:FS1048576 GR3:GR1048576">
       <formula1>0</formula1>
       <formula2>9999999999999.99</formula2>
     </dataValidation>
@@ -10548,10 +10512,6 @@
       <formula1>0</formula1>
       <formula2>9999999999999.99</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="金额输入值必须大于等于0且必须为n(15,2)格式。" sqref="FS3:FS1048576 GR3:GR1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999999.99</formula2>
-    </dataValidation>
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值整数位不可超过3位，小数位不可超过5位" sqref="GB1:GB2">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
@@ -10593,9 +10553,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="95.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="95.08984375" style="1" customWidth="1"/>
     <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -10645,22 +10605,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IV319"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="32.25" style="30" customWidth="1"/>
-    <col min="2" max="2" width="44.75" style="30" customWidth="1"/>
+    <col min="1" max="1" width="32.26953125" style="30" customWidth="1"/>
+    <col min="2" max="2" width="44.7265625" style="30" customWidth="1"/>
     <col min="3" max="256" width="9" style="30"/>
     <col min="257" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="145" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="147"/>
+      <c r="B1" s="146"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="160" t="s">
+      <c r="A2" s="159" t="s">
         <v>239</v>
       </c>
       <c r="B2" s="42" t="s">
@@ -10668,25 +10628,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="161"/>
+      <c r="A3" s="160"/>
       <c r="B3" s="39" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="161"/>
+      <c r="A4" s="160"/>
       <c r="B4" s="39" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="162"/>
+      <c r="A5" s="161"/>
       <c r="B5" s="37" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="30" customFormat="1">
-      <c r="A6" s="163" t="s">
+      <c r="A6" s="162" t="s">
         <v>241</v>
       </c>
       <c r="B6" s="42" t="s">
@@ -10694,13 +10654,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="30" customFormat="1">
-      <c r="A7" s="164"/>
+      <c r="A7" s="163"/>
       <c r="B7" s="36" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="30" customFormat="1">
-      <c r="A8" s="165" t="s">
+      <c r="A8" s="164" t="s">
         <v>244</v>
       </c>
       <c r="B8" s="35" t="s">
@@ -10708,13 +10668,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="30" customFormat="1">
-      <c r="A9" s="164"/>
+      <c r="A9" s="163"/>
       <c r="B9" s="36" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="153" t="s">
+      <c r="A10" s="152" t="s">
         <v>247</v>
       </c>
       <c r="B10" s="39" t="s">
@@ -10722,61 +10682,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="166"/>
+      <c r="A11" s="165"/>
       <c r="B11" s="39" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="166"/>
+      <c r="A12" s="165"/>
       <c r="B12" s="39" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="166"/>
+      <c r="A13" s="165"/>
       <c r="B13" s="39" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="166"/>
+      <c r="A14" s="165"/>
       <c r="B14" s="39" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="166"/>
+      <c r="A15" s="165"/>
       <c r="B15" s="39" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="166"/>
+      <c r="A16" s="165"/>
       <c r="B16" s="39" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="166"/>
+      <c r="A17" s="165"/>
       <c r="B17" s="39" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="166"/>
+      <c r="A18" s="165"/>
       <c r="B18" s="39" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="166"/>
+      <c r="A19" s="165"/>
       <c r="B19" s="39" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="166"/>
+      <c r="A20" s="165"/>
       <c r="B20" s="39" t="s">
         <v>258</v>
       </c>
@@ -10790,7 +10750,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="153" t="s">
+      <c r="A22" s="152" t="s">
         <v>261</v>
       </c>
       <c r="B22" s="42" t="s">
@@ -10798,19 +10758,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="166"/>
+      <c r="A23" s="165"/>
       <c r="B23" s="39" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="154"/>
+      <c r="A24" s="153"/>
       <c r="B24" s="37" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="153" t="s">
+      <c r="A25" s="152" t="s">
         <v>265</v>
       </c>
       <c r="B25" s="39" t="s">
@@ -10818,67 +10778,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="166"/>
+      <c r="A26" s="165"/>
       <c r="B26" s="39" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="166"/>
+      <c r="A27" s="165"/>
       <c r="B27" s="34" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="166"/>
+      <c r="A28" s="165"/>
       <c r="B28" s="34" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="166"/>
+      <c r="A29" s="165"/>
       <c r="B29" s="34" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="166"/>
+      <c r="A30" s="165"/>
       <c r="B30" s="34" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="166"/>
+      <c r="A31" s="165"/>
       <c r="B31" s="34" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="166"/>
+      <c r="A32" s="165"/>
       <c r="B32" s="34" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="166"/>
+      <c r="A33" s="165"/>
       <c r="B33" s="34" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="166"/>
+      <c r="A34" s="165"/>
       <c r="B34" s="34" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="154"/>
+      <c r="A35" s="153"/>
       <c r="B35" s="55" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="153" t="s">
+      <c r="A36" s="152" t="s">
         <v>277</v>
       </c>
       <c r="B36" s="34" t="s">
@@ -10886,25 +10846,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="166"/>
+      <c r="A37" s="165"/>
       <c r="B37" s="39" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="166"/>
+      <c r="A38" s="165"/>
       <c r="B38" s="34" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="154"/>
+      <c r="A39" s="153"/>
       <c r="B39" s="34" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="153" t="s">
+      <c r="A40" s="152" t="s">
         <v>282</v>
       </c>
       <c r="B40" s="33" t="s">
@@ -10912,43 +10872,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="166"/>
+      <c r="A41" s="165"/>
       <c r="B41" s="34" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="166"/>
+      <c r="A42" s="165"/>
       <c r="B42" s="34" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="166"/>
+      <c r="A43" s="165"/>
       <c r="B43" s="34" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="166"/>
+      <c r="A44" s="165"/>
       <c r="B44" s="34" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="166"/>
+      <c r="A45" s="165"/>
       <c r="B45" s="34" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="154"/>
+      <c r="A46" s="153"/>
       <c r="B46" s="37" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="153" t="s">
+      <c r="A47" s="152" t="s">
         <v>290</v>
       </c>
       <c r="B47" s="42" t="s">
@@ -10956,61 +10916,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="166"/>
+      <c r="A48" s="165"/>
       <c r="B48" s="34" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="166"/>
+      <c r="A49" s="165"/>
       <c r="B49" s="34" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="166"/>
+      <c r="A50" s="165"/>
       <c r="B50" s="34" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="166"/>
+      <c r="A51" s="165"/>
       <c r="B51" s="34" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="166"/>
+      <c r="A52" s="165"/>
       <c r="B52" s="34" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="166"/>
+      <c r="A53" s="165"/>
       <c r="B53" s="39" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="166"/>
+      <c r="A54" s="165"/>
       <c r="B54" s="34" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="166"/>
+      <c r="A55" s="165"/>
       <c r="B55" s="39" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="154"/>
+      <c r="A56" s="153"/>
       <c r="B56" s="37" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="153" t="s">
+      <c r="A57" s="152" t="s">
         <v>301</v>
       </c>
       <c r="B57" s="33" t="s">
@@ -11018,19 +10978,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="166"/>
+      <c r="A58" s="165"/>
       <c r="B58" s="34" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="154"/>
+      <c r="A59" s="153"/>
       <c r="B59" s="37" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="153" t="s">
+      <c r="A60" s="152" t="s">
         <v>305</v>
       </c>
       <c r="B60" s="47" t="s">
@@ -11038,37 +10998,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="166"/>
+      <c r="A61" s="165"/>
       <c r="B61" s="34" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="166"/>
+      <c r="A62" s="165"/>
       <c r="B62" s="48" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="166"/>
+      <c r="A63" s="165"/>
       <c r="B63" s="34" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="166"/>
+      <c r="A64" s="165"/>
       <c r="B64" s="34" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="154"/>
+      <c r="A65" s="153"/>
       <c r="B65" s="41" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="153" t="s">
+      <c r="A66" s="152" t="s">
         <v>312</v>
       </c>
       <c r="B66" s="47" t="s">
@@ -11076,37 +11036,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="166"/>
+      <c r="A67" s="165"/>
       <c r="B67" s="34" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="166"/>
+      <c r="A68" s="165"/>
       <c r="B68" s="34" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="166"/>
+      <c r="A69" s="165"/>
       <c r="B69" s="34" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="166"/>
+      <c r="A70" s="165"/>
       <c r="B70" s="34" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="154"/>
+      <c r="A71" s="153"/>
       <c r="B71" s="41" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="30" customFormat="1">
-      <c r="A72" s="153" t="s">
+      <c r="A72" s="152" t="s">
         <v>319</v>
       </c>
       <c r="B72" s="34" t="s">
@@ -11114,103 +11074,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="30" customFormat="1">
-      <c r="A73" s="166"/>
+      <c r="A73" s="165"/>
       <c r="B73" s="34" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="30" customFormat="1">
-      <c r="A74" s="166"/>
+      <c r="A74" s="165"/>
       <c r="B74" s="34" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="30" customFormat="1">
-      <c r="A75" s="166"/>
+      <c r="A75" s="165"/>
       <c r="B75" s="34" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="30" customFormat="1">
-      <c r="A76" s="166"/>
+      <c r="A76" s="165"/>
       <c r="B76" s="34" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="30" customFormat="1">
-      <c r="A77" s="166"/>
+      <c r="A77" s="165"/>
       <c r="B77" s="49" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="30" customFormat="1">
-      <c r="A78" s="166"/>
+      <c r="A78" s="165"/>
       <c r="B78" s="34" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="30" customFormat="1">
-      <c r="A79" s="166"/>
+      <c r="A79" s="165"/>
       <c r="B79" s="34" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="30" customFormat="1">
-      <c r="A80" s="166"/>
+      <c r="A80" s="165"/>
       <c r="B80" s="34" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="30" customFormat="1">
-      <c r="A81" s="166"/>
+      <c r="A81" s="165"/>
       <c r="B81" s="49" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="30" customFormat="1">
-      <c r="A82" s="166"/>
+      <c r="A82" s="165"/>
       <c r="B82" s="34" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="30" customFormat="1">
-      <c r="A83" s="166"/>
+      <c r="A83" s="165"/>
       <c r="B83" s="34" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="30" customFormat="1">
-      <c r="A84" s="166"/>
+      <c r="A84" s="165"/>
       <c r="B84" s="34" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="30" customFormat="1">
-      <c r="A85" s="166"/>
+      <c r="A85" s="165"/>
       <c r="B85" s="49" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="30" customFormat="1">
-      <c r="A86" s="166"/>
+      <c r="A86" s="165"/>
       <c r="B86" s="49" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="30" customFormat="1">
-      <c r="A87" s="166"/>
+      <c r="A87" s="165"/>
       <c r="B87" s="49" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="30" customFormat="1">
-      <c r="A88" s="154"/>
+      <c r="A88" s="153"/>
       <c r="B88" s="37" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="30" customFormat="1">
-      <c r="A89" s="153" t="s">
+      <c r="A89" s="152" t="s">
         <v>337</v>
       </c>
       <c r="B89" s="39" t="s">
@@ -11218,38 +11178,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="30" customFormat="1">
-      <c r="A90" s="166"/>
+      <c r="A90" s="165"/>
       <c r="B90" s="39" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="30" customFormat="1">
-      <c r="A91" s="166"/>
+      <c r="A91" s="165"/>
       <c r="B91" s="39" t="s">
         <v>340</v>
       </c>
       <c r="F91" s="56"/>
     </row>
     <row r="92" spans="1:6" s="30" customFormat="1">
-      <c r="A92" s="166"/>
+      <c r="A92" s="165"/>
       <c r="B92" s="57" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="30" customFormat="1">
-      <c r="A93" s="166"/>
+      <c r="A93" s="165"/>
       <c r="B93" s="39" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="30" customFormat="1">
-      <c r="A94" s="154"/>
+      <c r="A94" s="153"/>
       <c r="B94" s="37" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="30" customFormat="1">
-      <c r="A95" s="153" t="s">
+      <c r="A95" s="152" t="s">
         <v>344</v>
       </c>
       <c r="B95" s="50" t="s">
@@ -11257,43 +11217,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="30" customFormat="1">
-      <c r="A96" s="166"/>
+      <c r="A96" s="165"/>
       <c r="B96" s="51" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="30" customFormat="1">
-      <c r="A97" s="166"/>
+      <c r="A97" s="165"/>
       <c r="B97" s="51" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="30" customFormat="1">
-      <c r="A98" s="166"/>
+      <c r="A98" s="165"/>
       <c r="B98" s="51" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="30" customFormat="1">
-      <c r="A99" s="166"/>
+      <c r="A99" s="165"/>
       <c r="B99" s="51" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="30" customFormat="1">
-      <c r="A100" s="166"/>
+      <c r="A100" s="165"/>
       <c r="B100" s="51" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="30" customFormat="1">
-      <c r="A101" s="154"/>
+      <c r="A101" s="153"/>
       <c r="B101" s="45" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="30" customFormat="1">
-      <c r="A102" s="153" t="s">
+      <c r="A102" s="152" t="s">
         <v>352</v>
       </c>
       <c r="B102" s="33" t="s">
@@ -11301,7 +11261,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="30" customFormat="1">
-      <c r="A103" s="154"/>
+      <c r="A103" s="153"/>
       <c r="B103" s="37" t="s">
         <v>354</v>
       </c>
@@ -11319,10 +11279,10 @@
       <c r="B105" s="40"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="148" t="s">
+      <c r="A107" s="147" t="s">
         <v>357</v>
       </c>
-      <c r="B107" s="147"/>
+      <c r="B107" s="146"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="61"/>
@@ -11493,17 +11453,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="167" t="s">
+      <c r="A137" s="166" t="s">
         <v>386</v>
       </c>
-      <c r="B137" s="168"/>
+      <c r="B137" s="167"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="169"/>
-      <c r="B138" s="170"/>
+      <c r="A138" s="168"/>
+      <c r="B138" s="169"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="155" t="s">
+      <c r="A139" s="154" t="s">
         <v>387</v>
       </c>
       <c r="B139" s="63" t="s">
@@ -11511,31 +11471,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="156"/>
+      <c r="A140" s="155"/>
       <c r="B140" s="64" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="156"/>
+      <c r="A141" s="155"/>
       <c r="B141" s="64" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="156"/>
+      <c r="A142" s="155"/>
       <c r="B142" s="64" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="157"/>
+      <c r="A143" s="156"/>
       <c r="B143" s="66" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="155" t="s">
+      <c r="A144" s="154" t="s">
         <v>393</v>
       </c>
       <c r="B144" s="63" t="s">
@@ -11543,43 +11503,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="156"/>
+      <c r="A145" s="155"/>
       <c r="B145" s="64" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="156"/>
+      <c r="A146" s="155"/>
       <c r="B146" s="64" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="156"/>
+      <c r="A147" s="155"/>
       <c r="B147" s="64" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="156"/>
+      <c r="A148" s="155"/>
       <c r="B148" s="64" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="156"/>
+      <c r="A149" s="155"/>
       <c r="B149" s="64" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="157"/>
+      <c r="A150" s="156"/>
       <c r="B150" s="66" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="155" t="s">
+      <c r="A151" s="154" t="s">
         <v>401</v>
       </c>
       <c r="B151" s="63" t="s">
@@ -11587,187 +11547,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="156"/>
+      <c r="A152" s="155"/>
       <c r="B152" s="64" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="156"/>
+      <c r="A153" s="155"/>
       <c r="B153" s="64" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="156"/>
+      <c r="A154" s="155"/>
       <c r="B154" s="64" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="156"/>
+      <c r="A155" s="155"/>
       <c r="B155" s="64" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="156"/>
+      <c r="A156" s="155"/>
       <c r="B156" s="64" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="156"/>
+      <c r="A157" s="155"/>
       <c r="B157" s="64" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="156"/>
+      <c r="A158" s="155"/>
       <c r="B158" s="64" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="156"/>
+      <c r="A159" s="155"/>
       <c r="B159" s="64" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="156"/>
+      <c r="A160" s="155"/>
       <c r="B160" s="64" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="156"/>
+      <c r="A161" s="155"/>
       <c r="B161" s="64" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="156"/>
+      <c r="A162" s="155"/>
       <c r="B162" s="64" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="156"/>
+      <c r="A163" s="155"/>
       <c r="B163" s="64" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="156"/>
+      <c r="A164" s="155"/>
       <c r="B164" s="64" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="156"/>
+      <c r="A165" s="155"/>
       <c r="B165" s="64" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="156"/>
+      <c r="A166" s="155"/>
       <c r="B166" s="64" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="156"/>
+      <c r="A167" s="155"/>
       <c r="B167" s="64" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="156"/>
+      <c r="A168" s="155"/>
       <c r="B168" s="64" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="156"/>
+      <c r="A169" s="155"/>
       <c r="B169" s="64" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="156"/>
+      <c r="A170" s="155"/>
       <c r="B170" s="64" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="156"/>
+      <c r="A171" s="155"/>
       <c r="B171" s="64" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="156"/>
+      <c r="A172" s="155"/>
       <c r="B172" s="64" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="156"/>
+      <c r="A173" s="155"/>
       <c r="B173" s="64" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="156"/>
+      <c r="A174" s="155"/>
       <c r="B174" s="64" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="156"/>
+      <c r="A175" s="155"/>
       <c r="B175" s="64" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="156"/>
+      <c r="A176" s="155"/>
       <c r="B176" s="64" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="156"/>
+      <c r="A177" s="155"/>
       <c r="B177" s="64" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="156"/>
+      <c r="A178" s="155"/>
       <c r="B178" s="64" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="156"/>
+      <c r="A179" s="155"/>
       <c r="B179" s="64" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="156"/>
+      <c r="A180" s="155"/>
       <c r="B180" s="64" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="157"/>
+      <c r="A181" s="156"/>
       <c r="B181" s="66" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="155" t="s">
+      <c r="A182" s="154" t="s">
         <v>433</v>
       </c>
       <c r="B182" s="63" t="s">
@@ -11775,19 +11735,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="156"/>
+      <c r="A183" s="155"/>
       <c r="B183" s="64" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="157"/>
+      <c r="A184" s="156"/>
       <c r="B184" s="66" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="155" t="s">
+      <c r="A185" s="154" t="s">
         <v>437</v>
       </c>
       <c r="B185" s="63" t="s">
@@ -11795,25 +11755,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="156"/>
+      <c r="A186" s="155"/>
       <c r="B186" s="64" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="156"/>
+      <c r="A187" s="155"/>
       <c r="B187" s="64" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="157"/>
+      <c r="A188" s="156"/>
       <c r="B188" s="66" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="155" t="s">
+      <c r="A189" s="154" t="s">
         <v>442</v>
       </c>
       <c r="B189" s="63" t="s">
@@ -11821,13 +11781,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="157"/>
+      <c r="A190" s="156"/>
       <c r="B190" s="66" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="155" t="s">
+      <c r="A191" s="154" t="s">
         <v>445</v>
       </c>
       <c r="B191" s="63" t="s">
@@ -11835,49 +11795,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="156"/>
+      <c r="A192" s="155"/>
       <c r="B192" s="64" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="156"/>
+      <c r="A193" s="155"/>
       <c r="B193" s="64" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="156"/>
+      <c r="A194" s="155"/>
       <c r="B194" s="64" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="156"/>
+      <c r="A195" s="155"/>
       <c r="B195" s="64" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="156"/>
+      <c r="A196" s="155"/>
       <c r="B196" s="64" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="156"/>
+      <c r="A197" s="155"/>
       <c r="B197" s="64" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="157"/>
+      <c r="A198" s="156"/>
       <c r="B198" s="66" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="155" t="s">
+      <c r="A199" s="154" t="s">
         <v>454</v>
       </c>
       <c r="B199" s="63" t="s">
@@ -11885,13 +11845,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="157"/>
+      <c r="A200" s="156"/>
       <c r="B200" s="66" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="155" t="s">
+      <c r="A201" s="154" t="s">
         <v>457</v>
       </c>
       <c r="B201" s="63" t="s">
@@ -11899,19 +11859,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="156"/>
+      <c r="A202" s="155"/>
       <c r="B202" s="64" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="157"/>
+      <c r="A203" s="156"/>
       <c r="B203" s="66" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="155" t="s">
+      <c r="A204" s="154" t="s">
         <v>461</v>
       </c>
       <c r="B204" s="63" t="s">
@@ -11919,19 +11879,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="156"/>
+      <c r="A205" s="155"/>
       <c r="B205" s="64" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="156"/>
+      <c r="A206" s="155"/>
       <c r="B206" s="64" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="157"/>
+      <c r="A207" s="156"/>
       <c r="B207" s="66" t="s">
         <v>465</v>
       </c>
@@ -11945,7 +11905,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="155" t="s">
+      <c r="A209" s="154" t="s">
         <v>468</v>
       </c>
       <c r="B209" s="63" t="s">
@@ -11953,13 +11913,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="157"/>
+      <c r="A210" s="156"/>
       <c r="B210" s="66" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="155" t="s">
+      <c r="A211" s="154" t="s">
         <v>471</v>
       </c>
       <c r="B211" s="63" t="s">
@@ -11967,19 +11927,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="156"/>
+      <c r="A212" s="155"/>
       <c r="B212" s="64" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="157"/>
+      <c r="A213" s="156"/>
       <c r="B213" s="66" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="155" t="s">
+      <c r="A214" s="154" t="s">
         <v>475</v>
       </c>
       <c r="B214" s="63" t="s">
@@ -11987,19 +11947,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="156"/>
+      <c r="A215" s="155"/>
       <c r="B215" s="64" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="157"/>
+      <c r="A216" s="156"/>
       <c r="B216" s="66" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="155" t="s">
+      <c r="A217" s="154" t="s">
         <v>479</v>
       </c>
       <c r="B217" s="63" t="s">
@@ -12007,13 +11967,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="156"/>
+      <c r="A218" s="155"/>
       <c r="B218" s="64" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="157"/>
+      <c r="A219" s="156"/>
       <c r="B219" s="66" t="s">
         <v>482</v>
       </c>
@@ -12027,7 +11987,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="155" t="s">
+      <c r="A221" s="154" t="s">
         <v>485</v>
       </c>
       <c r="B221" s="63" t="s">
@@ -12035,13 +11995,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="157"/>
+      <c r="A222" s="156"/>
       <c r="B222" s="66" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="155" t="s">
+      <c r="A223" s="154" t="s">
         <v>488</v>
       </c>
       <c r="B223" s="63" t="s">
@@ -12049,31 +12009,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="156"/>
+      <c r="A224" s="155"/>
       <c r="B224" s="64" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="156"/>
+      <c r="A225" s="155"/>
       <c r="B225" s="64" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="156"/>
+      <c r="A226" s="155"/>
       <c r="B226" s="64" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="157"/>
+      <c r="A227" s="156"/>
       <c r="B227" s="66" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="155" t="s">
+      <c r="A228" s="154" t="s">
         <v>494</v>
       </c>
       <c r="B228" s="63" t="s">
@@ -12081,31 +12041,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="156"/>
+      <c r="A229" s="155"/>
       <c r="B229" s="64" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="156"/>
+      <c r="A230" s="155"/>
       <c r="B230" s="64" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="156"/>
+      <c r="A231" s="155"/>
       <c r="B231" s="64" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="156"/>
+      <c r="A232" s="155"/>
       <c r="B232" s="64" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="157"/>
+      <c r="A233" s="156"/>
       <c r="B233" s="66" t="s">
         <v>500</v>
       </c>
@@ -12119,16 +12079,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="149" t="s">
+      <c r="A236" s="148" t="s">
         <v>503</v>
       </c>
-      <c r="B236" s="150"/>
+      <c r="B236" s="149"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="148" t="s">
+      <c r="A239" s="147" t="s">
         <v>504</v>
       </c>
-      <c r="B239" s="147"/>
+      <c r="B239" s="146"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="61"/>
@@ -12227,10 +12187,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="151" t="s">
+      <c r="A257" s="150" t="s">
         <v>520</v>
       </c>
-      <c r="B257" s="152"/>
+      <c r="B257" s="151"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="61"/>
@@ -12406,11 +12366,11 @@
         <v>549</v>
       </c>
     </row>
-    <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="158" t="s">
+    <row r="288" spans="1:2" ht="23">
+      <c r="A288" s="157" t="s">
         <v>550</v>
       </c>
-      <c r="B288" s="159"/>
+      <c r="B288" s="158"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="69"/>
@@ -12456,13 +12416,13 @@
     </row>
     <row r="296" spans="1:2">
       <c r="A296" s="61"/>
-      <c r="B296" s="122" t="s">
+      <c r="B296" s="119" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" s="61"/>
-      <c r="B297" s="122" t="s">
+      <c r="B297" s="119" t="s">
         <v>559</v>
       </c>
     </row>
@@ -12651,21 +12611,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IV105"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="38.125" style="30" customWidth="1"/>
-    <col min="2" max="2" width="76.625" style="30" customWidth="1"/>
+    <col min="1" max="1" width="38.08984375" style="30" customWidth="1"/>
+    <col min="2" max="2" width="76.6328125" style="30" customWidth="1"/>
     <col min="3" max="256" width="9" style="30"/>
     <col min="257" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="170" t="s">
         <v>582</v>
       </c>
-      <c r="B1" s="172"/>
-    </row>
-    <row r="2" spans="1:2" s="28" customFormat="1" ht="14.25">
+      <c r="B1" s="171"/>
+    </row>
+    <row r="2" spans="1:2" s="28" customFormat="1" ht="15">
       <c r="A2" s="31" t="s">
         <v>583</v>
       </c>
@@ -12677,7 +12637,7 @@
       <c r="A3" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="172" t="s">
         <v>1</v>
       </c>
     </row>
@@ -12685,25 +12645,25 @@
       <c r="A4" s="34" t="s">
         <v>585</v>
       </c>
-      <c r="B4" s="174"/>
+      <c r="B4" s="173"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="B5" s="174"/>
+      <c r="B5" s="173"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="B6" s="175"/>
+      <c r="B6" s="174"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="35" t="s">
         <v>245</v>
       </c>
-      <c r="B7" s="173" t="s">
+      <c r="B7" s="172" t="s">
         <v>586</v>
       </c>
     </row>
@@ -12711,25 +12671,25 @@
       <c r="A8" s="36" t="s">
         <v>246</v>
       </c>
-      <c r="B8" s="174"/>
+      <c r="B8" s="173"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="33" t="s">
         <v>353</v>
       </c>
-      <c r="B9" s="174"/>
+      <c r="B9" s="173"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="37" t="s">
         <v>354</v>
       </c>
-      <c r="B10" s="175"/>
+      <c r="B10" s="174"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="B11" s="173" t="s">
+      <c r="B11" s="172" t="s">
         <v>2</v>
       </c>
     </row>
@@ -12737,85 +12697,85 @@
       <c r="A12" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="B12" s="174"/>
+      <c r="B12" s="173"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="38" t="s">
         <v>250</v>
       </c>
-      <c r="B13" s="174"/>
+      <c r="B13" s="173"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="34" t="s">
         <v>251</v>
       </c>
-      <c r="B14" s="174"/>
+      <c r="B14" s="173"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="B15" s="174"/>
+      <c r="B15" s="173"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="B16" s="174"/>
+      <c r="B16" s="173"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="B17" s="174"/>
+      <c r="B17" s="173"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="34" t="s">
         <v>587</v>
       </c>
-      <c r="B18" s="174"/>
+      <c r="B18" s="173"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="B19" s="174"/>
+      <c r="B19" s="173"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="34" t="s">
         <v>588</v>
       </c>
-      <c r="B20" s="174"/>
+      <c r="B20" s="173"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="39" t="s">
         <v>589</v>
       </c>
-      <c r="B21" s="174"/>
+      <c r="B21" s="173"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="39" t="s">
         <v>260</v>
       </c>
-      <c r="B22" s="174"/>
+      <c r="B22" s="173"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="40" t="s">
         <v>242</v>
       </c>
-      <c r="B23" s="176"/>
+      <c r="B23" s="175"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="B24" s="177"/>
+      <c r="B24" s="176"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="33" t="s">
         <v>590</v>
       </c>
-      <c r="B25" s="173" t="s">
+      <c r="B25" s="172" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12823,61 +12783,61 @@
       <c r="A26" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="B26" s="174"/>
+      <c r="B26" s="173"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="34" t="s">
         <v>270</v>
       </c>
-      <c r="B27" s="174"/>
+      <c r="B27" s="173"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="B28" s="174"/>
+      <c r="B28" s="173"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="34" t="s">
         <v>272</v>
       </c>
-      <c r="B29" s="174"/>
+      <c r="B29" s="173"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="34" t="s">
         <v>591</v>
       </c>
-      <c r="B30" s="174"/>
+      <c r="B30" s="173"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="B31" s="174"/>
+      <c r="B31" s="173"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="34" t="s">
         <v>592</v>
       </c>
-      <c r="B32" s="174"/>
+      <c r="B32" s="173"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="34" t="s">
         <v>593</v>
       </c>
-      <c r="B33" s="174"/>
+      <c r="B33" s="173"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="41" t="s">
         <v>263</v>
       </c>
-      <c r="B34" s="175"/>
+      <c r="B34" s="174"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="42" t="s">
         <v>594</v>
       </c>
-      <c r="B35" s="173" t="s">
+      <c r="B35" s="172" t="s">
         <v>595</v>
       </c>
     </row>
@@ -12885,13 +12845,13 @@
       <c r="A36" s="41" t="s">
         <v>596</v>
       </c>
-      <c r="B36" s="175"/>
+      <c r="B36" s="174"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="34" t="s">
         <v>278</v>
       </c>
-      <c r="B37" s="173" t="s">
+      <c r="B37" s="172" t="s">
         <v>6</v>
       </c>
     </row>
@@ -12899,19 +12859,19 @@
       <c r="A38" s="39" t="s">
         <v>279</v>
       </c>
-      <c r="B38" s="174"/>
+      <c r="B38" s="173"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="B39" s="174"/>
+      <c r="B39" s="173"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="33" t="s">
         <v>597</v>
       </c>
-      <c r="B40" s="173" t="s">
+      <c r="B40" s="172" t="s">
         <v>598</v>
       </c>
     </row>
@@ -12919,37 +12879,37 @@
       <c r="A41" s="34" t="s">
         <v>599</v>
       </c>
-      <c r="B41" s="174"/>
+      <c r="B41" s="173"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="B42" s="174"/>
+      <c r="B42" s="173"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="34" t="s">
         <v>600</v>
       </c>
-      <c r="B43" s="174"/>
+      <c r="B43" s="173"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="34" t="s">
         <v>601</v>
       </c>
-      <c r="B44" s="174"/>
+      <c r="B44" s="173"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="34" t="s">
         <v>288</v>
       </c>
-      <c r="B45" s="174"/>
+      <c r="B45" s="173"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="37" t="s">
         <v>289</v>
       </c>
-      <c r="B46" s="175"/>
+      <c r="B46" s="174"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="43" t="s">
@@ -12963,7 +12923,7 @@
       <c r="A48" s="34" t="s">
         <v>292</v>
       </c>
-      <c r="B48" s="173" t="s">
+      <c r="B48" s="172" t="s">
         <v>602</v>
       </c>
     </row>
@@ -12971,13 +12931,13 @@
       <c r="A49" s="34" t="s">
         <v>293</v>
       </c>
-      <c r="B49" s="175"/>
+      <c r="B49" s="174"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="B50" s="173" t="s">
+      <c r="B50" s="172" t="s">
         <v>10</v>
       </c>
     </row>
@@ -12985,25 +12945,25 @@
       <c r="A51" s="34" t="s">
         <v>297</v>
       </c>
-      <c r="B51" s="174"/>
+      <c r="B51" s="173"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="34" t="s">
         <v>294</v>
       </c>
-      <c r="B52" s="174"/>
+      <c r="B52" s="173"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="34" t="s">
         <v>295</v>
       </c>
-      <c r="B53" s="174"/>
+      <c r="B53" s="173"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="41" t="s">
         <v>296</v>
       </c>
-      <c r="B54" s="175"/>
+      <c r="B54" s="174"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="43" t="s">
@@ -13017,7 +12977,7 @@
       <c r="A56" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="B56" s="173" t="s">
+      <c r="B56" s="172" t="s">
         <v>13</v>
       </c>
     </row>
@@ -13025,19 +12985,19 @@
       <c r="A57" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="B57" s="174"/>
+      <c r="B57" s="173"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="37" t="s">
         <v>304</v>
       </c>
-      <c r="B58" s="175"/>
+      <c r="B58" s="174"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="34" t="s">
         <v>338</v>
       </c>
-      <c r="B59" s="181" t="s">
+      <c r="B59" s="180" t="s">
         <v>12</v>
       </c>
     </row>
@@ -13045,37 +13005,37 @@
       <c r="A60" s="34" t="s">
         <v>342</v>
       </c>
-      <c r="B60" s="182"/>
+      <c r="B60" s="181"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="34" t="s">
         <v>339</v>
       </c>
-      <c r="B61" s="182"/>
+      <c r="B61" s="181"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="B62" s="182"/>
+      <c r="B62" s="181"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="34" t="s">
         <v>343</v>
       </c>
-      <c r="B63" s="182"/>
+      <c r="B63" s="181"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="45" t="s">
         <v>341</v>
       </c>
-      <c r="B64" s="183"/>
+      <c r="B64" s="182"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="34" t="s">
         <v>605</v>
       </c>
-      <c r="B65" s="184" t="s">
+      <c r="B65" s="183" t="s">
         <v>606</v>
       </c>
     </row>
@@ -13083,26 +13043,26 @@
       <c r="A66" s="34" t="s">
         <v>281</v>
       </c>
-      <c r="B66" s="185"/>
+      <c r="B66" s="184"/>
       <c r="E66" s="46"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="39" t="s">
         <v>300</v>
       </c>
-      <c r="B67" s="185"/>
+      <c r="B67" s="184"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="B68" s="186"/>
+      <c r="B68" s="185"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="47" t="s">
         <v>306</v>
       </c>
-      <c r="B69" s="181" t="s">
+      <c r="B69" s="180" t="s">
         <v>15</v>
       </c>
     </row>
@@ -13110,37 +13070,37 @@
       <c r="A70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="B70" s="182"/>
+      <c r="B70" s="181"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="48" t="s">
         <v>308</v>
       </c>
-      <c r="B71" s="182"/>
+      <c r="B71" s="181"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="34" t="s">
         <v>309</v>
       </c>
-      <c r="B72" s="182"/>
+      <c r="B72" s="181"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="B73" s="182"/>
+      <c r="B73" s="181"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="34" t="s">
         <v>311</v>
       </c>
-      <c r="B74" s="183"/>
+      <c r="B74" s="182"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="47" t="s">
         <v>313</v>
       </c>
-      <c r="B75" s="181" t="s">
+      <c r="B75" s="180" t="s">
         <v>16</v>
       </c>
     </row>
@@ -13148,139 +13108,139 @@
       <c r="A76" s="34" t="s">
         <v>314</v>
       </c>
-      <c r="B76" s="182"/>
+      <c r="B76" s="181"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="34" t="s">
         <v>315</v>
       </c>
-      <c r="B77" s="182"/>
+      <c r="B77" s="181"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="34" t="s">
         <v>316</v>
       </c>
-      <c r="B78" s="182"/>
+      <c r="B78" s="181"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="B79" s="182"/>
+      <c r="B79" s="181"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="B80" s="182"/>
+      <c r="B80" s="181"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="B81" s="182"/>
+      <c r="B81" s="181"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="B82" s="182"/>
+      <c r="B82" s="181"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="34" t="s">
         <v>322</v>
       </c>
-      <c r="B83" s="182"/>
+      <c r="B83" s="181"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="34" t="s">
         <v>323</v>
       </c>
-      <c r="B84" s="182"/>
+      <c r="B84" s="181"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="34" t="s">
         <v>324</v>
       </c>
-      <c r="B85" s="182"/>
+      <c r="B85" s="181"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="49" t="s">
         <v>325</v>
       </c>
-      <c r="B86" s="182"/>
+      <c r="B86" s="181"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="B87" s="182"/>
+      <c r="B87" s="181"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="34" t="s">
         <v>327</v>
       </c>
-      <c r="B88" s="182"/>
+      <c r="B88" s="181"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="34" t="s">
         <v>328</v>
       </c>
-      <c r="B89" s="182"/>
+      <c r="B89" s="181"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="B90" s="182"/>
+      <c r="B90" s="181"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="B91" s="182"/>
+      <c r="B91" s="181"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="34" t="s">
         <v>331</v>
       </c>
-      <c r="B92" s="182"/>
+      <c r="B92" s="181"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="34" t="s">
         <v>332</v>
       </c>
-      <c r="B93" s="182"/>
+      <c r="B93" s="181"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="49" t="s">
         <v>333</v>
       </c>
-      <c r="B94" s="182"/>
+      <c r="B94" s="181"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="49" t="s">
         <v>334</v>
       </c>
-      <c r="B95" s="182"/>
+      <c r="B95" s="181"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="49" t="s">
         <v>335</v>
       </c>
-      <c r="B96" s="182"/>
+      <c r="B96" s="181"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="34" t="s">
         <v>336</v>
       </c>
-      <c r="B97" s="182"/>
+      <c r="B97" s="181"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="50" t="s">
         <v>345</v>
       </c>
-      <c r="B98" s="178" t="s">
+      <c r="B98" s="177" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13288,37 +13248,37 @@
       <c r="A99" s="51" t="s">
         <v>346</v>
       </c>
-      <c r="B99" s="179"/>
+      <c r="B99" s="178"/>
     </row>
     <row r="100" spans="1:2" s="29" customFormat="1">
       <c r="A100" s="51" t="s">
         <v>347</v>
       </c>
-      <c r="B100" s="179"/>
+      <c r="B100" s="178"/>
     </row>
     <row r="101" spans="1:2" s="29" customFormat="1">
       <c r="A101" s="51" t="s">
         <v>348</v>
       </c>
-      <c r="B101" s="179"/>
+      <c r="B101" s="178"/>
     </row>
     <row r="102" spans="1:2" s="29" customFormat="1">
       <c r="A102" s="51" t="s">
         <v>349</v>
       </c>
-      <c r="B102" s="179"/>
+      <c r="B102" s="178"/>
     </row>
     <row r="103" spans="1:2" s="29" customFormat="1">
       <c r="A103" s="51" t="s">
         <v>350</v>
       </c>
-      <c r="B103" s="179"/>
+      <c r="B103" s="178"/>
     </row>
     <row r="104" spans="1:2" s="29" customFormat="1">
       <c r="A104" s="45" t="s">
         <v>351</v>
       </c>
-      <c r="B104" s="180"/>
+      <c r="B104" s="179"/>
     </row>
     <row r="105" spans="1:2" s="29" customFormat="1">
       <c r="A105" s="52" t="s">
@@ -13380,19 +13340,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IV240"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" style="10" customWidth="1"/>
-    <col min="2" max="2" width="35.5" style="23" customWidth="1"/>
-    <col min="3" max="256" width="9.125" style="10"/>
-    <col min="257" max="16384" width="9.125" style="1"/>
+    <col min="2" max="2" width="35.453125" style="23" customWidth="1"/>
+    <col min="3" max="256" width="9.08984375" style="10"/>
+    <col min="257" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27" customHeight="1">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="186" t="s">
         <v>609</v>
       </c>
-      <c r="B1" s="188"/>
+      <c r="B1" s="187"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="24" t="s">
@@ -15320,18 +15280,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B179"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" style="16" customWidth="1"/>
-    <col min="2" max="2" width="35.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.453125" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="188" t="s">
         <v>1088</v>
       </c>
-      <c r="B1" s="189"/>
+      <c r="B1" s="188"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="17" t="s">
@@ -16769,10 +16729,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="103.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="103.7265625" style="2" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16800,7 +16760,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="27">
+    <row r="4" spans="1:2" ht="28">
       <c r="B4" s="2" t="s">
         <v>1446</v>
       </c>
@@ -16810,7 +16770,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="67.5">
+    <row r="6" spans="1:2" ht="84">
       <c r="B6" s="2" t="s">
         <v>1448</v>
       </c>
@@ -16844,7 +16804,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="27">
+    <row r="14" spans="1:2" ht="28">
       <c r="B14" s="7" t="s">
         <v>1452</v>
       </c>
@@ -16864,7 +16824,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="40.5">
+    <row r="18" spans="1:2" ht="42">
       <c r="B18" s="7" t="s">
         <v>1456</v>
       </c>
@@ -16889,7 +16849,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="27">
+    <row r="23" spans="1:2" ht="28">
       <c r="B23" s="7" t="s">
         <v>1461</v>
       </c>
@@ -16913,7 +16873,7 @@
         <v>43245</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="67.5">
+    <row r="28" spans="1:2" ht="84">
       <c r="A28" s="9" t="s">
         <v>1444</v>
       </c>
@@ -16940,7 +16900,7 @@
         <v>43126</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="297">
+    <row r="32" spans="1:2" ht="322">
       <c r="A32" s="9" t="s">
         <v>1444</v>
       </c>
@@ -16992,7 +16952,7 @@
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="190" t="s">
+      <c r="A40" s="189" t="s">
         <v>1444</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -17000,120 +16960,120 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="190"/>
+      <c r="A41" s="189"/>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="190"/>
+      <c r="A42" s="189"/>
       <c r="B42" s="11" t="s">
         <v>1470</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="190"/>
+      <c r="A43" s="189"/>
       <c r="B43" s="11"/>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="190"/>
+      <c r="A44" s="189"/>
       <c r="B44" s="11" t="s">
         <v>1471</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="190"/>
+      <c r="A45" s="189"/>
       <c r="B45" s="11"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="190"/>
+      <c r="A46" s="189"/>
       <c r="B46" s="11" t="s">
         <v>1472</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="190"/>
+      <c r="A47" s="189"/>
       <c r="B47" s="11"/>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="190"/>
+      <c r="A48" s="189"/>
       <c r="B48" s="11" t="s">
         <v>1473</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="190"/>
+      <c r="A49" s="189"/>
       <c r="B49" s="11"/>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="190"/>
+      <c r="A50" s="189"/>
       <c r="B50" s="11" t="s">
         <v>1474</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="190"/>
+      <c r="A51" s="189"/>
       <c r="B51" s="11"/>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="190"/>
+      <c r="A52" s="189"/>
       <c r="B52" s="11" t="s">
         <v>1475</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="190"/>
+      <c r="A53" s="189"/>
       <c r="B53" s="11"/>
     </row>
-    <row r="54" spans="1:2" ht="27">
-      <c r="A54" s="190"/>
+    <row r="54" spans="1:2" ht="28">
+      <c r="A54" s="189"/>
       <c r="B54" s="11" t="s">
         <v>1476</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="190"/>
+      <c r="A55" s="189"/>
       <c r="B55" s="11"/>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="190"/>
+      <c r="A56" s="189"/>
       <c r="B56" s="11" t="s">
         <v>1477</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="190"/>
+      <c r="A57" s="189"/>
       <c r="B57" s="11"/>
     </row>
-    <row r="58" spans="1:2" ht="27">
-      <c r="A58" s="190"/>
+    <row r="58" spans="1:2" ht="28">
+      <c r="A58" s="189"/>
       <c r="B58" s="11" t="s">
         <v>1478</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="190"/>
+      <c r="A59" s="189"/>
       <c r="B59" s="11"/>
     </row>
-    <row r="60" spans="1:2" ht="27">
-      <c r="A60" s="190"/>
+    <row r="60" spans="1:2" ht="28">
+      <c r="A60" s="189"/>
       <c r="B60" s="11" t="s">
         <v>1479</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="190"/>
+      <c r="A61" s="189"/>
       <c r="B61" s="11"/>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="190"/>
+      <c r="A62" s="189"/>
       <c r="B62" s="11" t="s">
         <v>1480</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="190"/>
+      <c r="A63" s="189"/>
       <c r="B63" s="11"/>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="190"/>
+      <c r="A64" s="189"/>
       <c r="B64" s="11" t="s">
         <v>1481</v>
       </c>
@@ -17138,7 +17098,7 @@
         <v>42685</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="108">
+    <row r="68" spans="1:2" ht="112">
       <c r="A68" s="10" t="s">
         <v>1444</v>
       </c>
@@ -17230,7 +17190,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="54">
+    <row r="86" spans="1:2" ht="56">
       <c r="A86" s="10" t="s">
         <v>1444</v>
       </c>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetInfoRegist.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetInfoRegist.xlsx
@@ -7637,28 +7637,58 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -7669,35 +7699,59 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7720,58 +7774,40 @@
     <xf numFmtId="49" fontId="16" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7780,47 +7816,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8384,316 +8384,316 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:273" s="72" customFormat="1">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="128" t="s">
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="125" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="130"/>
-      <c r="L1" s="129"/>
-      <c r="M1" s="129"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="132" t="s">
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="126"/>
+      <c r="M1" s="126"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
-      <c r="R1" s="132"/>
-      <c r="S1" s="132"/>
-      <c r="T1" s="132"/>
-      <c r="U1" s="132"/>
-      <c r="V1" s="132"/>
-      <c r="W1" s="132"/>
-      <c r="X1" s="132"/>
-      <c r="Y1" s="132"/>
-      <c r="Z1" s="128" t="s">
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="137"/>
+      <c r="Y1" s="137"/>
+      <c r="Z1" s="125" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="129"/>
-      <c r="AB1" s="129"/>
-      <c r="AC1" s="129"/>
-      <c r="AD1" s="129"/>
-      <c r="AE1" s="129"/>
-      <c r="AF1" s="129"/>
-      <c r="AG1" s="131"/>
-      <c r="AH1" s="125" t="s">
+      <c r="AA1" s="126"/>
+      <c r="AB1" s="126"/>
+      <c r="AC1" s="126"/>
+      <c r="AD1" s="126"/>
+      <c r="AE1" s="126"/>
+      <c r="AF1" s="126"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="141" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="126"/>
-      <c r="AJ1" s="126"/>
-      <c r="AK1" s="126"/>
-      <c r="AL1" s="126"/>
-      <c r="AM1" s="126"/>
-      <c r="AN1" s="126"/>
-      <c r="AO1" s="126"/>
-      <c r="AP1" s="126"/>
-      <c r="AQ1" s="126"/>
-      <c r="AR1" s="126"/>
-      <c r="AS1" s="126"/>
-      <c r="AT1" s="126"/>
-      <c r="AU1" s="126"/>
-      <c r="AV1" s="126"/>
-      <c r="AW1" s="126"/>
-      <c r="AX1" s="126"/>
-      <c r="AY1" s="126"/>
-      <c r="AZ1" s="126"/>
-      <c r="BA1" s="126"/>
-      <c r="BB1" s="126"/>
-      <c r="BC1" s="126"/>
-      <c r="BD1" s="126"/>
-      <c r="BE1" s="126"/>
-      <c r="BF1" s="126"/>
-      <c r="BG1" s="126"/>
-      <c r="BH1" s="126"/>
-      <c r="BI1" s="126"/>
-      <c r="BJ1" s="126"/>
-      <c r="BK1" s="126"/>
-      <c r="BL1" s="126"/>
-      <c r="BM1" s="126"/>
-      <c r="BN1" s="126"/>
-      <c r="BO1" s="126"/>
-      <c r="BP1" s="126"/>
-      <c r="BQ1" s="126"/>
-      <c r="BR1" s="126"/>
-      <c r="BS1" s="126"/>
-      <c r="BT1" s="126"/>
-      <c r="BU1" s="126"/>
-      <c r="BV1" s="126"/>
-      <c r="BW1" s="126"/>
-      <c r="BX1" s="126"/>
-      <c r="BY1" s="126"/>
-      <c r="BZ1" s="126"/>
-      <c r="CA1" s="126"/>
-      <c r="CB1" s="133"/>
-      <c r="CC1" s="133"/>
-      <c r="CD1" s="133"/>
-      <c r="CE1" s="133"/>
-      <c r="CF1" s="133"/>
-      <c r="CG1" s="133"/>
-      <c r="CH1" s="133"/>
-      <c r="CI1" s="133"/>
-      <c r="CJ1" s="133"/>
-      <c r="CK1" s="133"/>
-      <c r="CL1" s="133"/>
-      <c r="CM1" s="134"/>
-      <c r="CN1" s="126"/>
-      <c r="CO1" s="126"/>
-      <c r="CP1" s="126"/>
-      <c r="CQ1" s="126"/>
-      <c r="CR1" s="126"/>
-      <c r="CS1" s="126"/>
-      <c r="CT1" s="126"/>
-      <c r="CU1" s="127"/>
-      <c r="CV1" s="135" t="s">
+      <c r="AI1" s="135"/>
+      <c r="AJ1" s="135"/>
+      <c r="AK1" s="135"/>
+      <c r="AL1" s="135"/>
+      <c r="AM1" s="135"/>
+      <c r="AN1" s="135"/>
+      <c r="AO1" s="135"/>
+      <c r="AP1" s="135"/>
+      <c r="AQ1" s="135"/>
+      <c r="AR1" s="135"/>
+      <c r="AS1" s="135"/>
+      <c r="AT1" s="135"/>
+      <c r="AU1" s="135"/>
+      <c r="AV1" s="135"/>
+      <c r="AW1" s="135"/>
+      <c r="AX1" s="135"/>
+      <c r="AY1" s="135"/>
+      <c r="AZ1" s="135"/>
+      <c r="BA1" s="135"/>
+      <c r="BB1" s="135"/>
+      <c r="BC1" s="135"/>
+      <c r="BD1" s="135"/>
+      <c r="BE1" s="135"/>
+      <c r="BF1" s="135"/>
+      <c r="BG1" s="135"/>
+      <c r="BH1" s="135"/>
+      <c r="BI1" s="135"/>
+      <c r="BJ1" s="135"/>
+      <c r="BK1" s="135"/>
+      <c r="BL1" s="135"/>
+      <c r="BM1" s="135"/>
+      <c r="BN1" s="135"/>
+      <c r="BO1" s="135"/>
+      <c r="BP1" s="135"/>
+      <c r="BQ1" s="135"/>
+      <c r="BR1" s="135"/>
+      <c r="BS1" s="135"/>
+      <c r="BT1" s="135"/>
+      <c r="BU1" s="135"/>
+      <c r="BV1" s="135"/>
+      <c r="BW1" s="135"/>
+      <c r="BX1" s="135"/>
+      <c r="BY1" s="135"/>
+      <c r="BZ1" s="135"/>
+      <c r="CA1" s="135"/>
+      <c r="CB1" s="143"/>
+      <c r="CC1" s="143"/>
+      <c r="CD1" s="143"/>
+      <c r="CE1" s="143"/>
+      <c r="CF1" s="143"/>
+      <c r="CG1" s="143"/>
+      <c r="CH1" s="143"/>
+      <c r="CI1" s="143"/>
+      <c r="CJ1" s="143"/>
+      <c r="CK1" s="143"/>
+      <c r="CL1" s="143"/>
+      <c r="CM1" s="144"/>
+      <c r="CN1" s="135"/>
+      <c r="CO1" s="135"/>
+      <c r="CP1" s="135"/>
+      <c r="CQ1" s="135"/>
+      <c r="CR1" s="135"/>
+      <c r="CS1" s="135"/>
+      <c r="CT1" s="135"/>
+      <c r="CU1" s="142"/>
+      <c r="CV1" s="136" t="s">
         <v>5</v>
       </c>
-      <c r="CW1" s="132"/>
-      <c r="CX1" s="132"/>
-      <c r="CY1" s="132"/>
-      <c r="CZ1" s="132"/>
-      <c r="DA1" s="132"/>
-      <c r="DB1" s="132"/>
-      <c r="DC1" s="132"/>
-      <c r="DD1" s="132"/>
-      <c r="DE1" s="132"/>
-      <c r="DF1" s="132"/>
-      <c r="DG1" s="136"/>
-      <c r="DH1" s="137" t="s">
+      <c r="CW1" s="137"/>
+      <c r="CX1" s="137"/>
+      <c r="CY1" s="137"/>
+      <c r="CZ1" s="137"/>
+      <c r="DA1" s="137"/>
+      <c r="DB1" s="137"/>
+      <c r="DC1" s="137"/>
+      <c r="DD1" s="137"/>
+      <c r="DE1" s="137"/>
+      <c r="DF1" s="137"/>
+      <c r="DG1" s="138"/>
+      <c r="DH1" s="131" t="s">
         <v>6</v>
       </c>
-      <c r="DI1" s="138"/>
-      <c r="DJ1" s="138"/>
-      <c r="DK1" s="138"/>
-      <c r="DL1" s="138"/>
-      <c r="DM1" s="138"/>
-      <c r="DN1" s="138"/>
-      <c r="DO1" s="138"/>
-      <c r="DP1" s="138"/>
-      <c r="DQ1" s="138"/>
-      <c r="DR1" s="138"/>
+      <c r="DI1" s="132"/>
+      <c r="DJ1" s="132"/>
+      <c r="DK1" s="132"/>
+      <c r="DL1" s="132"/>
+      <c r="DM1" s="132"/>
+      <c r="DN1" s="132"/>
+      <c r="DO1" s="132"/>
+      <c r="DP1" s="132"/>
+      <c r="DQ1" s="132"/>
+      <c r="DR1" s="132"/>
       <c r="DS1" s="139" t="s">
         <v>7</v>
       </c>
       <c r="DT1" s="140"/>
       <c r="DU1" s="140"/>
       <c r="DV1" s="140"/>
-      <c r="DW1" s="141" t="s">
+      <c r="DW1" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="DX1" s="130"/>
-      <c r="DY1" s="142"/>
-      <c r="DZ1" s="142"/>
-      <c r="EA1" s="142"/>
-      <c r="EB1" s="142"/>
-      <c r="EC1" s="142"/>
-      <c r="ED1" s="142"/>
-      <c r="EE1" s="142"/>
-      <c r="EF1" s="142"/>
-      <c r="EG1" s="142"/>
-      <c r="EH1" s="142"/>
-      <c r="EI1" s="142"/>
-      <c r="EJ1" s="143"/>
-      <c r="EK1" s="137" t="s">
+      <c r="DX1" s="134"/>
+      <c r="DY1" s="129"/>
+      <c r="DZ1" s="129"/>
+      <c r="EA1" s="129"/>
+      <c r="EB1" s="129"/>
+      <c r="EC1" s="129"/>
+      <c r="ED1" s="129"/>
+      <c r="EE1" s="129"/>
+      <c r="EF1" s="129"/>
+      <c r="EG1" s="129"/>
+      <c r="EH1" s="129"/>
+      <c r="EI1" s="129"/>
+      <c r="EJ1" s="130"/>
+      <c r="EK1" s="131" t="s">
         <v>9</v>
       </c>
-      <c r="EL1" s="138"/>
-      <c r="EM1" s="138"/>
-      <c r="EN1" s="138"/>
-      <c r="EO1" s="138"/>
-      <c r="EP1" s="144"/>
-      <c r="EQ1" s="137" t="s">
+      <c r="EL1" s="132"/>
+      <c r="EM1" s="132"/>
+      <c r="EN1" s="132"/>
+      <c r="EO1" s="132"/>
+      <c r="EP1" s="133"/>
+      <c r="EQ1" s="131" t="s">
         <v>10</v>
       </c>
-      <c r="ER1" s="138"/>
-      <c r="ES1" s="138"/>
-      <c r="ET1" s="138"/>
-      <c r="EU1" s="144"/>
-      <c r="EV1" s="137" t="s">
+      <c r="ER1" s="132"/>
+      <c r="ES1" s="132"/>
+      <c r="ET1" s="132"/>
+      <c r="EU1" s="133"/>
+      <c r="EV1" s="131" t="s">
         <v>11</v>
       </c>
-      <c r="EW1" s="138"/>
-      <c r="EX1" s="138"/>
-      <c r="EY1" s="138"/>
-      <c r="EZ1" s="138"/>
-      <c r="FA1" s="138"/>
-      <c r="FB1" s="138"/>
-      <c r="FC1" s="138"/>
-      <c r="FD1" s="138"/>
-      <c r="FE1" s="138"/>
-      <c r="FF1" s="138"/>
-      <c r="FG1" s="138"/>
-      <c r="FH1" s="138"/>
-      <c r="FI1" s="138"/>
-      <c r="FJ1" s="138"/>
-      <c r="FK1" s="138"/>
-      <c r="FL1" s="144"/>
-      <c r="FM1" s="130" t="s">
+      <c r="EW1" s="132"/>
+      <c r="EX1" s="132"/>
+      <c r="EY1" s="132"/>
+      <c r="EZ1" s="132"/>
+      <c r="FA1" s="132"/>
+      <c r="FB1" s="132"/>
+      <c r="FC1" s="132"/>
+      <c r="FD1" s="132"/>
+      <c r="FE1" s="132"/>
+      <c r="FF1" s="132"/>
+      <c r="FG1" s="132"/>
+      <c r="FH1" s="132"/>
+      <c r="FI1" s="132"/>
+      <c r="FJ1" s="132"/>
+      <c r="FK1" s="132"/>
+      <c r="FL1" s="133"/>
+      <c r="FM1" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="FN1" s="130"/>
-      <c r="FO1" s="130"/>
-      <c r="FP1" s="130"/>
-      <c r="FQ1" s="130"/>
-      <c r="FR1" s="130"/>
-      <c r="FS1" s="130"/>
-      <c r="FT1" s="130"/>
-      <c r="FU1" s="130"/>
-      <c r="FV1" s="130"/>
-      <c r="FW1" s="130"/>
-      <c r="FX1" s="130"/>
-      <c r="FY1" s="130"/>
-      <c r="FZ1" s="130"/>
-      <c r="GA1" s="130"/>
-      <c r="GB1" s="130"/>
-      <c r="GC1" s="130"/>
-      <c r="GD1" s="130"/>
-      <c r="GE1" s="130"/>
-      <c r="GF1" s="130"/>
-      <c r="GG1" s="130"/>
-      <c r="GH1" s="130"/>
-      <c r="GI1" s="130"/>
-      <c r="GJ1" s="137" t="s">
+      <c r="FN1" s="134"/>
+      <c r="FO1" s="134"/>
+      <c r="FP1" s="134"/>
+      <c r="FQ1" s="134"/>
+      <c r="FR1" s="134"/>
+      <c r="FS1" s="134"/>
+      <c r="FT1" s="134"/>
+      <c r="FU1" s="134"/>
+      <c r="FV1" s="134"/>
+      <c r="FW1" s="134"/>
+      <c r="FX1" s="134"/>
+      <c r="FY1" s="134"/>
+      <c r="FZ1" s="134"/>
+      <c r="GA1" s="134"/>
+      <c r="GB1" s="134"/>
+      <c r="GC1" s="134"/>
+      <c r="GD1" s="134"/>
+      <c r="GE1" s="134"/>
+      <c r="GF1" s="134"/>
+      <c r="GG1" s="134"/>
+      <c r="GH1" s="134"/>
+      <c r="GI1" s="134"/>
+      <c r="GJ1" s="131" t="s">
         <v>13</v>
       </c>
-      <c r="GK1" s="138"/>
-      <c r="GL1" s="138"/>
-      <c r="GM1" s="138"/>
-      <c r="GN1" s="144"/>
-      <c r="GO1" s="128" t="s">
+      <c r="GK1" s="132"/>
+      <c r="GL1" s="132"/>
+      <c r="GM1" s="132"/>
+      <c r="GN1" s="133"/>
+      <c r="GO1" s="125" t="s">
         <v>14</v>
       </c>
-      <c r="GP1" s="129"/>
-      <c r="GQ1" s="129"/>
-      <c r="GR1" s="129"/>
-      <c r="GS1" s="129"/>
-      <c r="GT1" s="129"/>
-      <c r="GU1" s="129"/>
-      <c r="GV1" s="129"/>
-      <c r="GW1" s="129"/>
-      <c r="GX1" s="129"/>
-      <c r="GY1" s="129"/>
-      <c r="GZ1" s="129"/>
-      <c r="HA1" s="129"/>
-      <c r="HB1" s="129"/>
-      <c r="HC1" s="129"/>
-      <c r="HD1" s="129"/>
-      <c r="HE1" s="129"/>
-      <c r="HF1" s="129"/>
-      <c r="HG1" s="129"/>
-      <c r="HH1" s="129"/>
-      <c r="HI1" s="129"/>
-      <c r="HJ1" s="129"/>
-      <c r="HK1" s="129"/>
-      <c r="HL1" s="129"/>
-      <c r="HM1" s="129"/>
-      <c r="HN1" s="129"/>
-      <c r="HO1" s="129"/>
-      <c r="HP1" s="129"/>
-      <c r="HQ1" s="126"/>
-      <c r="HR1" s="129"/>
-      <c r="HS1" s="128" t="s">
+      <c r="GP1" s="126"/>
+      <c r="GQ1" s="126"/>
+      <c r="GR1" s="126"/>
+      <c r="GS1" s="126"/>
+      <c r="GT1" s="126"/>
+      <c r="GU1" s="126"/>
+      <c r="GV1" s="126"/>
+      <c r="GW1" s="126"/>
+      <c r="GX1" s="126"/>
+      <c r="GY1" s="126"/>
+      <c r="GZ1" s="126"/>
+      <c r="HA1" s="126"/>
+      <c r="HB1" s="126"/>
+      <c r="HC1" s="126"/>
+      <c r="HD1" s="126"/>
+      <c r="HE1" s="126"/>
+      <c r="HF1" s="126"/>
+      <c r="HG1" s="126"/>
+      <c r="HH1" s="126"/>
+      <c r="HI1" s="126"/>
+      <c r="HJ1" s="126"/>
+      <c r="HK1" s="126"/>
+      <c r="HL1" s="126"/>
+      <c r="HM1" s="126"/>
+      <c r="HN1" s="126"/>
+      <c r="HO1" s="126"/>
+      <c r="HP1" s="126"/>
+      <c r="HQ1" s="135"/>
+      <c r="HR1" s="126"/>
+      <c r="HS1" s="125" t="s">
         <v>15</v>
       </c>
-      <c r="HT1" s="129"/>
-      <c r="HU1" s="129"/>
-      <c r="HV1" s="129"/>
-      <c r="HW1" s="129"/>
-      <c r="HX1" s="131"/>
-      <c r="HY1" s="128" t="s">
+      <c r="HT1" s="126"/>
+      <c r="HU1" s="126"/>
+      <c r="HV1" s="126"/>
+      <c r="HW1" s="126"/>
+      <c r="HX1" s="127"/>
+      <c r="HY1" s="125" t="s">
         <v>16</v>
       </c>
-      <c r="HZ1" s="129"/>
-      <c r="IA1" s="129"/>
-      <c r="IB1" s="129"/>
-      <c r="IC1" s="129"/>
-      <c r="ID1" s="129"/>
-      <c r="IE1" s="129"/>
-      <c r="IF1" s="129"/>
-      <c r="IG1" s="129"/>
-      <c r="IH1" s="129"/>
-      <c r="II1" s="129"/>
-      <c r="IJ1" s="129"/>
-      <c r="IK1" s="129"/>
-      <c r="IL1" s="129"/>
-      <c r="IM1" s="131"/>
-      <c r="IN1" s="141" t="s">
+      <c r="HZ1" s="126"/>
+      <c r="IA1" s="126"/>
+      <c r="IB1" s="126"/>
+      <c r="IC1" s="126"/>
+      <c r="ID1" s="126"/>
+      <c r="IE1" s="126"/>
+      <c r="IF1" s="126"/>
+      <c r="IG1" s="126"/>
+      <c r="IH1" s="126"/>
+      <c r="II1" s="126"/>
+      <c r="IJ1" s="126"/>
+      <c r="IK1" s="126"/>
+      <c r="IL1" s="126"/>
+      <c r="IM1" s="127"/>
+      <c r="IN1" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="IO1" s="142"/>
-      <c r="IP1" s="142"/>
-      <c r="IQ1" s="142"/>
-      <c r="IR1" s="142"/>
-      <c r="IS1" s="142"/>
-      <c r="IT1" s="142"/>
-      <c r="IU1" s="142"/>
-      <c r="IV1" s="142"/>
-      <c r="IW1" s="142"/>
-      <c r="IX1" s="142"/>
-      <c r="IY1" s="142"/>
-      <c r="IZ1" s="142"/>
-      <c r="JA1" s="142"/>
-      <c r="JB1" s="142"/>
-      <c r="JC1" s="142"/>
-      <c r="JD1" s="142"/>
-      <c r="JE1" s="142"/>
-      <c r="JF1" s="142"/>
-      <c r="JG1" s="143"/>
-      <c r="JH1" s="141" t="s">
+      <c r="IO1" s="129"/>
+      <c r="IP1" s="129"/>
+      <c r="IQ1" s="129"/>
+      <c r="IR1" s="129"/>
+      <c r="IS1" s="129"/>
+      <c r="IT1" s="129"/>
+      <c r="IU1" s="129"/>
+      <c r="IV1" s="129"/>
+      <c r="IW1" s="129"/>
+      <c r="IX1" s="129"/>
+      <c r="IY1" s="129"/>
+      <c r="IZ1" s="129"/>
+      <c r="JA1" s="129"/>
+      <c r="JB1" s="129"/>
+      <c r="JC1" s="129"/>
+      <c r="JD1" s="129"/>
+      <c r="JE1" s="129"/>
+      <c r="JF1" s="129"/>
+      <c r="JG1" s="130"/>
+      <c r="JH1" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="JI1" s="142"/>
-      <c r="JJ1" s="142"/>
-      <c r="JK1" s="142"/>
-      <c r="JL1" s="142"/>
+      <c r="JI1" s="129"/>
+      <c r="JJ1" s="129"/>
+      <c r="JK1" s="129"/>
+      <c r="JL1" s="129"/>
       <c r="JM1" s="117"/>
     </row>
     <row r="2" spans="1:273" s="73" customFormat="1">
@@ -10095,6 +10095,16 @@
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="19">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:N1"/>
+    <mergeCell ref="O1:Y1"/>
+    <mergeCell ref="Z1:AG1"/>
+    <mergeCell ref="AH1:CU1"/>
+    <mergeCell ref="CV1:DG1"/>
+    <mergeCell ref="DH1:DR1"/>
+    <mergeCell ref="DS1:DV1"/>
+    <mergeCell ref="DW1:EJ1"/>
+    <mergeCell ref="EK1:EP1"/>
     <mergeCell ref="HS1:HX1"/>
     <mergeCell ref="HY1:IM1"/>
     <mergeCell ref="IN1:JG1"/>
@@ -10104,16 +10114,6 @@
     <mergeCell ref="FM1:GI1"/>
     <mergeCell ref="GJ1:GN1"/>
     <mergeCell ref="GO1:HR1"/>
-    <mergeCell ref="CV1:DG1"/>
-    <mergeCell ref="DH1:DR1"/>
-    <mergeCell ref="DS1:DV1"/>
-    <mergeCell ref="DW1:EJ1"/>
-    <mergeCell ref="EK1:EP1"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:N1"/>
-    <mergeCell ref="O1:Y1"/>
-    <mergeCell ref="Z1:AG1"/>
-    <mergeCell ref="AH1:CU1"/>
   </mergeCells>
   <phoneticPr fontId="36" type="noConversion"/>
   <dataValidations count="130">
@@ -10614,13 +10614,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="163" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="146"/>
+      <c r="B1" s="164"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="154" t="s">
         <v>239</v>
       </c>
       <c r="B2" s="42" t="s">
@@ -10628,25 +10628,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="160"/>
+      <c r="A3" s="155"/>
       <c r="B3" s="39" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="160"/>
+      <c r="A4" s="155"/>
       <c r="B4" s="39" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="161"/>
+      <c r="A5" s="156"/>
       <c r="B5" s="37" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="30" customFormat="1">
-      <c r="A6" s="162" t="s">
+      <c r="A6" s="157" t="s">
         <v>241</v>
       </c>
       <c r="B6" s="42" t="s">
@@ -10654,13 +10654,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="30" customFormat="1">
-      <c r="A7" s="163"/>
+      <c r="A7" s="158"/>
       <c r="B7" s="36" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="30" customFormat="1">
-      <c r="A8" s="164" t="s">
+      <c r="A8" s="159" t="s">
         <v>244</v>
       </c>
       <c r="B8" s="35" t="s">
@@ -10668,13 +10668,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="30" customFormat="1">
-      <c r="A9" s="163"/>
+      <c r="A9" s="158"/>
       <c r="B9" s="36" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="152" t="s">
+      <c r="A10" s="160" t="s">
         <v>247</v>
       </c>
       <c r="B10" s="39" t="s">
@@ -10682,61 +10682,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="165"/>
+      <c r="A11" s="161"/>
       <c r="B11" s="39" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="165"/>
+      <c r="A12" s="161"/>
       <c r="B12" s="39" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="165"/>
+      <c r="A13" s="161"/>
       <c r="B13" s="39" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="165"/>
+      <c r="A14" s="161"/>
       <c r="B14" s="39" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="165"/>
+      <c r="A15" s="161"/>
       <c r="B15" s="39" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="165"/>
+      <c r="A16" s="161"/>
       <c r="B16" s="39" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="165"/>
+      <c r="A17" s="161"/>
       <c r="B17" s="39" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="165"/>
+      <c r="A18" s="161"/>
       <c r="B18" s="39" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="165"/>
+      <c r="A19" s="161"/>
       <c r="B19" s="39" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="165"/>
+      <c r="A20" s="161"/>
       <c r="B20" s="39" t="s">
         <v>258</v>
       </c>
@@ -10750,7 +10750,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="152" t="s">
+      <c r="A22" s="160" t="s">
         <v>261</v>
       </c>
       <c r="B22" s="42" t="s">
@@ -10758,19 +10758,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="165"/>
+      <c r="A23" s="161"/>
       <c r="B23" s="39" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="153"/>
+      <c r="A24" s="162"/>
       <c r="B24" s="37" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="152" t="s">
+      <c r="A25" s="160" t="s">
         <v>265</v>
       </c>
       <c r="B25" s="39" t="s">
@@ -10778,67 +10778,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="165"/>
+      <c r="A26" s="161"/>
       <c r="B26" s="39" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="165"/>
+      <c r="A27" s="161"/>
       <c r="B27" s="34" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="165"/>
+      <c r="A28" s="161"/>
       <c r="B28" s="34" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="165"/>
+      <c r="A29" s="161"/>
       <c r="B29" s="34" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="165"/>
+      <c r="A30" s="161"/>
       <c r="B30" s="34" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="165"/>
+      <c r="A31" s="161"/>
       <c r="B31" s="34" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="165"/>
+      <c r="A32" s="161"/>
       <c r="B32" s="34" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="165"/>
+      <c r="A33" s="161"/>
       <c r="B33" s="34" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="165"/>
+      <c r="A34" s="161"/>
       <c r="B34" s="34" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="153"/>
+      <c r="A35" s="162"/>
       <c r="B35" s="55" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="152" t="s">
+      <c r="A36" s="160" t="s">
         <v>277</v>
       </c>
       <c r="B36" s="34" t="s">
@@ -10846,25 +10846,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="165"/>
+      <c r="A37" s="161"/>
       <c r="B37" s="39" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="165"/>
+      <c r="A38" s="161"/>
       <c r="B38" s="34" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="153"/>
+      <c r="A39" s="162"/>
       <c r="B39" s="34" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="152" t="s">
+      <c r="A40" s="160" t="s">
         <v>282</v>
       </c>
       <c r="B40" s="33" t="s">
@@ -10872,43 +10872,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="165"/>
+      <c r="A41" s="161"/>
       <c r="B41" s="34" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="165"/>
+      <c r="A42" s="161"/>
       <c r="B42" s="34" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="165"/>
+      <c r="A43" s="161"/>
       <c r="B43" s="34" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="165"/>
+      <c r="A44" s="161"/>
       <c r="B44" s="34" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="165"/>
+      <c r="A45" s="161"/>
       <c r="B45" s="34" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="153"/>
+      <c r="A46" s="162"/>
       <c r="B46" s="37" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="152" t="s">
+      <c r="A47" s="160" t="s">
         <v>290</v>
       </c>
       <c r="B47" s="42" t="s">
@@ -10916,61 +10916,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="165"/>
+      <c r="A48" s="161"/>
       <c r="B48" s="34" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="165"/>
+      <c r="A49" s="161"/>
       <c r="B49" s="34" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="165"/>
+      <c r="A50" s="161"/>
       <c r="B50" s="34" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="165"/>
+      <c r="A51" s="161"/>
       <c r="B51" s="34" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="165"/>
+      <c r="A52" s="161"/>
       <c r="B52" s="34" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="165"/>
+      <c r="A53" s="161"/>
       <c r="B53" s="39" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="165"/>
+      <c r="A54" s="161"/>
       <c r="B54" s="34" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="165"/>
+      <c r="A55" s="161"/>
       <c r="B55" s="39" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="153"/>
+      <c r="A56" s="162"/>
       <c r="B56" s="37" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="152" t="s">
+      <c r="A57" s="160" t="s">
         <v>301</v>
       </c>
       <c r="B57" s="33" t="s">
@@ -10978,19 +10978,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="165"/>
+      <c r="A58" s="161"/>
       <c r="B58" s="34" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="153"/>
+      <c r="A59" s="162"/>
       <c r="B59" s="37" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="152" t="s">
+      <c r="A60" s="160" t="s">
         <v>305</v>
       </c>
       <c r="B60" s="47" t="s">
@@ -10998,37 +10998,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="165"/>
+      <c r="A61" s="161"/>
       <c r="B61" s="34" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="165"/>
+      <c r="A62" s="161"/>
       <c r="B62" s="48" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="165"/>
+      <c r="A63" s="161"/>
       <c r="B63" s="34" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="165"/>
+      <c r="A64" s="161"/>
       <c r="B64" s="34" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="153"/>
+      <c r="A65" s="162"/>
       <c r="B65" s="41" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="152" t="s">
+      <c r="A66" s="160" t="s">
         <v>312</v>
       </c>
       <c r="B66" s="47" t="s">
@@ -11036,37 +11036,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="165"/>
+      <c r="A67" s="161"/>
       <c r="B67" s="34" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="165"/>
+      <c r="A68" s="161"/>
       <c r="B68" s="34" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="165"/>
+      <c r="A69" s="161"/>
       <c r="B69" s="34" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="165"/>
+      <c r="A70" s="161"/>
       <c r="B70" s="34" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="153"/>
+      <c r="A71" s="162"/>
       <c r="B71" s="41" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="30" customFormat="1">
-      <c r="A72" s="152" t="s">
+      <c r="A72" s="160" t="s">
         <v>319</v>
       </c>
       <c r="B72" s="34" t="s">
@@ -11074,103 +11074,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="30" customFormat="1">
-      <c r="A73" s="165"/>
+      <c r="A73" s="161"/>
       <c r="B73" s="34" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="30" customFormat="1">
-      <c r="A74" s="165"/>
+      <c r="A74" s="161"/>
       <c r="B74" s="34" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="30" customFormat="1">
-      <c r="A75" s="165"/>
+      <c r="A75" s="161"/>
       <c r="B75" s="34" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="30" customFormat="1">
-      <c r="A76" s="165"/>
+      <c r="A76" s="161"/>
       <c r="B76" s="34" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="30" customFormat="1">
-      <c r="A77" s="165"/>
+      <c r="A77" s="161"/>
       <c r="B77" s="49" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="30" customFormat="1">
-      <c r="A78" s="165"/>
+      <c r="A78" s="161"/>
       <c r="B78" s="34" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="30" customFormat="1">
-      <c r="A79" s="165"/>
+      <c r="A79" s="161"/>
       <c r="B79" s="34" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="30" customFormat="1">
-      <c r="A80" s="165"/>
+      <c r="A80" s="161"/>
       <c r="B80" s="34" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="30" customFormat="1">
-      <c r="A81" s="165"/>
+      <c r="A81" s="161"/>
       <c r="B81" s="49" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="30" customFormat="1">
-      <c r="A82" s="165"/>
+      <c r="A82" s="161"/>
       <c r="B82" s="34" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="30" customFormat="1">
-      <c r="A83" s="165"/>
+      <c r="A83" s="161"/>
       <c r="B83" s="34" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="30" customFormat="1">
-      <c r="A84" s="165"/>
+      <c r="A84" s="161"/>
       <c r="B84" s="34" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="30" customFormat="1">
-      <c r="A85" s="165"/>
+      <c r="A85" s="161"/>
       <c r="B85" s="49" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="30" customFormat="1">
-      <c r="A86" s="165"/>
+      <c r="A86" s="161"/>
       <c r="B86" s="49" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="30" customFormat="1">
-      <c r="A87" s="165"/>
+      <c r="A87" s="161"/>
       <c r="B87" s="49" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="30" customFormat="1">
-      <c r="A88" s="153"/>
+      <c r="A88" s="162"/>
       <c r="B88" s="37" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="30" customFormat="1">
-      <c r="A89" s="152" t="s">
+      <c r="A89" s="160" t="s">
         <v>337</v>
       </c>
       <c r="B89" s="39" t="s">
@@ -11178,38 +11178,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="30" customFormat="1">
-      <c r="A90" s="165"/>
+      <c r="A90" s="161"/>
       <c r="B90" s="39" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="30" customFormat="1">
-      <c r="A91" s="165"/>
+      <c r="A91" s="161"/>
       <c r="B91" s="39" t="s">
         <v>340</v>
       </c>
       <c r="F91" s="56"/>
     </row>
     <row r="92" spans="1:6" s="30" customFormat="1">
-      <c r="A92" s="165"/>
+      <c r="A92" s="161"/>
       <c r="B92" s="57" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="30" customFormat="1">
-      <c r="A93" s="165"/>
+      <c r="A93" s="161"/>
       <c r="B93" s="39" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="30" customFormat="1">
-      <c r="A94" s="153"/>
+      <c r="A94" s="162"/>
       <c r="B94" s="37" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="30" customFormat="1">
-      <c r="A95" s="152" t="s">
+      <c r="A95" s="160" t="s">
         <v>344</v>
       </c>
       <c r="B95" s="50" t="s">
@@ -11217,43 +11217,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="30" customFormat="1">
-      <c r="A96" s="165"/>
+      <c r="A96" s="161"/>
       <c r="B96" s="51" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="30" customFormat="1">
-      <c r="A97" s="165"/>
+      <c r="A97" s="161"/>
       <c r="B97" s="51" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="30" customFormat="1">
-      <c r="A98" s="165"/>
+      <c r="A98" s="161"/>
       <c r="B98" s="51" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="30" customFormat="1">
-      <c r="A99" s="165"/>
+      <c r="A99" s="161"/>
       <c r="B99" s="51" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="30" customFormat="1">
-      <c r="A100" s="165"/>
+      <c r="A100" s="161"/>
       <c r="B100" s="51" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="30" customFormat="1">
-      <c r="A101" s="153"/>
+      <c r="A101" s="162"/>
       <c r="B101" s="45" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="30" customFormat="1">
-      <c r="A102" s="152" t="s">
+      <c r="A102" s="160" t="s">
         <v>352</v>
       </c>
       <c r="B102" s="33" t="s">
@@ -11261,7 +11261,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="30" customFormat="1">
-      <c r="A103" s="153"/>
+      <c r="A103" s="162"/>
       <c r="B103" s="37" t="s">
         <v>354</v>
       </c>
@@ -11279,10 +11279,10 @@
       <c r="B105" s="40"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="147" t="s">
+      <c r="A107" s="165" t="s">
         <v>357</v>
       </c>
-      <c r="B107" s="146"/>
+      <c r="B107" s="164"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="61"/>
@@ -11453,17 +11453,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="166" t="s">
+      <c r="A137" s="148" t="s">
         <v>386</v>
       </c>
-      <c r="B137" s="167"/>
+      <c r="B137" s="149"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="168"/>
-      <c r="B138" s="169"/>
+      <c r="A138" s="150"/>
+      <c r="B138" s="151"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="154" t="s">
+      <c r="A139" s="145" t="s">
         <v>387</v>
       </c>
       <c r="B139" s="63" t="s">
@@ -11471,31 +11471,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="155"/>
+      <c r="A140" s="146"/>
       <c r="B140" s="64" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="155"/>
+      <c r="A141" s="146"/>
       <c r="B141" s="64" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="155"/>
+      <c r="A142" s="146"/>
       <c r="B142" s="64" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="156"/>
+      <c r="A143" s="147"/>
       <c r="B143" s="66" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="154" t="s">
+      <c r="A144" s="145" t="s">
         <v>393</v>
       </c>
       <c r="B144" s="63" t="s">
@@ -11503,43 +11503,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="155"/>
+      <c r="A145" s="146"/>
       <c r="B145" s="64" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="155"/>
+      <c r="A146" s="146"/>
       <c r="B146" s="64" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="155"/>
+      <c r="A147" s="146"/>
       <c r="B147" s="64" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="155"/>
+      <c r="A148" s="146"/>
       <c r="B148" s="64" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="155"/>
+      <c r="A149" s="146"/>
       <c r="B149" s="64" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="156"/>
+      <c r="A150" s="147"/>
       <c r="B150" s="66" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="154" t="s">
+      <c r="A151" s="145" t="s">
         <v>401</v>
       </c>
       <c r="B151" s="63" t="s">
@@ -11547,187 +11547,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="155"/>
+      <c r="A152" s="146"/>
       <c r="B152" s="64" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="155"/>
+      <c r="A153" s="146"/>
       <c r="B153" s="64" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="155"/>
+      <c r="A154" s="146"/>
       <c r="B154" s="64" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="155"/>
+      <c r="A155" s="146"/>
       <c r="B155" s="64" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="155"/>
+      <c r="A156" s="146"/>
       <c r="B156" s="64" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="155"/>
+      <c r="A157" s="146"/>
       <c r="B157" s="64" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="155"/>
+      <c r="A158" s="146"/>
       <c r="B158" s="64" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="155"/>
+      <c r="A159" s="146"/>
       <c r="B159" s="64" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="155"/>
+      <c r="A160" s="146"/>
       <c r="B160" s="64" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="155"/>
+      <c r="A161" s="146"/>
       <c r="B161" s="64" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="155"/>
+      <c r="A162" s="146"/>
       <c r="B162" s="64" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="155"/>
+      <c r="A163" s="146"/>
       <c r="B163" s="64" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="155"/>
+      <c r="A164" s="146"/>
       <c r="B164" s="64" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="155"/>
+      <c r="A165" s="146"/>
       <c r="B165" s="64" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="155"/>
+      <c r="A166" s="146"/>
       <c r="B166" s="64" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="155"/>
+      <c r="A167" s="146"/>
       <c r="B167" s="64" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="155"/>
+      <c r="A168" s="146"/>
       <c r="B168" s="64" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="155"/>
+      <c r="A169" s="146"/>
       <c r="B169" s="64" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="155"/>
+      <c r="A170" s="146"/>
       <c r="B170" s="64" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="155"/>
+      <c r="A171" s="146"/>
       <c r="B171" s="64" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="155"/>
+      <c r="A172" s="146"/>
       <c r="B172" s="64" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="155"/>
+      <c r="A173" s="146"/>
       <c r="B173" s="64" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="155"/>
+      <c r="A174" s="146"/>
       <c r="B174" s="64" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="155"/>
+      <c r="A175" s="146"/>
       <c r="B175" s="64" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="155"/>
+      <c r="A176" s="146"/>
       <c r="B176" s="64" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="155"/>
+      <c r="A177" s="146"/>
       <c r="B177" s="64" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="155"/>
+      <c r="A178" s="146"/>
       <c r="B178" s="64" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="155"/>
+      <c r="A179" s="146"/>
       <c r="B179" s="64" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="155"/>
+      <c r="A180" s="146"/>
       <c r="B180" s="64" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="156"/>
+      <c r="A181" s="147"/>
       <c r="B181" s="66" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="154" t="s">
+      <c r="A182" s="145" t="s">
         <v>433</v>
       </c>
       <c r="B182" s="63" t="s">
@@ -11735,19 +11735,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="155"/>
+      <c r="A183" s="146"/>
       <c r="B183" s="64" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="156"/>
+      <c r="A184" s="147"/>
       <c r="B184" s="66" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="154" t="s">
+      <c r="A185" s="145" t="s">
         <v>437</v>
       </c>
       <c r="B185" s="63" t="s">
@@ -11755,25 +11755,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="155"/>
+      <c r="A186" s="146"/>
       <c r="B186" s="64" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="155"/>
+      <c r="A187" s="146"/>
       <c r="B187" s="64" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="156"/>
+      <c r="A188" s="147"/>
       <c r="B188" s="66" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="154" t="s">
+      <c r="A189" s="145" t="s">
         <v>442</v>
       </c>
       <c r="B189" s="63" t="s">
@@ -11781,13 +11781,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="156"/>
+      <c r="A190" s="147"/>
       <c r="B190" s="66" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="154" t="s">
+      <c r="A191" s="145" t="s">
         <v>445</v>
       </c>
       <c r="B191" s="63" t="s">
@@ -11795,49 +11795,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="155"/>
+      <c r="A192" s="146"/>
       <c r="B192" s="64" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="155"/>
+      <c r="A193" s="146"/>
       <c r="B193" s="64" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="155"/>
+      <c r="A194" s="146"/>
       <c r="B194" s="64" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="155"/>
+      <c r="A195" s="146"/>
       <c r="B195" s="64" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="155"/>
+      <c r="A196" s="146"/>
       <c r="B196" s="64" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="155"/>
+      <c r="A197" s="146"/>
       <c r="B197" s="64" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="156"/>
+      <c r="A198" s="147"/>
       <c r="B198" s="66" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="154" t="s">
+      <c r="A199" s="145" t="s">
         <v>454</v>
       </c>
       <c r="B199" s="63" t="s">
@@ -11845,13 +11845,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="156"/>
+      <c r="A200" s="147"/>
       <c r="B200" s="66" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="154" t="s">
+      <c r="A201" s="145" t="s">
         <v>457</v>
       </c>
       <c r="B201" s="63" t="s">
@@ -11859,19 +11859,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="155"/>
+      <c r="A202" s="146"/>
       <c r="B202" s="64" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="156"/>
+      <c r="A203" s="147"/>
       <c r="B203" s="66" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="154" t="s">
+      <c r="A204" s="145" t="s">
         <v>461</v>
       </c>
       <c r="B204" s="63" t="s">
@@ -11879,19 +11879,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="155"/>
+      <c r="A205" s="146"/>
       <c r="B205" s="64" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="155"/>
+      <c r="A206" s="146"/>
       <c r="B206" s="64" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="156"/>
+      <c r="A207" s="147"/>
       <c r="B207" s="66" t="s">
         <v>465</v>
       </c>
@@ -11905,7 +11905,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="154" t="s">
+      <c r="A209" s="145" t="s">
         <v>468</v>
       </c>
       <c r="B209" s="63" t="s">
@@ -11913,13 +11913,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="156"/>
+      <c r="A210" s="147"/>
       <c r="B210" s="66" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="154" t="s">
+      <c r="A211" s="145" t="s">
         <v>471</v>
       </c>
       <c r="B211" s="63" t="s">
@@ -11927,19 +11927,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="155"/>
+      <c r="A212" s="146"/>
       <c r="B212" s="64" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="156"/>
+      <c r="A213" s="147"/>
       <c r="B213" s="66" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="154" t="s">
+      <c r="A214" s="145" t="s">
         <v>475</v>
       </c>
       <c r="B214" s="63" t="s">
@@ -11947,19 +11947,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="155"/>
+      <c r="A215" s="146"/>
       <c r="B215" s="64" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="156"/>
+      <c r="A216" s="147"/>
       <c r="B216" s="66" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="154" t="s">
+      <c r="A217" s="145" t="s">
         <v>479</v>
       </c>
       <c r="B217" s="63" t="s">
@@ -11967,13 +11967,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="155"/>
+      <c r="A218" s="146"/>
       <c r="B218" s="64" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="156"/>
+      <c r="A219" s="147"/>
       <c r="B219" s="66" t="s">
         <v>482</v>
       </c>
@@ -11987,7 +11987,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="154" t="s">
+      <c r="A221" s="145" t="s">
         <v>485</v>
       </c>
       <c r="B221" s="63" t="s">
@@ -11995,13 +11995,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="156"/>
+      <c r="A222" s="147"/>
       <c r="B222" s="66" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="154" t="s">
+      <c r="A223" s="145" t="s">
         <v>488</v>
       </c>
       <c r="B223" s="63" t="s">
@@ -12009,31 +12009,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="155"/>
+      <c r="A224" s="146"/>
       <c r="B224" s="64" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="155"/>
+      <c r="A225" s="146"/>
       <c r="B225" s="64" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="155"/>
+      <c r="A226" s="146"/>
       <c r="B226" s="64" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="156"/>
+      <c r="A227" s="147"/>
       <c r="B227" s="66" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="154" t="s">
+      <c r="A228" s="145" t="s">
         <v>494</v>
       </c>
       <c r="B228" s="63" t="s">
@@ -12041,31 +12041,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="155"/>
+      <c r="A229" s="146"/>
       <c r="B229" s="64" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="155"/>
+      <c r="A230" s="146"/>
       <c r="B230" s="64" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="155"/>
+      <c r="A231" s="146"/>
       <c r="B231" s="64" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="155"/>
+      <c r="A232" s="146"/>
       <c r="B232" s="64" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="156"/>
+      <c r="A233" s="147"/>
       <c r="B233" s="66" t="s">
         <v>500</v>
       </c>
@@ -12079,16 +12079,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="148" t="s">
+      <c r="A236" s="166" t="s">
         <v>503</v>
       </c>
-      <c r="B236" s="149"/>
+      <c r="B236" s="167"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="147" t="s">
+      <c r="A239" s="165" t="s">
         <v>504</v>
       </c>
-      <c r="B239" s="146"/>
+      <c r="B239" s="164"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="61"/>
@@ -12187,10 +12187,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="150" t="s">
+      <c r="A257" s="168" t="s">
         <v>520</v>
       </c>
-      <c r="B257" s="151"/>
+      <c r="B257" s="169"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="61"/>
@@ -12367,10 +12367,10 @@
       </c>
     </row>
     <row r="288" spans="1:2" ht="23">
-      <c r="A288" s="157" t="s">
+      <c r="A288" s="152" t="s">
         <v>550</v>
       </c>
-      <c r="B288" s="158"/>
+      <c r="B288" s="153"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="69"/>
@@ -12561,14 +12561,22 @@
   </sheetData>
   <sheetProtection password="EC2B" sheet="1" objects="1"/>
   <mergeCells count="40">
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A236:B236"/>
+    <mergeCell ref="A239:B239"/>
+    <mergeCell ref="A257:B257"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A139:A143"/>
+    <mergeCell ref="A144:A150"/>
+    <mergeCell ref="A151:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A188"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="A191:A198"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A201:A203"/>
+    <mergeCell ref="A204:A207"/>
     <mergeCell ref="A288:B288"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -12585,22 +12593,14 @@
     <mergeCell ref="A72:A88"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A236:B236"/>
-    <mergeCell ref="A239:B239"/>
-    <mergeCell ref="A257:B257"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A139:A143"/>
-    <mergeCell ref="A144:A150"/>
-    <mergeCell ref="A151:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="A191:A198"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A201:A203"/>
-    <mergeCell ref="A204:A207"/>
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="36" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12620,10 +12620,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="182" t="s">
         <v>582</v>
       </c>
-      <c r="B1" s="171"/>
+      <c r="B1" s="183"/>
     </row>
     <row r="2" spans="1:2" s="28" customFormat="1" ht="15">
       <c r="A2" s="31" t="s">
@@ -12637,7 +12637,7 @@
       <c r="A3" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="B3" s="172" t="s">
+      <c r="B3" s="173" t="s">
         <v>1</v>
       </c>
     </row>
@@ -12645,25 +12645,25 @@
       <c r="A4" s="34" t="s">
         <v>585</v>
       </c>
-      <c r="B4" s="173"/>
+      <c r="B4" s="174"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="B5" s="173"/>
+      <c r="B5" s="174"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="B6" s="174"/>
+      <c r="B6" s="175"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="35" t="s">
         <v>245</v>
       </c>
-      <c r="B7" s="172" t="s">
+      <c r="B7" s="173" t="s">
         <v>586</v>
       </c>
     </row>
@@ -12671,25 +12671,25 @@
       <c r="A8" s="36" t="s">
         <v>246</v>
       </c>
-      <c r="B8" s="173"/>
+      <c r="B8" s="174"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="33" t="s">
         <v>353</v>
       </c>
-      <c r="B9" s="173"/>
+      <c r="B9" s="174"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="37" t="s">
         <v>354</v>
       </c>
-      <c r="B10" s="174"/>
+      <c r="B10" s="175"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="B11" s="172" t="s">
+      <c r="B11" s="173" t="s">
         <v>2</v>
       </c>
     </row>
@@ -12697,85 +12697,85 @@
       <c r="A12" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="B12" s="173"/>
+      <c r="B12" s="174"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="38" t="s">
         <v>250</v>
       </c>
-      <c r="B13" s="173"/>
+      <c r="B13" s="174"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="34" t="s">
         <v>251</v>
       </c>
-      <c r="B14" s="173"/>
+      <c r="B14" s="174"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="B15" s="173"/>
+      <c r="B15" s="174"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="B16" s="173"/>
+      <c r="B16" s="174"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="B17" s="173"/>
+      <c r="B17" s="174"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="34" t="s">
         <v>587</v>
       </c>
-      <c r="B18" s="173"/>
+      <c r="B18" s="174"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="B19" s="173"/>
+      <c r="B19" s="174"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="34" t="s">
         <v>588</v>
       </c>
-      <c r="B20" s="173"/>
+      <c r="B20" s="174"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="39" t="s">
         <v>589</v>
       </c>
-      <c r="B21" s="173"/>
+      <c r="B21" s="174"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="39" t="s">
         <v>260</v>
       </c>
-      <c r="B22" s="173"/>
+      <c r="B22" s="174"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="40" t="s">
         <v>242</v>
       </c>
-      <c r="B23" s="175"/>
+      <c r="B23" s="184"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="B24" s="176"/>
+      <c r="B24" s="185"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="33" t="s">
         <v>590</v>
       </c>
-      <c r="B25" s="172" t="s">
+      <c r="B25" s="173" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12783,61 +12783,61 @@
       <c r="A26" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="B26" s="173"/>
+      <c r="B26" s="174"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="34" t="s">
         <v>270</v>
       </c>
-      <c r="B27" s="173"/>
+      <c r="B27" s="174"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="B28" s="173"/>
+      <c r="B28" s="174"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="34" t="s">
         <v>272</v>
       </c>
-      <c r="B29" s="173"/>
+      <c r="B29" s="174"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="34" t="s">
         <v>591</v>
       </c>
-      <c r="B30" s="173"/>
+      <c r="B30" s="174"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="B31" s="173"/>
+      <c r="B31" s="174"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="34" t="s">
         <v>592</v>
       </c>
-      <c r="B32" s="173"/>
+      <c r="B32" s="174"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="34" t="s">
         <v>593</v>
       </c>
-      <c r="B33" s="173"/>
+      <c r="B33" s="174"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="41" t="s">
         <v>263</v>
       </c>
-      <c r="B34" s="174"/>
+      <c r="B34" s="175"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="42" t="s">
         <v>594</v>
       </c>
-      <c r="B35" s="172" t="s">
+      <c r="B35" s="173" t="s">
         <v>595</v>
       </c>
     </row>
@@ -12845,13 +12845,13 @@
       <c r="A36" s="41" t="s">
         <v>596</v>
       </c>
-      <c r="B36" s="174"/>
+      <c r="B36" s="175"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="34" t="s">
         <v>278</v>
       </c>
-      <c r="B37" s="172" t="s">
+      <c r="B37" s="173" t="s">
         <v>6</v>
       </c>
     </row>
@@ -12859,19 +12859,19 @@
       <c r="A38" s="39" t="s">
         <v>279</v>
       </c>
-      <c r="B38" s="173"/>
+      <c r="B38" s="174"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="B39" s="173"/>
+      <c r="B39" s="174"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="33" t="s">
         <v>597</v>
       </c>
-      <c r="B40" s="172" t="s">
+      <c r="B40" s="173" t="s">
         <v>598</v>
       </c>
     </row>
@@ -12879,37 +12879,37 @@
       <c r="A41" s="34" t="s">
         <v>599</v>
       </c>
-      <c r="B41" s="173"/>
+      <c r="B41" s="174"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="B42" s="173"/>
+      <c r="B42" s="174"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="34" t="s">
         <v>600</v>
       </c>
-      <c r="B43" s="173"/>
+      <c r="B43" s="174"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="34" t="s">
         <v>601</v>
       </c>
-      <c r="B44" s="173"/>
+      <c r="B44" s="174"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="34" t="s">
         <v>288</v>
       </c>
-      <c r="B45" s="173"/>
+      <c r="B45" s="174"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="37" t="s">
         <v>289</v>
       </c>
-      <c r="B46" s="174"/>
+      <c r="B46" s="175"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="43" t="s">
@@ -12923,7 +12923,7 @@
       <c r="A48" s="34" t="s">
         <v>292</v>
       </c>
-      <c r="B48" s="172" t="s">
+      <c r="B48" s="173" t="s">
         <v>602</v>
       </c>
     </row>
@@ -12931,13 +12931,13 @@
       <c r="A49" s="34" t="s">
         <v>293</v>
       </c>
-      <c r="B49" s="174"/>
+      <c r="B49" s="175"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="B50" s="172" t="s">
+      <c r="B50" s="173" t="s">
         <v>10</v>
       </c>
     </row>
@@ -12945,25 +12945,25 @@
       <c r="A51" s="34" t="s">
         <v>297</v>
       </c>
-      <c r="B51" s="173"/>
+      <c r="B51" s="174"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="34" t="s">
         <v>294</v>
       </c>
-      <c r="B52" s="173"/>
+      <c r="B52" s="174"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="34" t="s">
         <v>295</v>
       </c>
-      <c r="B53" s="173"/>
+      <c r="B53" s="174"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="41" t="s">
         <v>296</v>
       </c>
-      <c r="B54" s="174"/>
+      <c r="B54" s="175"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="43" t="s">
@@ -12977,7 +12977,7 @@
       <c r="A56" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="B56" s="172" t="s">
+      <c r="B56" s="173" t="s">
         <v>13</v>
       </c>
     </row>
@@ -12985,19 +12985,19 @@
       <c r="A57" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="B57" s="173"/>
+      <c r="B57" s="174"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="37" t="s">
         <v>304</v>
       </c>
-      <c r="B58" s="174"/>
+      <c r="B58" s="175"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="34" t="s">
         <v>338</v>
       </c>
-      <c r="B59" s="180" t="s">
+      <c r="B59" s="176" t="s">
         <v>12</v>
       </c>
     </row>
@@ -13005,37 +13005,37 @@
       <c r="A60" s="34" t="s">
         <v>342</v>
       </c>
-      <c r="B60" s="181"/>
+      <c r="B60" s="177"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="34" t="s">
         <v>339</v>
       </c>
-      <c r="B61" s="181"/>
+      <c r="B61" s="177"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="B62" s="181"/>
+      <c r="B62" s="177"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="34" t="s">
         <v>343</v>
       </c>
-      <c r="B63" s="181"/>
+      <c r="B63" s="177"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="45" t="s">
         <v>341</v>
       </c>
-      <c r="B64" s="182"/>
+      <c r="B64" s="178"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="34" t="s">
         <v>605</v>
       </c>
-      <c r="B65" s="183" t="s">
+      <c r="B65" s="179" t="s">
         <v>606</v>
       </c>
     </row>
@@ -13043,26 +13043,26 @@
       <c r="A66" s="34" t="s">
         <v>281</v>
       </c>
-      <c r="B66" s="184"/>
+      <c r="B66" s="180"/>
       <c r="E66" s="46"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="39" t="s">
         <v>300</v>
       </c>
-      <c r="B67" s="184"/>
+      <c r="B67" s="180"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="B68" s="185"/>
+      <c r="B68" s="181"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="47" t="s">
         <v>306</v>
       </c>
-      <c r="B69" s="180" t="s">
+      <c r="B69" s="176" t="s">
         <v>15</v>
       </c>
     </row>
@@ -13070,37 +13070,37 @@
       <c r="A70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="B70" s="181"/>
+      <c r="B70" s="177"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="48" t="s">
         <v>308</v>
       </c>
-      <c r="B71" s="181"/>
+      <c r="B71" s="177"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="34" t="s">
         <v>309</v>
       </c>
-      <c r="B72" s="181"/>
+      <c r="B72" s="177"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="B73" s="181"/>
+      <c r="B73" s="177"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="34" t="s">
         <v>311</v>
       </c>
-      <c r="B74" s="182"/>
+      <c r="B74" s="178"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="47" t="s">
         <v>313</v>
       </c>
-      <c r="B75" s="180" t="s">
+      <c r="B75" s="176" t="s">
         <v>16</v>
       </c>
     </row>
@@ -13108,139 +13108,139 @@
       <c r="A76" s="34" t="s">
         <v>314</v>
       </c>
-      <c r="B76" s="181"/>
+      <c r="B76" s="177"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="34" t="s">
         <v>315</v>
       </c>
-      <c r="B77" s="181"/>
+      <c r="B77" s="177"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="34" t="s">
         <v>316</v>
       </c>
-      <c r="B78" s="181"/>
+      <c r="B78" s="177"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="B79" s="181"/>
+      <c r="B79" s="177"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="B80" s="181"/>
+      <c r="B80" s="177"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="B81" s="181"/>
+      <c r="B81" s="177"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="B82" s="181"/>
+      <c r="B82" s="177"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="34" t="s">
         <v>322</v>
       </c>
-      <c r="B83" s="181"/>
+      <c r="B83" s="177"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="34" t="s">
         <v>323</v>
       </c>
-      <c r="B84" s="181"/>
+      <c r="B84" s="177"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="34" t="s">
         <v>324</v>
       </c>
-      <c r="B85" s="181"/>
+      <c r="B85" s="177"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="49" t="s">
         <v>325</v>
       </c>
-      <c r="B86" s="181"/>
+      <c r="B86" s="177"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="B87" s="181"/>
+      <c r="B87" s="177"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="34" t="s">
         <v>327</v>
       </c>
-      <c r="B88" s="181"/>
+      <c r="B88" s="177"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="34" t="s">
         <v>328</v>
       </c>
-      <c r="B89" s="181"/>
+      <c r="B89" s="177"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="B90" s="181"/>
+      <c r="B90" s="177"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="B91" s="181"/>
+      <c r="B91" s="177"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="34" t="s">
         <v>331</v>
       </c>
-      <c r="B92" s="181"/>
+      <c r="B92" s="177"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="34" t="s">
         <v>332</v>
       </c>
-      <c r="B93" s="181"/>
+      <c r="B93" s="177"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="49" t="s">
         <v>333</v>
       </c>
-      <c r="B94" s="181"/>
+      <c r="B94" s="177"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="49" t="s">
         <v>334</v>
       </c>
-      <c r="B95" s="181"/>
+      <c r="B95" s="177"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="49" t="s">
         <v>335</v>
       </c>
-      <c r="B96" s="181"/>
+      <c r="B96" s="177"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="34" t="s">
         <v>336</v>
       </c>
-      <c r="B97" s="181"/>
+      <c r="B97" s="177"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="50" t="s">
         <v>345</v>
       </c>
-      <c r="B98" s="177" t="s">
+      <c r="B98" s="170" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13248,37 +13248,37 @@
       <c r="A99" s="51" t="s">
         <v>346</v>
       </c>
-      <c r="B99" s="178"/>
+      <c r="B99" s="171"/>
     </row>
     <row r="100" spans="1:2" s="29" customFormat="1">
       <c r="A100" s="51" t="s">
         <v>347</v>
       </c>
-      <c r="B100" s="178"/>
+      <c r="B100" s="171"/>
     </row>
     <row r="101" spans="1:2" s="29" customFormat="1">
       <c r="A101" s="51" t="s">
         <v>348</v>
       </c>
-      <c r="B101" s="178"/>
+      <c r="B101" s="171"/>
     </row>
     <row r="102" spans="1:2" s="29" customFormat="1">
       <c r="A102" s="51" t="s">
         <v>349</v>
       </c>
-      <c r="B102" s="178"/>
+      <c r="B102" s="171"/>
     </row>
     <row r="103" spans="1:2" s="29" customFormat="1">
       <c r="A103" s="51" t="s">
         <v>350</v>
       </c>
-      <c r="B103" s="178"/>
+      <c r="B103" s="171"/>
     </row>
     <row r="104" spans="1:2" s="29" customFormat="1">
       <c r="A104" s="45" t="s">
         <v>351</v>
       </c>
-      <c r="B104" s="179"/>
+      <c r="B104" s="172"/>
     </row>
     <row r="105" spans="1:2" s="29" customFormat="1">
       <c r="A105" s="52" t="s">
@@ -13290,22 +13290,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="36" type="noConversion"/>
   <hyperlinks>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetInfoRegist.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetInfoRegist.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\tamsDoubleBranch\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="资产要素登记" sheetId="1" r:id="rId1"/>
@@ -18,7 +13,7 @@
     <sheet name="各类资产应填要素列说明" sheetId="4" r:id="rId4"/>
     <sheet name="国家或区域填写规则" sheetId="5" r:id="rId5"/>
     <sheet name="币种填写规则" sheetId="6" r:id="rId6"/>
-    <sheet name="版本号1.0.15" sheetId="7" r:id="rId7"/>
+    <sheet name="版本号2.0.0" sheetId="7" r:id="rId7"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId8"/>
@@ -5695,9 +5690,6 @@
     <t>3.对于“其他非标准化债权投资”二级分类的资产，新增“担保情况说明”要素；</t>
   </si>
   <si>
-    <t>4.对于包括信托贷款、委托贷款、信贷资产转让、委托债权、应收账款、收/受益权、带回购条款的股权性融资、债权融资类产品在内的非标准化债权类资产新增登记要素“法定到期日”“份额面值”“计息类型”“规则付息标识”“利息分布方式”“是否有浮动因子”“结构档次”“还本方式”“分期还本条款标识”“基础资产类型”“超额收益分配比例”“增信机构代码”“增信机构名称”“含权类型”“行权方式”“固定行权日”“首次行权日期”“行权周期”“行权价格”“永续条款类型”“递延利息条款类型”“递延利息是否计息”“首次重定价日期”“重定价周期”“部分赎回标识”“部分赎回比例”；</t>
-  </si>
-  <si>
     <t>1.0.16</t>
   </si>
   <si>
@@ -6440,6 +6432,10 @@
   </si>
   <si>
     <t>6、申报登记要素“产品资产配置方式”值域变更</t>
+  </si>
+  <si>
+    <t>4.对于包括信托贷款、委托贷款、信贷资产转让、委托债权、应收账款、收/受益权、带回购条款的股权性融资、债权融资类产品在内的非标准化债权类资产新增登记要素“法定到期日”“份额面值”“计息类型”“规则付息标识”“利息分布方式”“是否有浮动因子”“结构档次”“还本方式”“分期还本条款标识”“基础资产类型”“超额收益分配比例”“增信机构代码”“增信机构名称”“含权类型”“行权方式”“固定行权日”“首次行权日期”“行权周期”“行权价格”“永续条款类型”“递延利息条款类型”“递延利息是否计息”“首次重定价日期”“重定价周期”“部分赎回标识”“部分赎回比例”；</t>
+    <phoneticPr fontId="36" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -7637,58 +7633,28 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -7699,6 +7665,63 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7708,6 +7731,33 @@
     <xf numFmtId="49" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7720,58 +7770,25 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="5" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -7783,15 +7800,6 @@
     <xf numFmtId="49" fontId="8" fillId="5" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7809,18 +7817,6 @@
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8167,533 +8163,533 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:JM11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="44.453125" style="75" customWidth="1"/>
-    <col min="2" max="2" width="15.36328125" style="76"/>
-    <col min="3" max="3" width="22.7265625" style="76" customWidth="1"/>
-    <col min="4" max="4" width="18.453125" style="76" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" style="77" customWidth="1"/>
-    <col min="6" max="6" width="14.08984375" style="75"/>
-    <col min="7" max="7" width="10.7265625" style="78" customWidth="1"/>
-    <col min="8" max="8" width="10.36328125" style="79" customWidth="1"/>
-    <col min="9" max="9" width="9.453125" style="79"/>
-    <col min="10" max="10" width="11.26953125" style="80" customWidth="1"/>
-    <col min="11" max="11" width="11.6328125" style="76" customWidth="1"/>
-    <col min="12" max="12" width="19.7265625" style="76"/>
-    <col min="13" max="13" width="25.26953125" style="76"/>
-    <col min="14" max="14" width="20.7265625" style="77"/>
-    <col min="15" max="15" width="12.7265625" style="81" customWidth="1"/>
-    <col min="16" max="17" width="12.26953125" style="82" customWidth="1"/>
-    <col min="18" max="18" width="15.36328125" style="82"/>
-    <col min="19" max="19" width="10.90625" style="82"/>
-    <col min="20" max="20" width="30.90625" style="82"/>
-    <col min="21" max="22" width="35.36328125" style="82"/>
-    <col min="23" max="23" width="22.26953125" style="82" customWidth="1"/>
-    <col min="24" max="24" width="22.36328125" style="82" customWidth="1"/>
-    <col min="25" max="25" width="19.90625" style="82" customWidth="1"/>
-    <col min="26" max="26" width="9.453125" style="75"/>
-    <col min="27" max="27" width="9.453125" style="76"/>
+    <col min="1" max="1" width="44.5" style="75" customWidth="1"/>
+    <col min="2" max="2" width="15.375" style="76"/>
+    <col min="3" max="3" width="22.75" style="76" customWidth="1"/>
+    <col min="4" max="4" width="18.5" style="76" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="77" customWidth="1"/>
+    <col min="6" max="6" width="14.125" style="75"/>
+    <col min="7" max="7" width="10.75" style="78" customWidth="1"/>
+    <col min="8" max="8" width="10.375" style="79" customWidth="1"/>
+    <col min="9" max="9" width="9.5" style="79"/>
+    <col min="10" max="10" width="11.25" style="80" customWidth="1"/>
+    <col min="11" max="11" width="11.625" style="76" customWidth="1"/>
+    <col min="12" max="12" width="19.75" style="76"/>
+    <col min="13" max="13" width="25.25" style="76"/>
+    <col min="14" max="14" width="20.75" style="77"/>
+    <col min="15" max="15" width="12.75" style="81" customWidth="1"/>
+    <col min="16" max="17" width="12.25" style="82" customWidth="1"/>
+    <col min="18" max="18" width="15.375" style="82"/>
+    <col min="19" max="19" width="10.875" style="82"/>
+    <col min="20" max="20" width="30.875" style="82"/>
+    <col min="21" max="22" width="35.375" style="82"/>
+    <col min="23" max="23" width="22.25" style="82" customWidth="1"/>
+    <col min="24" max="24" width="22.375" style="82" customWidth="1"/>
+    <col min="25" max="25" width="19.875" style="82" customWidth="1"/>
+    <col min="26" max="26" width="9.5" style="75"/>
+    <col min="27" max="27" width="9.5" style="76"/>
     <col min="28" max="28" width="9" style="76"/>
-    <col min="29" max="29" width="22.90625" style="76" customWidth="1"/>
-    <col min="30" max="30" width="11.6328125" style="80" customWidth="1"/>
-    <col min="31" max="31" width="11.6328125" style="76" customWidth="1"/>
-    <col min="32" max="32" width="14.08984375" style="76"/>
+    <col min="29" max="29" width="22.875" style="76" customWidth="1"/>
+    <col min="30" max="30" width="11.625" style="80" customWidth="1"/>
+    <col min="31" max="31" width="11.625" style="76" customWidth="1"/>
+    <col min="32" max="32" width="14.125" style="76"/>
     <col min="33" max="33" width="56" style="83"/>
-    <col min="34" max="34" width="18.08984375" style="75" customWidth="1"/>
-    <col min="35" max="35" width="19.7265625" style="76"/>
-    <col min="36" max="36" width="13.6328125" style="76" customWidth="1"/>
-    <col min="37" max="37" width="15.36328125" style="78" customWidth="1"/>
-    <col min="38" max="38" width="15.36328125" style="79" customWidth="1"/>
-    <col min="39" max="39" width="9.08984375" style="76" customWidth="1"/>
-    <col min="40" max="40" width="9.36328125" style="76" customWidth="1"/>
-    <col min="41" max="41" width="11.453125" style="76" customWidth="1"/>
-    <col min="42" max="42" width="19.90625" style="76" customWidth="1"/>
-    <col min="43" max="45" width="20.08984375" style="80"/>
-    <col min="46" max="47" width="21.90625" style="84" customWidth="1"/>
-    <col min="48" max="48" width="18.90625" style="76" customWidth="1"/>
-    <col min="49" max="49" width="11.90625" style="76" customWidth="1"/>
-    <col min="50" max="51" width="24.26953125" style="76" customWidth="1"/>
-    <col min="52" max="52" width="15.453125" style="80" customWidth="1"/>
-    <col min="53" max="55" width="13.26953125" style="80" customWidth="1"/>
-    <col min="56" max="57" width="19.453125" style="80" customWidth="1"/>
-    <col min="58" max="58" width="23.90625" style="80" customWidth="1"/>
+    <col min="34" max="34" width="18.125" style="75" customWidth="1"/>
+    <col min="35" max="35" width="19.75" style="76"/>
+    <col min="36" max="36" width="13.625" style="76" customWidth="1"/>
+    <col min="37" max="37" width="15.375" style="78" customWidth="1"/>
+    <col min="38" max="38" width="15.375" style="79" customWidth="1"/>
+    <col min="39" max="39" width="9.125" style="76" customWidth="1"/>
+    <col min="40" max="40" width="9.375" style="76" customWidth="1"/>
+    <col min="41" max="41" width="11.5" style="76" customWidth="1"/>
+    <col min="42" max="42" width="19.875" style="76" customWidth="1"/>
+    <col min="43" max="45" width="20.125" style="80"/>
+    <col min="46" max="47" width="21.875" style="84" customWidth="1"/>
+    <col min="48" max="48" width="18.875" style="76" customWidth="1"/>
+    <col min="49" max="49" width="11.875" style="76" customWidth="1"/>
+    <col min="50" max="51" width="24.25" style="76" customWidth="1"/>
+    <col min="52" max="52" width="15.5" style="80" customWidth="1"/>
+    <col min="53" max="55" width="13.25" style="80" customWidth="1"/>
+    <col min="56" max="57" width="19.5" style="80" customWidth="1"/>
+    <col min="58" max="58" width="23.875" style="80" customWidth="1"/>
     <col min="59" max="59" width="9" style="76"/>
-    <col min="60" max="60" width="22.7265625" style="76" customWidth="1"/>
-    <col min="61" max="61" width="36.08984375" style="76" customWidth="1"/>
-    <col min="62" max="62" width="28.6328125" style="76"/>
-    <col min="63" max="64" width="33.08984375" style="76"/>
-    <col min="65" max="65" width="12.36328125" style="76" customWidth="1"/>
-    <col min="66" max="66" width="22.90625" style="76" customWidth="1"/>
-    <col min="67" max="67" width="35.36328125" style="76"/>
-    <col min="68" max="68" width="25.26953125" style="76"/>
-    <col min="69" max="69" width="29.6328125" style="76"/>
-    <col min="70" max="71" width="15.36328125" style="76" customWidth="1"/>
-    <col min="72" max="72" width="20.90625" style="76" customWidth="1"/>
-    <col min="73" max="73" width="15.36328125" style="76" customWidth="1"/>
-    <col min="74" max="74" width="20.7265625" style="76" customWidth="1"/>
-    <col min="75" max="75" width="16.6328125" style="76" customWidth="1"/>
-    <col min="76" max="76" width="15.7265625" style="76" customWidth="1"/>
-    <col min="77" max="77" width="19.36328125" style="76" customWidth="1"/>
-    <col min="78" max="79" width="14.453125" style="76" customWidth="1"/>
-    <col min="80" max="85" width="16.6328125" style="76" customWidth="1"/>
-    <col min="86" max="90" width="19.453125" style="76" customWidth="1"/>
-    <col min="91" max="91" width="19.453125" style="85" customWidth="1"/>
+    <col min="60" max="60" width="22.75" style="76" customWidth="1"/>
+    <col min="61" max="61" width="36.125" style="76" customWidth="1"/>
+    <col min="62" max="62" width="28.625" style="76"/>
+    <col min="63" max="64" width="33.125" style="76"/>
+    <col min="65" max="65" width="12.375" style="76" customWidth="1"/>
+    <col min="66" max="66" width="22.875" style="76" customWidth="1"/>
+    <col min="67" max="67" width="35.375" style="76"/>
+    <col min="68" max="68" width="25.25" style="76"/>
+    <col min="69" max="69" width="29.625" style="76"/>
+    <col min="70" max="71" width="15.375" style="76" customWidth="1"/>
+    <col min="72" max="72" width="20.875" style="76" customWidth="1"/>
+    <col min="73" max="73" width="15.375" style="76" customWidth="1"/>
+    <col min="74" max="74" width="20.75" style="76" customWidth="1"/>
+    <col min="75" max="75" width="16.625" style="76" customWidth="1"/>
+    <col min="76" max="76" width="15.75" style="76" customWidth="1"/>
+    <col min="77" max="77" width="19.375" style="76" customWidth="1"/>
+    <col min="78" max="79" width="14.5" style="76" customWidth="1"/>
+    <col min="80" max="85" width="16.625" style="76" customWidth="1"/>
+    <col min="86" max="90" width="19.5" style="76" customWidth="1"/>
+    <col min="91" max="91" width="19.5" style="85" customWidth="1"/>
     <col min="92" max="92" width="14" style="76" customWidth="1"/>
-    <col min="93" max="93" width="14.36328125" style="76" customWidth="1"/>
+    <col min="93" max="93" width="14.375" style="76" customWidth="1"/>
     <col min="94" max="97" width="19" style="76" customWidth="1"/>
-    <col min="98" max="98" width="14.90625" style="80" customWidth="1"/>
-    <col min="99" max="99" width="19.7265625" style="77"/>
-    <col min="100" max="100" width="17.6328125" style="76" customWidth="1"/>
-    <col min="101" max="101" width="19.7265625" style="76"/>
-    <col min="102" max="102" width="16.36328125" style="76" customWidth="1"/>
-    <col min="103" max="103" width="13.453125" style="84" customWidth="1"/>
-    <col min="104" max="104" width="14.6328125" style="78" customWidth="1"/>
+    <col min="98" max="98" width="14.875" style="80" customWidth="1"/>
+    <col min="99" max="99" width="19.75" style="77"/>
+    <col min="100" max="100" width="17.625" style="76" customWidth="1"/>
+    <col min="101" max="101" width="19.75" style="76"/>
+    <col min="102" max="102" width="16.375" style="76" customWidth="1"/>
+    <col min="103" max="103" width="13.5" style="84" customWidth="1"/>
+    <col min="104" max="104" width="14.625" style="78" customWidth="1"/>
     <col min="105" max="105" width="22" style="124"/>
     <col min="106" max="106" width="22" style="84"/>
     <col min="107" max="107" width="22" style="84" customWidth="1"/>
     <col min="108" max="108" width="22" style="79" customWidth="1"/>
-    <col min="109" max="109" width="13.90625" style="79" customWidth="1"/>
-    <col min="110" max="110" width="16.453125" style="76" customWidth="1"/>
-    <col min="111" max="111" width="16.08984375" style="80" customWidth="1"/>
-    <col min="112" max="112" width="16.90625" style="75" customWidth="1"/>
-    <col min="113" max="113" width="17.90625" style="76"/>
-    <col min="114" max="114" width="9.7265625" style="76"/>
-    <col min="115" max="117" width="17.90625" style="76" customWidth="1"/>
-    <col min="118" max="118" width="26.453125" style="76"/>
-    <col min="119" max="120" width="30.90625" style="76"/>
-    <col min="121" max="122" width="26.453125" style="76" customWidth="1"/>
+    <col min="109" max="109" width="13.875" style="79" customWidth="1"/>
+    <col min="110" max="110" width="16.5" style="76" customWidth="1"/>
+    <col min="111" max="111" width="16.125" style="80" customWidth="1"/>
+    <col min="112" max="112" width="16.875" style="75" customWidth="1"/>
+    <col min="113" max="113" width="17.875" style="76"/>
+    <col min="114" max="114" width="9.75" style="76"/>
+    <col min="115" max="117" width="17.875" style="76" customWidth="1"/>
+    <col min="118" max="118" width="26.5" style="76"/>
+    <col min="119" max="120" width="30.875" style="76"/>
+    <col min="121" max="122" width="26.5" style="76" customWidth="1"/>
     <col min="123" max="123" width="9" style="75"/>
-    <col min="124" max="124" width="13.90625" style="78"/>
-    <col min="125" max="126" width="11.453125" style="76" customWidth="1"/>
-    <col min="127" max="127" width="19.36328125" style="75" customWidth="1"/>
-    <col min="128" max="128" width="10.6328125" style="76" customWidth="1"/>
-    <col min="129" max="129" width="10.08984375" style="82" customWidth="1"/>
+    <col min="124" max="124" width="13.875" style="78"/>
+    <col min="125" max="126" width="11.5" style="76" customWidth="1"/>
+    <col min="127" max="127" width="19.375" style="75" customWidth="1"/>
+    <col min="128" max="128" width="10.625" style="76" customWidth="1"/>
+    <col min="129" max="129" width="10.125" style="82" customWidth="1"/>
     <col min="130" max="130" width="11" style="82" customWidth="1"/>
-    <col min="131" max="131" width="21.453125" style="82" customWidth="1"/>
+    <col min="131" max="131" width="21.5" style="82" customWidth="1"/>
     <col min="132" max="133" width="10" style="82" customWidth="1"/>
-    <col min="134" max="134" width="11.90625" style="86" customWidth="1"/>
-    <col min="135" max="135" width="21.7265625" style="82" customWidth="1"/>
-    <col min="136" max="136" width="14.36328125" style="82" customWidth="1"/>
-    <col min="137" max="137" width="11.90625" style="87" customWidth="1"/>
-    <col min="138" max="138" width="21.08984375" style="86" customWidth="1"/>
-    <col min="139" max="139" width="14.6328125" style="82" customWidth="1"/>
-    <col min="140" max="140" width="28.453125" style="76" customWidth="1"/>
-    <col min="141" max="141" width="16.90625" style="75" customWidth="1"/>
-    <col min="142" max="143" width="9.453125" style="76"/>
+    <col min="134" max="134" width="11.875" style="86" customWidth="1"/>
+    <col min="135" max="135" width="21.75" style="82" customWidth="1"/>
+    <col min="136" max="136" width="14.375" style="82" customWidth="1"/>
+    <col min="137" max="137" width="11.875" style="87" customWidth="1"/>
+    <col min="138" max="138" width="21.125" style="86" customWidth="1"/>
+    <col min="139" max="139" width="14.625" style="82" customWidth="1"/>
+    <col min="140" max="140" width="28.5" style="76" customWidth="1"/>
+    <col min="141" max="141" width="16.875" style="75" customWidth="1"/>
+    <col min="142" max="143" width="9.5" style="76"/>
     <col min="144" max="144" width="9" style="76"/>
-    <col min="145" max="145" width="12.6328125" style="80" customWidth="1"/>
-    <col min="146" max="146" width="11.36328125" style="77" customWidth="1"/>
-    <col min="147" max="147" width="16.26953125" style="75" customWidth="1"/>
-    <col min="148" max="148" width="16.08984375" style="76" customWidth="1"/>
-    <col min="149" max="149" width="15.90625" style="76" customWidth="1"/>
-    <col min="150" max="150" width="11.26953125" style="76" customWidth="1"/>
-    <col min="151" max="151" width="23.7265625" style="77"/>
-    <col min="152" max="152" width="16.26953125" style="75" customWidth="1"/>
-    <col min="153" max="155" width="10.26953125" style="76" customWidth="1"/>
-    <col min="156" max="156" width="10.90625" style="80" customWidth="1"/>
-    <col min="157" max="157" width="20.7265625" style="84" customWidth="1"/>
+    <col min="145" max="145" width="12.625" style="80" customWidth="1"/>
+    <col min="146" max="146" width="11.375" style="77" customWidth="1"/>
+    <col min="147" max="147" width="16.25" style="75" customWidth="1"/>
+    <col min="148" max="148" width="16.125" style="76" customWidth="1"/>
+    <col min="149" max="149" width="15.875" style="76" customWidth="1"/>
+    <col min="150" max="150" width="11.25" style="76" customWidth="1"/>
+    <col min="151" max="151" width="23.75" style="77"/>
+    <col min="152" max="152" width="16.25" style="75" customWidth="1"/>
+    <col min="153" max="155" width="10.25" style="76" customWidth="1"/>
+    <col min="156" max="156" width="10.875" style="80" customWidth="1"/>
+    <col min="157" max="157" width="20.75" style="84" customWidth="1"/>
     <col min="158" max="159" width="28" style="80"/>
-    <col min="160" max="160" width="26.453125" style="76" customWidth="1"/>
-    <col min="161" max="161" width="29.08984375" style="76" customWidth="1"/>
-    <col min="162" max="162" width="14.7265625" style="76" customWidth="1"/>
+    <col min="160" max="160" width="26.5" style="76" customWidth="1"/>
+    <col min="161" max="161" width="29.125" style="76" customWidth="1"/>
+    <col min="162" max="162" width="14.75" style="76" customWidth="1"/>
     <col min="163" max="163" width="15" style="76" customWidth="1"/>
-    <col min="164" max="164" width="22.90625" style="80" customWidth="1"/>
-    <col min="165" max="165" width="23.6328125" style="80" customWidth="1"/>
-    <col min="166" max="166" width="21.6328125" style="78" customWidth="1"/>
-    <col min="167" max="167" width="24.7265625" style="78" customWidth="1"/>
-    <col min="168" max="168" width="12.26953125" style="121" customWidth="1"/>
-    <col min="169" max="169" width="15.26953125" style="82" customWidth="1"/>
-    <col min="170" max="170" width="28.36328125" style="82" customWidth="1"/>
-    <col min="171" max="171" width="25.26953125" style="82" customWidth="1"/>
-    <col min="172" max="172" width="17.7265625" style="82" customWidth="1"/>
-    <col min="173" max="173" width="9.7265625" style="82" customWidth="1"/>
+    <col min="164" max="164" width="22.875" style="80" customWidth="1"/>
+    <col min="165" max="165" width="23.625" style="80" customWidth="1"/>
+    <col min="166" max="166" width="21.625" style="78" customWidth="1"/>
+    <col min="167" max="167" width="24.75" style="78" customWidth="1"/>
+    <col min="168" max="168" width="12.25" style="121" customWidth="1"/>
+    <col min="169" max="169" width="15.25" style="82" customWidth="1"/>
+    <col min="170" max="170" width="28.375" style="82" customWidth="1"/>
+    <col min="171" max="171" width="25.25" style="82" customWidth="1"/>
+    <col min="172" max="172" width="17.75" style="82" customWidth="1"/>
+    <col min="173" max="173" width="9.75" style="82" customWidth="1"/>
     <col min="174" max="174" width="11" style="82" customWidth="1"/>
-    <col min="175" max="175" width="19.36328125" style="88"/>
-    <col min="176" max="176" width="17.453125" style="82" customWidth="1"/>
-    <col min="177" max="177" width="17.6328125" style="82" customWidth="1"/>
-    <col min="178" max="178" width="17.453125" style="82" customWidth="1"/>
-    <col min="179" max="179" width="18.453125" style="82" customWidth="1"/>
-    <col min="180" max="180" width="18.26953125" style="82" customWidth="1"/>
-    <col min="181" max="181" width="15.36328125" style="82"/>
-    <col min="182" max="182" width="17.453125" style="82" customWidth="1"/>
-    <col min="183" max="183" width="17.08984375" style="87" customWidth="1"/>
-    <col min="184" max="184" width="16.453125" style="87" customWidth="1"/>
-    <col min="185" max="185" width="12.7265625" style="82" customWidth="1"/>
-    <col min="186" max="186" width="12.90625" style="82" customWidth="1"/>
-    <col min="187" max="188" width="14.26953125" style="87" customWidth="1"/>
+    <col min="175" max="175" width="19.375" style="88"/>
+    <col min="176" max="176" width="17.5" style="82" customWidth="1"/>
+    <col min="177" max="177" width="17.625" style="82" customWidth="1"/>
+    <col min="178" max="178" width="17.5" style="82" customWidth="1"/>
+    <col min="179" max="179" width="18.5" style="82" customWidth="1"/>
+    <col min="180" max="180" width="18.25" style="82" customWidth="1"/>
+    <col min="181" max="181" width="15.375" style="82"/>
+    <col min="182" max="182" width="17.5" style="82" customWidth="1"/>
+    <col min="183" max="183" width="17.125" style="87" customWidth="1"/>
+    <col min="184" max="184" width="16.5" style="87" customWidth="1"/>
+    <col min="185" max="185" width="12.75" style="82" customWidth="1"/>
+    <col min="186" max="186" width="12.875" style="82" customWidth="1"/>
+    <col min="187" max="188" width="14.25" style="87" customWidth="1"/>
     <col min="189" max="189" width="21" style="87"/>
-    <col min="190" max="190" width="25.453125" style="87"/>
-    <col min="191" max="191" width="17.90625" style="87"/>
-    <col min="192" max="192" width="16.26953125" style="75" customWidth="1"/>
+    <col min="190" max="190" width="25.5" style="87"/>
+    <col min="191" max="191" width="17.875" style="87"/>
+    <col min="192" max="192" width="16.25" style="75" customWidth="1"/>
     <col min="193" max="193" width="9" style="76"/>
-    <col min="194" max="194" width="12.453125" style="84" customWidth="1"/>
+    <col min="194" max="194" width="12.5" style="84" customWidth="1"/>
     <col min="195" max="195" width="11" style="78" customWidth="1"/>
-    <col min="196" max="196" width="13.08984375" style="89" customWidth="1"/>
+    <col min="196" max="196" width="13.125" style="89" customWidth="1"/>
     <col min="197" max="197" width="20" style="76" customWidth="1"/>
-    <col min="198" max="198" width="15.36328125" style="76"/>
-    <col min="199" max="199" width="17.453125" style="76"/>
-    <col min="200" max="200" width="11.6328125" style="78" customWidth="1"/>
-    <col min="201" max="202" width="11.6328125" style="76" customWidth="1"/>
-    <col min="203" max="203" width="17.6328125" style="76"/>
-    <col min="204" max="204" width="19.7265625" style="76"/>
-    <col min="205" max="205" width="23.26953125" style="80"/>
-    <col min="206" max="206" width="23.26953125" style="90"/>
-    <col min="207" max="207" width="11.6328125" style="76" customWidth="1"/>
-    <col min="208" max="208" width="35.36328125" style="76"/>
-    <col min="209" max="209" width="38.453125" style="76"/>
-    <col min="210" max="210" width="28.6328125" style="76"/>
-    <col min="211" max="212" width="33.08984375" style="76"/>
-    <col min="213" max="213" width="11.6328125" style="76" customWidth="1"/>
-    <col min="214" max="214" width="16.36328125" style="76"/>
-    <col min="215" max="215" width="19.7265625" style="76"/>
-    <col min="216" max="216" width="35.36328125" style="76"/>
-    <col min="217" max="217" width="25.26953125" style="76"/>
-    <col min="218" max="218" width="29.6328125" style="76"/>
-    <col min="219" max="224" width="18.6328125" style="76"/>
-    <col min="225" max="225" width="16.6328125" style="76" customWidth="1"/>
-    <col min="226" max="226" width="18.6328125" style="76"/>
-    <col min="227" max="227" width="17.6328125" style="75"/>
-    <col min="228" max="230" width="13.08984375" style="76" customWidth="1"/>
-    <col min="231" max="231" width="13.08984375" style="78" customWidth="1"/>
-    <col min="232" max="232" width="14.7265625" style="89" customWidth="1"/>
-    <col min="233" max="233" width="16.08984375" style="75" customWidth="1"/>
-    <col min="234" max="236" width="16.08984375" style="76" customWidth="1"/>
-    <col min="237" max="237" width="21.7265625" style="76"/>
-    <col min="238" max="238" width="17.453125" style="76"/>
-    <col min="239" max="239" width="27.6328125" style="76" customWidth="1"/>
+    <col min="198" max="198" width="15.375" style="76"/>
+    <col min="199" max="199" width="17.5" style="76"/>
+    <col min="200" max="200" width="11.625" style="78" customWidth="1"/>
+    <col min="201" max="202" width="11.625" style="76" customWidth="1"/>
+    <col min="203" max="203" width="17.625" style="76"/>
+    <col min="204" max="204" width="19.75" style="76"/>
+    <col min="205" max="205" width="23.25" style="80"/>
+    <col min="206" max="206" width="23.25" style="90"/>
+    <col min="207" max="207" width="11.625" style="76" customWidth="1"/>
+    <col min="208" max="208" width="35.375" style="76"/>
+    <col min="209" max="209" width="38.5" style="76"/>
+    <col min="210" max="210" width="28.625" style="76"/>
+    <col min="211" max="212" width="33.125" style="76"/>
+    <col min="213" max="213" width="11.625" style="76" customWidth="1"/>
+    <col min="214" max="214" width="16.375" style="76"/>
+    <col min="215" max="215" width="19.75" style="76"/>
+    <col min="216" max="216" width="35.375" style="76"/>
+    <col min="217" max="217" width="25.25" style="76"/>
+    <col min="218" max="218" width="29.625" style="76"/>
+    <col min="219" max="224" width="18.625" style="76"/>
+    <col min="225" max="225" width="16.625" style="76" customWidth="1"/>
+    <col min="226" max="226" width="18.625" style="76"/>
+    <col min="227" max="227" width="17.625" style="75"/>
+    <col min="228" max="230" width="13.125" style="76" customWidth="1"/>
+    <col min="231" max="231" width="13.125" style="78" customWidth="1"/>
+    <col min="232" max="232" width="14.75" style="89" customWidth="1"/>
+    <col min="233" max="233" width="16.125" style="75" customWidth="1"/>
+    <col min="234" max="236" width="16.125" style="76" customWidth="1"/>
+    <col min="237" max="237" width="21.75" style="76"/>
+    <col min="238" max="238" width="17.5" style="76"/>
+    <col min="239" max="239" width="27.625" style="76" customWidth="1"/>
     <col min="240" max="240" width="23" style="76"/>
-    <col min="241" max="242" width="19.7265625" style="76"/>
-    <col min="243" max="243" width="19.7265625" style="76" customWidth="1"/>
-    <col min="244" max="244" width="29.6328125" style="76"/>
-    <col min="245" max="245" width="34.08984375" style="76"/>
-    <col min="246" max="246" width="34.08984375" style="76" customWidth="1"/>
-    <col min="247" max="247" width="34.08984375" style="77" customWidth="1"/>
-    <col min="248" max="252" width="34.08984375" style="76" customWidth="1"/>
-    <col min="253" max="253" width="34.08984375" style="91" customWidth="1"/>
-    <col min="254" max="260" width="34.08984375" style="76" customWidth="1"/>
-    <col min="261" max="261" width="34.08984375" style="92" customWidth="1"/>
-    <col min="262" max="267" width="34.08984375" style="74" customWidth="1"/>
-    <col min="268" max="268" width="15.7265625" style="82" customWidth="1"/>
+    <col min="241" max="242" width="19.75" style="76"/>
+    <col min="243" max="243" width="19.75" style="76" customWidth="1"/>
+    <col min="244" max="244" width="29.625" style="76"/>
+    <col min="245" max="245" width="34.125" style="76"/>
+    <col min="246" max="246" width="34.125" style="76" customWidth="1"/>
+    <col min="247" max="247" width="34.125" style="77" customWidth="1"/>
+    <col min="248" max="252" width="34.125" style="76" customWidth="1"/>
+    <col min="253" max="253" width="34.125" style="91" customWidth="1"/>
+    <col min="254" max="260" width="34.125" style="76" customWidth="1"/>
+    <col min="261" max="261" width="34.125" style="92" customWidth="1"/>
+    <col min="262" max="267" width="34.125" style="74" customWidth="1"/>
+    <col min="268" max="268" width="15.75" style="82" customWidth="1"/>
     <col min="269" max="269" width="9" style="82"/>
-    <col min="270" max="270" width="12.453125" style="86" customWidth="1"/>
+    <col min="270" max="270" width="12.5" style="86" customWidth="1"/>
     <col min="271" max="271" width="11" style="88" customWidth="1"/>
-    <col min="272" max="272" width="13.08984375" style="87" customWidth="1"/>
-    <col min="273" max="273" width="16.453125" style="75" customWidth="1"/>
+    <col min="272" max="272" width="13.125" style="87" customWidth="1"/>
+    <col min="273" max="273" width="16.5" style="75" customWidth="1"/>
     <col min="274" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:273" s="72" customFormat="1">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="125" t="s">
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="128" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="126"/>
-      <c r="M1" s="126"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="137" t="s">
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="132" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="137"/>
-      <c r="Y1" s="137"/>
-      <c r="Z1" s="125" t="s">
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="132"/>
+      <c r="T1" s="132"/>
+      <c r="U1" s="132"/>
+      <c r="V1" s="132"/>
+      <c r="W1" s="132"/>
+      <c r="X1" s="132"/>
+      <c r="Y1" s="132"/>
+      <c r="Z1" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="126"/>
-      <c r="AB1" s="126"/>
-      <c r="AC1" s="126"/>
-      <c r="AD1" s="126"/>
-      <c r="AE1" s="126"/>
-      <c r="AF1" s="126"/>
-      <c r="AG1" s="127"/>
-      <c r="AH1" s="141" t="s">
+      <c r="AA1" s="129"/>
+      <c r="AB1" s="129"/>
+      <c r="AC1" s="129"/>
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="129"/>
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="131"/>
+      <c r="AH1" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="135"/>
-      <c r="AJ1" s="135"/>
-      <c r="AK1" s="135"/>
-      <c r="AL1" s="135"/>
-      <c r="AM1" s="135"/>
-      <c r="AN1" s="135"/>
-      <c r="AO1" s="135"/>
-      <c r="AP1" s="135"/>
-      <c r="AQ1" s="135"/>
-      <c r="AR1" s="135"/>
-      <c r="AS1" s="135"/>
-      <c r="AT1" s="135"/>
-      <c r="AU1" s="135"/>
-      <c r="AV1" s="135"/>
-      <c r="AW1" s="135"/>
-      <c r="AX1" s="135"/>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="135"/>
-      <c r="BB1" s="135"/>
-      <c r="BC1" s="135"/>
-      <c r="BD1" s="135"/>
-      <c r="BE1" s="135"/>
-      <c r="BF1" s="135"/>
-      <c r="BG1" s="135"/>
-      <c r="BH1" s="135"/>
-      <c r="BI1" s="135"/>
-      <c r="BJ1" s="135"/>
-      <c r="BK1" s="135"/>
-      <c r="BL1" s="135"/>
-      <c r="BM1" s="135"/>
-      <c r="BN1" s="135"/>
-      <c r="BO1" s="135"/>
-      <c r="BP1" s="135"/>
-      <c r="BQ1" s="135"/>
-      <c r="BR1" s="135"/>
-      <c r="BS1" s="135"/>
-      <c r="BT1" s="135"/>
-      <c r="BU1" s="135"/>
-      <c r="BV1" s="135"/>
-      <c r="BW1" s="135"/>
-      <c r="BX1" s="135"/>
-      <c r="BY1" s="135"/>
-      <c r="BZ1" s="135"/>
-      <c r="CA1" s="135"/>
-      <c r="CB1" s="143"/>
-      <c r="CC1" s="143"/>
-      <c r="CD1" s="143"/>
-      <c r="CE1" s="143"/>
-      <c r="CF1" s="143"/>
-      <c r="CG1" s="143"/>
-      <c r="CH1" s="143"/>
-      <c r="CI1" s="143"/>
-      <c r="CJ1" s="143"/>
-      <c r="CK1" s="143"/>
-      <c r="CL1" s="143"/>
-      <c r="CM1" s="144"/>
-      <c r="CN1" s="135"/>
-      <c r="CO1" s="135"/>
-      <c r="CP1" s="135"/>
-      <c r="CQ1" s="135"/>
-      <c r="CR1" s="135"/>
-      <c r="CS1" s="135"/>
-      <c r="CT1" s="135"/>
-      <c r="CU1" s="142"/>
-      <c r="CV1" s="136" t="s">
+      <c r="AI1" s="126"/>
+      <c r="AJ1" s="126"/>
+      <c r="AK1" s="126"/>
+      <c r="AL1" s="126"/>
+      <c r="AM1" s="126"/>
+      <c r="AN1" s="126"/>
+      <c r="AO1" s="126"/>
+      <c r="AP1" s="126"/>
+      <c r="AQ1" s="126"/>
+      <c r="AR1" s="126"/>
+      <c r="AS1" s="126"/>
+      <c r="AT1" s="126"/>
+      <c r="AU1" s="126"/>
+      <c r="AV1" s="126"/>
+      <c r="AW1" s="126"/>
+      <c r="AX1" s="126"/>
+      <c r="AY1" s="126"/>
+      <c r="AZ1" s="126"/>
+      <c r="BA1" s="126"/>
+      <c r="BB1" s="126"/>
+      <c r="BC1" s="126"/>
+      <c r="BD1" s="126"/>
+      <c r="BE1" s="126"/>
+      <c r="BF1" s="126"/>
+      <c r="BG1" s="126"/>
+      <c r="BH1" s="126"/>
+      <c r="BI1" s="126"/>
+      <c r="BJ1" s="126"/>
+      <c r="BK1" s="126"/>
+      <c r="BL1" s="126"/>
+      <c r="BM1" s="126"/>
+      <c r="BN1" s="126"/>
+      <c r="BO1" s="126"/>
+      <c r="BP1" s="126"/>
+      <c r="BQ1" s="126"/>
+      <c r="BR1" s="126"/>
+      <c r="BS1" s="126"/>
+      <c r="BT1" s="126"/>
+      <c r="BU1" s="126"/>
+      <c r="BV1" s="126"/>
+      <c r="BW1" s="126"/>
+      <c r="BX1" s="126"/>
+      <c r="BY1" s="126"/>
+      <c r="BZ1" s="126"/>
+      <c r="CA1" s="126"/>
+      <c r="CB1" s="133"/>
+      <c r="CC1" s="133"/>
+      <c r="CD1" s="133"/>
+      <c r="CE1" s="133"/>
+      <c r="CF1" s="133"/>
+      <c r="CG1" s="133"/>
+      <c r="CH1" s="133"/>
+      <c r="CI1" s="133"/>
+      <c r="CJ1" s="133"/>
+      <c r="CK1" s="133"/>
+      <c r="CL1" s="133"/>
+      <c r="CM1" s="134"/>
+      <c r="CN1" s="126"/>
+      <c r="CO1" s="126"/>
+      <c r="CP1" s="126"/>
+      <c r="CQ1" s="126"/>
+      <c r="CR1" s="126"/>
+      <c r="CS1" s="126"/>
+      <c r="CT1" s="126"/>
+      <c r="CU1" s="127"/>
+      <c r="CV1" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="CW1" s="137"/>
-      <c r="CX1" s="137"/>
-      <c r="CY1" s="137"/>
-      <c r="CZ1" s="137"/>
-      <c r="DA1" s="137"/>
-      <c r="DB1" s="137"/>
-      <c r="DC1" s="137"/>
-      <c r="DD1" s="137"/>
-      <c r="DE1" s="137"/>
-      <c r="DF1" s="137"/>
-      <c r="DG1" s="138"/>
-      <c r="DH1" s="131" t="s">
+      <c r="CW1" s="132"/>
+      <c r="CX1" s="132"/>
+      <c r="CY1" s="132"/>
+      <c r="CZ1" s="132"/>
+      <c r="DA1" s="132"/>
+      <c r="DB1" s="132"/>
+      <c r="DC1" s="132"/>
+      <c r="DD1" s="132"/>
+      <c r="DE1" s="132"/>
+      <c r="DF1" s="132"/>
+      <c r="DG1" s="136"/>
+      <c r="DH1" s="137" t="s">
         <v>6</v>
       </c>
-      <c r="DI1" s="132"/>
-      <c r="DJ1" s="132"/>
-      <c r="DK1" s="132"/>
-      <c r="DL1" s="132"/>
-      <c r="DM1" s="132"/>
-      <c r="DN1" s="132"/>
-      <c r="DO1" s="132"/>
-      <c r="DP1" s="132"/>
-      <c r="DQ1" s="132"/>
-      <c r="DR1" s="132"/>
+      <c r="DI1" s="138"/>
+      <c r="DJ1" s="138"/>
+      <c r="DK1" s="138"/>
+      <c r="DL1" s="138"/>
+      <c r="DM1" s="138"/>
+      <c r="DN1" s="138"/>
+      <c r="DO1" s="138"/>
+      <c r="DP1" s="138"/>
+      <c r="DQ1" s="138"/>
+      <c r="DR1" s="138"/>
       <c r="DS1" s="139" t="s">
         <v>7</v>
       </c>
       <c r="DT1" s="140"/>
       <c r="DU1" s="140"/>
       <c r="DV1" s="140"/>
-      <c r="DW1" s="128" t="s">
+      <c r="DW1" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="DX1" s="134"/>
-      <c r="DY1" s="129"/>
-      <c r="DZ1" s="129"/>
-      <c r="EA1" s="129"/>
-      <c r="EB1" s="129"/>
-      <c r="EC1" s="129"/>
-      <c r="ED1" s="129"/>
-      <c r="EE1" s="129"/>
-      <c r="EF1" s="129"/>
-      <c r="EG1" s="129"/>
-      <c r="EH1" s="129"/>
-      <c r="EI1" s="129"/>
-      <c r="EJ1" s="130"/>
-      <c r="EK1" s="131" t="s">
+      <c r="DX1" s="130"/>
+      <c r="DY1" s="142"/>
+      <c r="DZ1" s="142"/>
+      <c r="EA1" s="142"/>
+      <c r="EB1" s="142"/>
+      <c r="EC1" s="142"/>
+      <c r="ED1" s="142"/>
+      <c r="EE1" s="142"/>
+      <c r="EF1" s="142"/>
+      <c r="EG1" s="142"/>
+      <c r="EH1" s="142"/>
+      <c r="EI1" s="142"/>
+      <c r="EJ1" s="143"/>
+      <c r="EK1" s="137" t="s">
         <v>9</v>
       </c>
-      <c r="EL1" s="132"/>
-      <c r="EM1" s="132"/>
-      <c r="EN1" s="132"/>
-      <c r="EO1" s="132"/>
-      <c r="EP1" s="133"/>
-      <c r="EQ1" s="131" t="s">
+      <c r="EL1" s="138"/>
+      <c r="EM1" s="138"/>
+      <c r="EN1" s="138"/>
+      <c r="EO1" s="138"/>
+      <c r="EP1" s="144"/>
+      <c r="EQ1" s="137" t="s">
         <v>10</v>
       </c>
-      <c r="ER1" s="132"/>
-      <c r="ES1" s="132"/>
-      <c r="ET1" s="132"/>
-      <c r="EU1" s="133"/>
-      <c r="EV1" s="131" t="s">
+      <c r="ER1" s="138"/>
+      <c r="ES1" s="138"/>
+      <c r="ET1" s="138"/>
+      <c r="EU1" s="144"/>
+      <c r="EV1" s="137" t="s">
         <v>11</v>
       </c>
-      <c r="EW1" s="132"/>
-      <c r="EX1" s="132"/>
-      <c r="EY1" s="132"/>
-      <c r="EZ1" s="132"/>
-      <c r="FA1" s="132"/>
-      <c r="FB1" s="132"/>
-      <c r="FC1" s="132"/>
-      <c r="FD1" s="132"/>
-      <c r="FE1" s="132"/>
-      <c r="FF1" s="132"/>
-      <c r="FG1" s="132"/>
-      <c r="FH1" s="132"/>
-      <c r="FI1" s="132"/>
-      <c r="FJ1" s="132"/>
-      <c r="FK1" s="132"/>
-      <c r="FL1" s="133"/>
-      <c r="FM1" s="134" t="s">
+      <c r="EW1" s="138"/>
+      <c r="EX1" s="138"/>
+      <c r="EY1" s="138"/>
+      <c r="EZ1" s="138"/>
+      <c r="FA1" s="138"/>
+      <c r="FB1" s="138"/>
+      <c r="FC1" s="138"/>
+      <c r="FD1" s="138"/>
+      <c r="FE1" s="138"/>
+      <c r="FF1" s="138"/>
+      <c r="FG1" s="138"/>
+      <c r="FH1" s="138"/>
+      <c r="FI1" s="138"/>
+      <c r="FJ1" s="138"/>
+      <c r="FK1" s="138"/>
+      <c r="FL1" s="144"/>
+      <c r="FM1" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="FN1" s="134"/>
-      <c r="FO1" s="134"/>
-      <c r="FP1" s="134"/>
-      <c r="FQ1" s="134"/>
-      <c r="FR1" s="134"/>
-      <c r="FS1" s="134"/>
-      <c r="FT1" s="134"/>
-      <c r="FU1" s="134"/>
-      <c r="FV1" s="134"/>
-      <c r="FW1" s="134"/>
-      <c r="FX1" s="134"/>
-      <c r="FY1" s="134"/>
-      <c r="FZ1" s="134"/>
-      <c r="GA1" s="134"/>
-      <c r="GB1" s="134"/>
-      <c r="GC1" s="134"/>
-      <c r="GD1" s="134"/>
-      <c r="GE1" s="134"/>
-      <c r="GF1" s="134"/>
-      <c r="GG1" s="134"/>
-      <c r="GH1" s="134"/>
-      <c r="GI1" s="134"/>
-      <c r="GJ1" s="131" t="s">
+      <c r="FN1" s="130"/>
+      <c r="FO1" s="130"/>
+      <c r="FP1" s="130"/>
+      <c r="FQ1" s="130"/>
+      <c r="FR1" s="130"/>
+      <c r="FS1" s="130"/>
+      <c r="FT1" s="130"/>
+      <c r="FU1" s="130"/>
+      <c r="FV1" s="130"/>
+      <c r="FW1" s="130"/>
+      <c r="FX1" s="130"/>
+      <c r="FY1" s="130"/>
+      <c r="FZ1" s="130"/>
+      <c r="GA1" s="130"/>
+      <c r="GB1" s="130"/>
+      <c r="GC1" s="130"/>
+      <c r="GD1" s="130"/>
+      <c r="GE1" s="130"/>
+      <c r="GF1" s="130"/>
+      <c r="GG1" s="130"/>
+      <c r="GH1" s="130"/>
+      <c r="GI1" s="130"/>
+      <c r="GJ1" s="137" t="s">
         <v>13</v>
       </c>
-      <c r="GK1" s="132"/>
-      <c r="GL1" s="132"/>
-      <c r="GM1" s="132"/>
-      <c r="GN1" s="133"/>
-      <c r="GO1" s="125" t="s">
+      <c r="GK1" s="138"/>
+      <c r="GL1" s="138"/>
+      <c r="GM1" s="138"/>
+      <c r="GN1" s="144"/>
+      <c r="GO1" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="GP1" s="126"/>
-      <c r="GQ1" s="126"/>
-      <c r="GR1" s="126"/>
-      <c r="GS1" s="126"/>
-      <c r="GT1" s="126"/>
-      <c r="GU1" s="126"/>
-      <c r="GV1" s="126"/>
-      <c r="GW1" s="126"/>
-      <c r="GX1" s="126"/>
-      <c r="GY1" s="126"/>
-      <c r="GZ1" s="126"/>
-      <c r="HA1" s="126"/>
-      <c r="HB1" s="126"/>
-      <c r="HC1" s="126"/>
-      <c r="HD1" s="126"/>
-      <c r="HE1" s="126"/>
-      <c r="HF1" s="126"/>
-      <c r="HG1" s="126"/>
-      <c r="HH1" s="126"/>
-      <c r="HI1" s="126"/>
-      <c r="HJ1" s="126"/>
-      <c r="HK1" s="126"/>
-      <c r="HL1" s="126"/>
-      <c r="HM1" s="126"/>
-      <c r="HN1" s="126"/>
-      <c r="HO1" s="126"/>
-      <c r="HP1" s="126"/>
-      <c r="HQ1" s="135"/>
-      <c r="HR1" s="126"/>
-      <c r="HS1" s="125" t="s">
+      <c r="GP1" s="129"/>
+      <c r="GQ1" s="129"/>
+      <c r="GR1" s="129"/>
+      <c r="GS1" s="129"/>
+      <c r="GT1" s="129"/>
+      <c r="GU1" s="129"/>
+      <c r="GV1" s="129"/>
+      <c r="GW1" s="129"/>
+      <c r="GX1" s="129"/>
+      <c r="GY1" s="129"/>
+      <c r="GZ1" s="129"/>
+      <c r="HA1" s="129"/>
+      <c r="HB1" s="129"/>
+      <c r="HC1" s="129"/>
+      <c r="HD1" s="129"/>
+      <c r="HE1" s="129"/>
+      <c r="HF1" s="129"/>
+      <c r="HG1" s="129"/>
+      <c r="HH1" s="129"/>
+      <c r="HI1" s="129"/>
+      <c r="HJ1" s="129"/>
+      <c r="HK1" s="129"/>
+      <c r="HL1" s="129"/>
+      <c r="HM1" s="129"/>
+      <c r="HN1" s="129"/>
+      <c r="HO1" s="129"/>
+      <c r="HP1" s="129"/>
+      <c r="HQ1" s="126"/>
+      <c r="HR1" s="129"/>
+      <c r="HS1" s="128" t="s">
         <v>15</v>
       </c>
-      <c r="HT1" s="126"/>
-      <c r="HU1" s="126"/>
-      <c r="HV1" s="126"/>
-      <c r="HW1" s="126"/>
-      <c r="HX1" s="127"/>
-      <c r="HY1" s="125" t="s">
+      <c r="HT1" s="129"/>
+      <c r="HU1" s="129"/>
+      <c r="HV1" s="129"/>
+      <c r="HW1" s="129"/>
+      <c r="HX1" s="131"/>
+      <c r="HY1" s="128" t="s">
         <v>16</v>
       </c>
-      <c r="HZ1" s="126"/>
-      <c r="IA1" s="126"/>
-      <c r="IB1" s="126"/>
-      <c r="IC1" s="126"/>
-      <c r="ID1" s="126"/>
-      <c r="IE1" s="126"/>
-      <c r="IF1" s="126"/>
-      <c r="IG1" s="126"/>
-      <c r="IH1" s="126"/>
-      <c r="II1" s="126"/>
-      <c r="IJ1" s="126"/>
-      <c r="IK1" s="126"/>
-      <c r="IL1" s="126"/>
-      <c r="IM1" s="127"/>
-      <c r="IN1" s="128" t="s">
+      <c r="HZ1" s="129"/>
+      <c r="IA1" s="129"/>
+      <c r="IB1" s="129"/>
+      <c r="IC1" s="129"/>
+      <c r="ID1" s="129"/>
+      <c r="IE1" s="129"/>
+      <c r="IF1" s="129"/>
+      <c r="IG1" s="129"/>
+      <c r="IH1" s="129"/>
+      <c r="II1" s="129"/>
+      <c r="IJ1" s="129"/>
+      <c r="IK1" s="129"/>
+      <c r="IL1" s="129"/>
+      <c r="IM1" s="131"/>
+      <c r="IN1" s="141" t="s">
         <v>17</v>
       </c>
-      <c r="IO1" s="129"/>
-      <c r="IP1" s="129"/>
-      <c r="IQ1" s="129"/>
-      <c r="IR1" s="129"/>
-      <c r="IS1" s="129"/>
-      <c r="IT1" s="129"/>
-      <c r="IU1" s="129"/>
-      <c r="IV1" s="129"/>
-      <c r="IW1" s="129"/>
-      <c r="IX1" s="129"/>
-      <c r="IY1" s="129"/>
-      <c r="IZ1" s="129"/>
-      <c r="JA1" s="129"/>
-      <c r="JB1" s="129"/>
-      <c r="JC1" s="129"/>
-      <c r="JD1" s="129"/>
-      <c r="JE1" s="129"/>
-      <c r="JF1" s="129"/>
-      <c r="JG1" s="130"/>
-      <c r="JH1" s="128" t="s">
+      <c r="IO1" s="142"/>
+      <c r="IP1" s="142"/>
+      <c r="IQ1" s="142"/>
+      <c r="IR1" s="142"/>
+      <c r="IS1" s="142"/>
+      <c r="IT1" s="142"/>
+      <c r="IU1" s="142"/>
+      <c r="IV1" s="142"/>
+      <c r="IW1" s="142"/>
+      <c r="IX1" s="142"/>
+      <c r="IY1" s="142"/>
+      <c r="IZ1" s="142"/>
+      <c r="JA1" s="142"/>
+      <c r="JB1" s="142"/>
+      <c r="JC1" s="142"/>
+      <c r="JD1" s="142"/>
+      <c r="JE1" s="142"/>
+      <c r="JF1" s="142"/>
+      <c r="JG1" s="143"/>
+      <c r="JH1" s="141" t="s">
         <v>18</v>
       </c>
-      <c r="JI1" s="129"/>
-      <c r="JJ1" s="129"/>
-      <c r="JK1" s="129"/>
-      <c r="JL1" s="129"/>
+      <c r="JI1" s="142"/>
+      <c r="JJ1" s="142"/>
+      <c r="JK1" s="142"/>
+      <c r="JL1" s="142"/>
       <c r="JM1" s="117"/>
     </row>
     <row r="2" spans="1:273" s="73" customFormat="1">
@@ -10095,16 +10091,6 @@
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="19">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:N1"/>
-    <mergeCell ref="O1:Y1"/>
-    <mergeCell ref="Z1:AG1"/>
-    <mergeCell ref="AH1:CU1"/>
-    <mergeCell ref="CV1:DG1"/>
-    <mergeCell ref="DH1:DR1"/>
-    <mergeCell ref="DS1:DV1"/>
-    <mergeCell ref="DW1:EJ1"/>
-    <mergeCell ref="EK1:EP1"/>
     <mergeCell ref="HS1:HX1"/>
     <mergeCell ref="HY1:IM1"/>
     <mergeCell ref="IN1:JG1"/>
@@ -10114,6 +10100,16 @@
     <mergeCell ref="FM1:GI1"/>
     <mergeCell ref="GJ1:GN1"/>
     <mergeCell ref="GO1:HR1"/>
+    <mergeCell ref="CV1:DG1"/>
+    <mergeCell ref="DH1:DR1"/>
+    <mergeCell ref="DS1:DV1"/>
+    <mergeCell ref="DW1:EJ1"/>
+    <mergeCell ref="EK1:EP1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:N1"/>
+    <mergeCell ref="O1:Y1"/>
+    <mergeCell ref="Z1:AG1"/>
+    <mergeCell ref="AH1:CU1"/>
   </mergeCells>
   <phoneticPr fontId="36" type="noConversion"/>
   <dataValidations count="130">
@@ -10553,9 +10549,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="95.08984375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="95.125" style="1" customWidth="1"/>
     <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -10605,22 +10601,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IV319"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="32.26953125" style="30" customWidth="1"/>
-    <col min="2" max="2" width="44.7265625" style="30" customWidth="1"/>
+    <col min="1" max="1" width="32.25" style="30" customWidth="1"/>
+    <col min="2" max="2" width="44.75" style="30" customWidth="1"/>
     <col min="3" max="256" width="9" style="30"/>
     <col min="257" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="145" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="164"/>
+      <c r="B1" s="146"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="154" t="s">
+      <c r="A2" s="159" t="s">
         <v>239</v>
       </c>
       <c r="B2" s="42" t="s">
@@ -10628,25 +10624,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="155"/>
+      <c r="A3" s="160"/>
       <c r="B3" s="39" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="155"/>
+      <c r="A4" s="160"/>
       <c r="B4" s="39" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="156"/>
+      <c r="A5" s="161"/>
       <c r="B5" s="37" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="30" customFormat="1">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="162" t="s">
         <v>241</v>
       </c>
       <c r="B6" s="42" t="s">
@@ -10654,13 +10650,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="30" customFormat="1">
-      <c r="A7" s="158"/>
+      <c r="A7" s="163"/>
       <c r="B7" s="36" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="30" customFormat="1">
-      <c r="A8" s="159" t="s">
+      <c r="A8" s="164" t="s">
         <v>244</v>
       </c>
       <c r="B8" s="35" t="s">
@@ -10668,13 +10664,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="30" customFormat="1">
-      <c r="A9" s="158"/>
+      <c r="A9" s="163"/>
       <c r="B9" s="36" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="160" t="s">
+      <c r="A10" s="152" t="s">
         <v>247</v>
       </c>
       <c r="B10" s="39" t="s">
@@ -10682,61 +10678,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="161"/>
+      <c r="A11" s="165"/>
       <c r="B11" s="39" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="161"/>
+      <c r="A12" s="165"/>
       <c r="B12" s="39" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="161"/>
+      <c r="A13" s="165"/>
       <c r="B13" s="39" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="161"/>
+      <c r="A14" s="165"/>
       <c r="B14" s="39" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="161"/>
+      <c r="A15" s="165"/>
       <c r="B15" s="39" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="161"/>
+      <c r="A16" s="165"/>
       <c r="B16" s="39" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="161"/>
+      <c r="A17" s="165"/>
       <c r="B17" s="39" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="161"/>
+      <c r="A18" s="165"/>
       <c r="B18" s="39" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="161"/>
+      <c r="A19" s="165"/>
       <c r="B19" s="39" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="161"/>
+      <c r="A20" s="165"/>
       <c r="B20" s="39" t="s">
         <v>258</v>
       </c>
@@ -10750,7 +10746,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="160" t="s">
+      <c r="A22" s="152" t="s">
         <v>261</v>
       </c>
       <c r="B22" s="42" t="s">
@@ -10758,19 +10754,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="161"/>
+      <c r="A23" s="165"/>
       <c r="B23" s="39" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="162"/>
+      <c r="A24" s="153"/>
       <c r="B24" s="37" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="160" t="s">
+      <c r="A25" s="152" t="s">
         <v>265</v>
       </c>
       <c r="B25" s="39" t="s">
@@ -10778,67 +10774,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="161"/>
+      <c r="A26" s="165"/>
       <c r="B26" s="39" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="161"/>
+      <c r="A27" s="165"/>
       <c r="B27" s="34" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="161"/>
+      <c r="A28" s="165"/>
       <c r="B28" s="34" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="161"/>
+      <c r="A29" s="165"/>
       <c r="B29" s="34" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="161"/>
+      <c r="A30" s="165"/>
       <c r="B30" s="34" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="161"/>
+      <c r="A31" s="165"/>
       <c r="B31" s="34" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="161"/>
+      <c r="A32" s="165"/>
       <c r="B32" s="34" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="161"/>
+      <c r="A33" s="165"/>
       <c r="B33" s="34" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="161"/>
+      <c r="A34" s="165"/>
       <c r="B34" s="34" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="162"/>
+      <c r="A35" s="153"/>
       <c r="B35" s="55" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="160" t="s">
+      <c r="A36" s="152" t="s">
         <v>277</v>
       </c>
       <c r="B36" s="34" t="s">
@@ -10846,25 +10842,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="161"/>
+      <c r="A37" s="165"/>
       <c r="B37" s="39" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="161"/>
+      <c r="A38" s="165"/>
       <c r="B38" s="34" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="162"/>
+      <c r="A39" s="153"/>
       <c r="B39" s="34" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="160" t="s">
+      <c r="A40" s="152" t="s">
         <v>282</v>
       </c>
       <c r="B40" s="33" t="s">
@@ -10872,43 +10868,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="161"/>
+      <c r="A41" s="165"/>
       <c r="B41" s="34" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="161"/>
+      <c r="A42" s="165"/>
       <c r="B42" s="34" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="161"/>
+      <c r="A43" s="165"/>
       <c r="B43" s="34" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="161"/>
+      <c r="A44" s="165"/>
       <c r="B44" s="34" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="161"/>
+      <c r="A45" s="165"/>
       <c r="B45" s="34" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="162"/>
+      <c r="A46" s="153"/>
       <c r="B46" s="37" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="160" t="s">
+      <c r="A47" s="152" t="s">
         <v>290</v>
       </c>
       <c r="B47" s="42" t="s">
@@ -10916,61 +10912,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="161"/>
+      <c r="A48" s="165"/>
       <c r="B48" s="34" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="161"/>
+      <c r="A49" s="165"/>
       <c r="B49" s="34" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="161"/>
+      <c r="A50" s="165"/>
       <c r="B50" s="34" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="161"/>
+      <c r="A51" s="165"/>
       <c r="B51" s="34" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="161"/>
+      <c r="A52" s="165"/>
       <c r="B52" s="34" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="161"/>
+      <c r="A53" s="165"/>
       <c r="B53" s="39" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="161"/>
+      <c r="A54" s="165"/>
       <c r="B54" s="34" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="161"/>
+      <c r="A55" s="165"/>
       <c r="B55" s="39" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="162"/>
+      <c r="A56" s="153"/>
       <c r="B56" s="37" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="160" t="s">
+      <c r="A57" s="152" t="s">
         <v>301</v>
       </c>
       <c r="B57" s="33" t="s">
@@ -10978,19 +10974,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="161"/>
+      <c r="A58" s="165"/>
       <c r="B58" s="34" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="162"/>
+      <c r="A59" s="153"/>
       <c r="B59" s="37" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="160" t="s">
+      <c r="A60" s="152" t="s">
         <v>305</v>
       </c>
       <c r="B60" s="47" t="s">
@@ -10998,37 +10994,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="161"/>
+      <c r="A61" s="165"/>
       <c r="B61" s="34" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="161"/>
+      <c r="A62" s="165"/>
       <c r="B62" s="48" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="161"/>
+      <c r="A63" s="165"/>
       <c r="B63" s="34" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="161"/>
+      <c r="A64" s="165"/>
       <c r="B64" s="34" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="162"/>
+      <c r="A65" s="153"/>
       <c r="B65" s="41" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="160" t="s">
+      <c r="A66" s="152" t="s">
         <v>312</v>
       </c>
       <c r="B66" s="47" t="s">
@@ -11036,37 +11032,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="161"/>
+      <c r="A67" s="165"/>
       <c r="B67" s="34" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="161"/>
+      <c r="A68" s="165"/>
       <c r="B68" s="34" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="161"/>
+      <c r="A69" s="165"/>
       <c r="B69" s="34" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="161"/>
+      <c r="A70" s="165"/>
       <c r="B70" s="34" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="162"/>
+      <c r="A71" s="153"/>
       <c r="B71" s="41" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="30" customFormat="1">
-      <c r="A72" s="160" t="s">
+      <c r="A72" s="152" t="s">
         <v>319</v>
       </c>
       <c r="B72" s="34" t="s">
@@ -11074,103 +11070,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="30" customFormat="1">
-      <c r="A73" s="161"/>
+      <c r="A73" s="165"/>
       <c r="B73" s="34" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="30" customFormat="1">
-      <c r="A74" s="161"/>
+      <c r="A74" s="165"/>
       <c r="B74" s="34" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="30" customFormat="1">
-      <c r="A75" s="161"/>
+      <c r="A75" s="165"/>
       <c r="B75" s="34" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="30" customFormat="1">
-      <c r="A76" s="161"/>
+      <c r="A76" s="165"/>
       <c r="B76" s="34" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="30" customFormat="1">
-      <c r="A77" s="161"/>
+      <c r="A77" s="165"/>
       <c r="B77" s="49" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="30" customFormat="1">
-      <c r="A78" s="161"/>
+      <c r="A78" s="165"/>
       <c r="B78" s="34" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="30" customFormat="1">
-      <c r="A79" s="161"/>
+      <c r="A79" s="165"/>
       <c r="B79" s="34" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="30" customFormat="1">
-      <c r="A80" s="161"/>
+      <c r="A80" s="165"/>
       <c r="B80" s="34" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="30" customFormat="1">
-      <c r="A81" s="161"/>
+      <c r="A81" s="165"/>
       <c r="B81" s="49" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="30" customFormat="1">
-      <c r="A82" s="161"/>
+      <c r="A82" s="165"/>
       <c r="B82" s="34" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="30" customFormat="1">
-      <c r="A83" s="161"/>
+      <c r="A83" s="165"/>
       <c r="B83" s="34" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="30" customFormat="1">
-      <c r="A84" s="161"/>
+      <c r="A84" s="165"/>
       <c r="B84" s="34" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="30" customFormat="1">
-      <c r="A85" s="161"/>
+      <c r="A85" s="165"/>
       <c r="B85" s="49" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="30" customFormat="1">
-      <c r="A86" s="161"/>
+      <c r="A86" s="165"/>
       <c r="B86" s="49" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="30" customFormat="1">
-      <c r="A87" s="161"/>
+      <c r="A87" s="165"/>
       <c r="B87" s="49" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="30" customFormat="1">
-      <c r="A88" s="162"/>
+      <c r="A88" s="153"/>
       <c r="B88" s="37" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="30" customFormat="1">
-      <c r="A89" s="160" t="s">
+      <c r="A89" s="152" t="s">
         <v>337</v>
       </c>
       <c r="B89" s="39" t="s">
@@ -11178,38 +11174,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="30" customFormat="1">
-      <c r="A90" s="161"/>
+      <c r="A90" s="165"/>
       <c r="B90" s="39" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="30" customFormat="1">
-      <c r="A91" s="161"/>
+      <c r="A91" s="165"/>
       <c r="B91" s="39" t="s">
         <v>340</v>
       </c>
       <c r="F91" s="56"/>
     </row>
     <row r="92" spans="1:6" s="30" customFormat="1">
-      <c r="A92" s="161"/>
+      <c r="A92" s="165"/>
       <c r="B92" s="57" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="30" customFormat="1">
-      <c r="A93" s="161"/>
+      <c r="A93" s="165"/>
       <c r="B93" s="39" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="30" customFormat="1">
-      <c r="A94" s="162"/>
+      <c r="A94" s="153"/>
       <c r="B94" s="37" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="30" customFormat="1">
-      <c r="A95" s="160" t="s">
+      <c r="A95" s="152" t="s">
         <v>344</v>
       </c>
       <c r="B95" s="50" t="s">
@@ -11217,43 +11213,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="30" customFormat="1">
-      <c r="A96" s="161"/>
+      <c r="A96" s="165"/>
       <c r="B96" s="51" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="30" customFormat="1">
-      <c r="A97" s="161"/>
+      <c r="A97" s="165"/>
       <c r="B97" s="51" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="30" customFormat="1">
-      <c r="A98" s="161"/>
+      <c r="A98" s="165"/>
       <c r="B98" s="51" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="30" customFormat="1">
-      <c r="A99" s="161"/>
+      <c r="A99" s="165"/>
       <c r="B99" s="51" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="30" customFormat="1">
-      <c r="A100" s="161"/>
+      <c r="A100" s="165"/>
       <c r="B100" s="51" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="30" customFormat="1">
-      <c r="A101" s="162"/>
+      <c r="A101" s="153"/>
       <c r="B101" s="45" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="30" customFormat="1">
-      <c r="A102" s="160" t="s">
+      <c r="A102" s="152" t="s">
         <v>352</v>
       </c>
       <c r="B102" s="33" t="s">
@@ -11261,7 +11257,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="30" customFormat="1">
-      <c r="A103" s="162"/>
+      <c r="A103" s="153"/>
       <c r="B103" s="37" t="s">
         <v>354</v>
       </c>
@@ -11279,10 +11275,10 @@
       <c r="B105" s="40"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="165" t="s">
+      <c r="A107" s="147" t="s">
         <v>357</v>
       </c>
-      <c r="B107" s="164"/>
+      <c r="B107" s="146"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="61"/>
@@ -11453,17 +11449,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="148" t="s">
+      <c r="A137" s="166" t="s">
         <v>386</v>
       </c>
-      <c r="B137" s="149"/>
+      <c r="B137" s="167"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="150"/>
-      <c r="B138" s="151"/>
+      <c r="A138" s="168"/>
+      <c r="B138" s="169"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="145" t="s">
+      <c r="A139" s="154" t="s">
         <v>387</v>
       </c>
       <c r="B139" s="63" t="s">
@@ -11471,31 +11467,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="146"/>
+      <c r="A140" s="155"/>
       <c r="B140" s="64" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="146"/>
+      <c r="A141" s="155"/>
       <c r="B141" s="64" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="146"/>
+      <c r="A142" s="155"/>
       <c r="B142" s="64" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="147"/>
+      <c r="A143" s="156"/>
       <c r="B143" s="66" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="145" t="s">
+      <c r="A144" s="154" t="s">
         <v>393</v>
       </c>
       <c r="B144" s="63" t="s">
@@ -11503,43 +11499,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="146"/>
+      <c r="A145" s="155"/>
       <c r="B145" s="64" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="146"/>
+      <c r="A146" s="155"/>
       <c r="B146" s="64" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="146"/>
+      <c r="A147" s="155"/>
       <c r="B147" s="64" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="146"/>
+      <c r="A148" s="155"/>
       <c r="B148" s="64" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="146"/>
+      <c r="A149" s="155"/>
       <c r="B149" s="64" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="147"/>
+      <c r="A150" s="156"/>
       <c r="B150" s="66" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="145" t="s">
+      <c r="A151" s="154" t="s">
         <v>401</v>
       </c>
       <c r="B151" s="63" t="s">
@@ -11547,187 +11543,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="146"/>
+      <c r="A152" s="155"/>
       <c r="B152" s="64" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="146"/>
+      <c r="A153" s="155"/>
       <c r="B153" s="64" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="146"/>
+      <c r="A154" s="155"/>
       <c r="B154" s="64" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="146"/>
+      <c r="A155" s="155"/>
       <c r="B155" s="64" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="146"/>
+      <c r="A156" s="155"/>
       <c r="B156" s="64" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="146"/>
+      <c r="A157" s="155"/>
       <c r="B157" s="64" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="146"/>
+      <c r="A158" s="155"/>
       <c r="B158" s="64" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="146"/>
+      <c r="A159" s="155"/>
       <c r="B159" s="64" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="146"/>
+      <c r="A160" s="155"/>
       <c r="B160" s="64" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="146"/>
+      <c r="A161" s="155"/>
       <c r="B161" s="64" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="146"/>
+      <c r="A162" s="155"/>
       <c r="B162" s="64" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="146"/>
+      <c r="A163" s="155"/>
       <c r="B163" s="64" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="146"/>
+      <c r="A164" s="155"/>
       <c r="B164" s="64" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="146"/>
+      <c r="A165" s="155"/>
       <c r="B165" s="64" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="146"/>
+      <c r="A166" s="155"/>
       <c r="B166" s="64" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="146"/>
+      <c r="A167" s="155"/>
       <c r="B167" s="64" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="146"/>
+      <c r="A168" s="155"/>
       <c r="B168" s="64" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="146"/>
+      <c r="A169" s="155"/>
       <c r="B169" s="64" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="146"/>
+      <c r="A170" s="155"/>
       <c r="B170" s="64" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="146"/>
+      <c r="A171" s="155"/>
       <c r="B171" s="64" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="146"/>
+      <c r="A172" s="155"/>
       <c r="B172" s="64" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="146"/>
+      <c r="A173" s="155"/>
       <c r="B173" s="64" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="146"/>
+      <c r="A174" s="155"/>
       <c r="B174" s="64" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="146"/>
+      <c r="A175" s="155"/>
       <c r="B175" s="64" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="146"/>
+      <c r="A176" s="155"/>
       <c r="B176" s="64" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="146"/>
+      <c r="A177" s="155"/>
       <c r="B177" s="64" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="146"/>
+      <c r="A178" s="155"/>
       <c r="B178" s="64" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="146"/>
+      <c r="A179" s="155"/>
       <c r="B179" s="64" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="146"/>
+      <c r="A180" s="155"/>
       <c r="B180" s="64" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="147"/>
+      <c r="A181" s="156"/>
       <c r="B181" s="66" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="145" t="s">
+      <c r="A182" s="154" t="s">
         <v>433</v>
       </c>
       <c r="B182" s="63" t="s">
@@ -11735,19 +11731,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="146"/>
+      <c r="A183" s="155"/>
       <c r="B183" s="64" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="147"/>
+      <c r="A184" s="156"/>
       <c r="B184" s="66" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="145" t="s">
+      <c r="A185" s="154" t="s">
         <v>437</v>
       </c>
       <c r="B185" s="63" t="s">
@@ -11755,25 +11751,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="146"/>
+      <c r="A186" s="155"/>
       <c r="B186" s="64" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="146"/>
+      <c r="A187" s="155"/>
       <c r="B187" s="64" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="147"/>
+      <c r="A188" s="156"/>
       <c r="B188" s="66" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="145" t="s">
+      <c r="A189" s="154" t="s">
         <v>442</v>
       </c>
       <c r="B189" s="63" t="s">
@@ -11781,13 +11777,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="147"/>
+      <c r="A190" s="156"/>
       <c r="B190" s="66" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="145" t="s">
+      <c r="A191" s="154" t="s">
         <v>445</v>
       </c>
       <c r="B191" s="63" t="s">
@@ -11795,49 +11791,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="146"/>
+      <c r="A192" s="155"/>
       <c r="B192" s="64" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="146"/>
+      <c r="A193" s="155"/>
       <c r="B193" s="64" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="146"/>
+      <c r="A194" s="155"/>
       <c r="B194" s="64" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="146"/>
+      <c r="A195" s="155"/>
       <c r="B195" s="64" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="146"/>
+      <c r="A196" s="155"/>
       <c r="B196" s="64" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="146"/>
+      <c r="A197" s="155"/>
       <c r="B197" s="64" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="147"/>
+      <c r="A198" s="156"/>
       <c r="B198" s="66" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="145" t="s">
+      <c r="A199" s="154" t="s">
         <v>454</v>
       </c>
       <c r="B199" s="63" t="s">
@@ -11845,13 +11841,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="147"/>
+      <c r="A200" s="156"/>
       <c r="B200" s="66" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="145" t="s">
+      <c r="A201" s="154" t="s">
         <v>457</v>
       </c>
       <c r="B201" s="63" t="s">
@@ -11859,19 +11855,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="146"/>
+      <c r="A202" s="155"/>
       <c r="B202" s="64" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="147"/>
+      <c r="A203" s="156"/>
       <c r="B203" s="66" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="145" t="s">
+      <c r="A204" s="154" t="s">
         <v>461</v>
       </c>
       <c r="B204" s="63" t="s">
@@ -11879,19 +11875,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="146"/>
+      <c r="A205" s="155"/>
       <c r="B205" s="64" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="146"/>
+      <c r="A206" s="155"/>
       <c r="B206" s="64" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="147"/>
+      <c r="A207" s="156"/>
       <c r="B207" s="66" t="s">
         <v>465</v>
       </c>
@@ -11905,7 +11901,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="145" t="s">
+      <c r="A209" s="154" t="s">
         <v>468</v>
       </c>
       <c r="B209" s="63" t="s">
@@ -11913,13 +11909,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="147"/>
+      <c r="A210" s="156"/>
       <c r="B210" s="66" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="145" t="s">
+      <c r="A211" s="154" t="s">
         <v>471</v>
       </c>
       <c r="B211" s="63" t="s">
@@ -11927,19 +11923,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="146"/>
+      <c r="A212" s="155"/>
       <c r="B212" s="64" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="147"/>
+      <c r="A213" s="156"/>
       <c r="B213" s="66" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="145" t="s">
+      <c r="A214" s="154" t="s">
         <v>475</v>
       </c>
       <c r="B214" s="63" t="s">
@@ -11947,19 +11943,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="146"/>
+      <c r="A215" s="155"/>
       <c r="B215" s="64" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="147"/>
+      <c r="A216" s="156"/>
       <c r="B216" s="66" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="145" t="s">
+      <c r="A217" s="154" t="s">
         <v>479</v>
       </c>
       <c r="B217" s="63" t="s">
@@ -11967,13 +11963,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="146"/>
+      <c r="A218" s="155"/>
       <c r="B218" s="64" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="147"/>
+      <c r="A219" s="156"/>
       <c r="B219" s="66" t="s">
         <v>482</v>
       </c>
@@ -11987,7 +11983,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="145" t="s">
+      <c r="A221" s="154" t="s">
         <v>485</v>
       </c>
       <c r="B221" s="63" t="s">
@@ -11995,13 +11991,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="147"/>
+      <c r="A222" s="156"/>
       <c r="B222" s="66" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="145" t="s">
+      <c r="A223" s="154" t="s">
         <v>488</v>
       </c>
       <c r="B223" s="63" t="s">
@@ -12009,31 +12005,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="146"/>
+      <c r="A224" s="155"/>
       <c r="B224" s="64" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="146"/>
+      <c r="A225" s="155"/>
       <c r="B225" s="64" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="146"/>
+      <c r="A226" s="155"/>
       <c r="B226" s="64" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="147"/>
+      <c r="A227" s="156"/>
       <c r="B227" s="66" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="145" t="s">
+      <c r="A228" s="154" t="s">
         <v>494</v>
       </c>
       <c r="B228" s="63" t="s">
@@ -12041,31 +12037,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="146"/>
+      <c r="A229" s="155"/>
       <c r="B229" s="64" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="146"/>
+      <c r="A230" s="155"/>
       <c r="B230" s="64" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="146"/>
+      <c r="A231" s="155"/>
       <c r="B231" s="64" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="146"/>
+      <c r="A232" s="155"/>
       <c r="B232" s="64" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="147"/>
+      <c r="A233" s="156"/>
       <c r="B233" s="66" t="s">
         <v>500</v>
       </c>
@@ -12079,16 +12075,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="166" t="s">
+      <c r="A236" s="148" t="s">
         <v>503</v>
       </c>
-      <c r="B236" s="167"/>
+      <c r="B236" s="149"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="165" t="s">
+      <c r="A239" s="147" t="s">
         <v>504</v>
       </c>
-      <c r="B239" s="164"/>
+      <c r="B239" s="146"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="61"/>
@@ -12187,10 +12183,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="168" t="s">
+      <c r="A257" s="150" t="s">
         <v>520</v>
       </c>
-      <c r="B257" s="169"/>
+      <c r="B257" s="151"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="61"/>
@@ -12366,11 +12362,11 @@
         <v>549</v>
       </c>
     </row>
-    <row r="288" spans="1:2" ht="23">
-      <c r="A288" s="152" t="s">
+    <row r="288" spans="1:2" ht="22.5">
+      <c r="A288" s="157" t="s">
         <v>550</v>
       </c>
-      <c r="B288" s="153"/>
+      <c r="B288" s="158"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="69"/>
@@ -12561,6 +12557,30 @@
   </sheetData>
   <sheetProtection password="EC2B" sheet="1" objects="1"/>
   <mergeCells count="40">
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A288:B288"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A20"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A40:A46"/>
+    <mergeCell ref="A47:A56"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="A60:A65"/>
+    <mergeCell ref="A66:A71"/>
+    <mergeCell ref="A72:A88"/>
+    <mergeCell ref="A89:A94"/>
+    <mergeCell ref="A95:A101"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A107:B107"/>
     <mergeCell ref="A236:B236"/>
@@ -12577,30 +12597,6 @@
     <mergeCell ref="A199:A200"/>
     <mergeCell ref="A201:A203"/>
     <mergeCell ref="A204:A207"/>
-    <mergeCell ref="A288:B288"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A20"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A25:A35"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A40:A46"/>
-    <mergeCell ref="A47:A56"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="A60:A65"/>
-    <mergeCell ref="A66:A71"/>
-    <mergeCell ref="A72:A88"/>
-    <mergeCell ref="A89:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="36" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12611,21 +12607,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IV105"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="38.08984375" style="30" customWidth="1"/>
-    <col min="2" max="2" width="76.6328125" style="30" customWidth="1"/>
+    <col min="1" max="1" width="38.125" style="30" customWidth="1"/>
+    <col min="2" max="2" width="76.625" style="30" customWidth="1"/>
     <col min="3" max="256" width="9" style="30"/>
     <col min="257" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="170" t="s">
         <v>582</v>
       </c>
-      <c r="B1" s="183"/>
-    </row>
-    <row r="2" spans="1:2" s="28" customFormat="1" ht="15">
+      <c r="B1" s="171"/>
+    </row>
+    <row r="2" spans="1:2" s="28" customFormat="1" ht="14.25">
       <c r="A2" s="31" t="s">
         <v>583</v>
       </c>
@@ -12637,7 +12633,7 @@
       <c r="A3" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="172" t="s">
         <v>1</v>
       </c>
     </row>
@@ -12645,25 +12641,25 @@
       <c r="A4" s="34" t="s">
         <v>585</v>
       </c>
-      <c r="B4" s="174"/>
+      <c r="B4" s="173"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="B5" s="174"/>
+      <c r="B5" s="173"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="B6" s="175"/>
+      <c r="B6" s="174"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="35" t="s">
         <v>245</v>
       </c>
-      <c r="B7" s="173" t="s">
+      <c r="B7" s="172" t="s">
         <v>586</v>
       </c>
     </row>
@@ -12671,25 +12667,25 @@
       <c r="A8" s="36" t="s">
         <v>246</v>
       </c>
-      <c r="B8" s="174"/>
+      <c r="B8" s="173"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="33" t="s">
         <v>353</v>
       </c>
-      <c r="B9" s="174"/>
+      <c r="B9" s="173"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="37" t="s">
         <v>354</v>
       </c>
-      <c r="B10" s="175"/>
+      <c r="B10" s="174"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="B11" s="173" t="s">
+      <c r="B11" s="172" t="s">
         <v>2</v>
       </c>
     </row>
@@ -12697,85 +12693,85 @@
       <c r="A12" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="B12" s="174"/>
+      <c r="B12" s="173"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="38" t="s">
         <v>250</v>
       </c>
-      <c r="B13" s="174"/>
+      <c r="B13" s="173"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="34" t="s">
         <v>251</v>
       </c>
-      <c r="B14" s="174"/>
+      <c r="B14" s="173"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="B15" s="174"/>
+      <c r="B15" s="173"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="B16" s="174"/>
+      <c r="B16" s="173"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="B17" s="174"/>
+      <c r="B17" s="173"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="34" t="s">
         <v>587</v>
       </c>
-      <c r="B18" s="174"/>
+      <c r="B18" s="173"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="B19" s="174"/>
+      <c r="B19" s="173"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="34" t="s">
         <v>588</v>
       </c>
-      <c r="B20" s="174"/>
+      <c r="B20" s="173"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="39" t="s">
         <v>589</v>
       </c>
-      <c r="B21" s="174"/>
+      <c r="B21" s="173"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="39" t="s">
         <v>260</v>
       </c>
-      <c r="B22" s="174"/>
+      <c r="B22" s="173"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="40" t="s">
         <v>242</v>
       </c>
-      <c r="B23" s="184"/>
+      <c r="B23" s="175"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="B24" s="185"/>
+      <c r="B24" s="176"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="33" t="s">
         <v>590</v>
       </c>
-      <c r="B25" s="173" t="s">
+      <c r="B25" s="172" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12783,61 +12779,61 @@
       <c r="A26" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="B26" s="174"/>
+      <c r="B26" s="173"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="34" t="s">
         <v>270</v>
       </c>
-      <c r="B27" s="174"/>
+      <c r="B27" s="173"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="B28" s="174"/>
+      <c r="B28" s="173"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="34" t="s">
         <v>272</v>
       </c>
-      <c r="B29" s="174"/>
+      <c r="B29" s="173"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="34" t="s">
         <v>591</v>
       </c>
-      <c r="B30" s="174"/>
+      <c r="B30" s="173"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="B31" s="174"/>
+      <c r="B31" s="173"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="34" t="s">
         <v>592</v>
       </c>
-      <c r="B32" s="174"/>
+      <c r="B32" s="173"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="34" t="s">
         <v>593</v>
       </c>
-      <c r="B33" s="174"/>
+      <c r="B33" s="173"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="41" t="s">
         <v>263</v>
       </c>
-      <c r="B34" s="175"/>
+      <c r="B34" s="174"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="42" t="s">
         <v>594</v>
       </c>
-      <c r="B35" s="173" t="s">
+      <c r="B35" s="172" t="s">
         <v>595</v>
       </c>
     </row>
@@ -12845,13 +12841,13 @@
       <c r="A36" s="41" t="s">
         <v>596</v>
       </c>
-      <c r="B36" s="175"/>
+      <c r="B36" s="174"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="34" t="s">
         <v>278</v>
       </c>
-      <c r="B37" s="173" t="s">
+      <c r="B37" s="172" t="s">
         <v>6</v>
       </c>
     </row>
@@ -12859,19 +12855,19 @@
       <c r="A38" s="39" t="s">
         <v>279</v>
       </c>
-      <c r="B38" s="174"/>
+      <c r="B38" s="173"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="B39" s="174"/>
+      <c r="B39" s="173"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="33" t="s">
         <v>597</v>
       </c>
-      <c r="B40" s="173" t="s">
+      <c r="B40" s="172" t="s">
         <v>598</v>
       </c>
     </row>
@@ -12879,37 +12875,37 @@
       <c r="A41" s="34" t="s">
         <v>599</v>
       </c>
-      <c r="B41" s="174"/>
+      <c r="B41" s="173"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="B42" s="174"/>
+      <c r="B42" s="173"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="34" t="s">
         <v>600</v>
       </c>
-      <c r="B43" s="174"/>
+      <c r="B43" s="173"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="34" t="s">
         <v>601</v>
       </c>
-      <c r="B44" s="174"/>
+      <c r="B44" s="173"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="34" t="s">
         <v>288</v>
       </c>
-      <c r="B45" s="174"/>
+      <c r="B45" s="173"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="37" t="s">
         <v>289</v>
       </c>
-      <c r="B46" s="175"/>
+      <c r="B46" s="174"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="43" t="s">
@@ -12923,7 +12919,7 @@
       <c r="A48" s="34" t="s">
         <v>292</v>
       </c>
-      <c r="B48" s="173" t="s">
+      <c r="B48" s="172" t="s">
         <v>602</v>
       </c>
     </row>
@@ -12931,13 +12927,13 @@
       <c r="A49" s="34" t="s">
         <v>293</v>
       </c>
-      <c r="B49" s="175"/>
+      <c r="B49" s="174"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="B50" s="173" t="s">
+      <c r="B50" s="172" t="s">
         <v>10</v>
       </c>
     </row>
@@ -12945,25 +12941,25 @@
       <c r="A51" s="34" t="s">
         <v>297</v>
       </c>
-      <c r="B51" s="174"/>
+      <c r="B51" s="173"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="34" t="s">
         <v>294</v>
       </c>
-      <c r="B52" s="174"/>
+      <c r="B52" s="173"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="34" t="s">
         <v>295</v>
       </c>
-      <c r="B53" s="174"/>
+      <c r="B53" s="173"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="41" t="s">
         <v>296</v>
       </c>
-      <c r="B54" s="175"/>
+      <c r="B54" s="174"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="43" t="s">
@@ -12977,7 +12973,7 @@
       <c r="A56" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="B56" s="173" t="s">
+      <c r="B56" s="172" t="s">
         <v>13</v>
       </c>
     </row>
@@ -12985,19 +12981,19 @@
       <c r="A57" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="B57" s="174"/>
+      <c r="B57" s="173"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="37" t="s">
         <v>304</v>
       </c>
-      <c r="B58" s="175"/>
+      <c r="B58" s="174"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="34" t="s">
         <v>338</v>
       </c>
-      <c r="B59" s="176" t="s">
+      <c r="B59" s="180" t="s">
         <v>12</v>
       </c>
     </row>
@@ -13005,37 +13001,37 @@
       <c r="A60" s="34" t="s">
         <v>342</v>
       </c>
-      <c r="B60" s="177"/>
+      <c r="B60" s="181"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="34" t="s">
         <v>339</v>
       </c>
-      <c r="B61" s="177"/>
+      <c r="B61" s="181"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="B62" s="177"/>
+      <c r="B62" s="181"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="34" t="s">
         <v>343</v>
       </c>
-      <c r="B63" s="177"/>
+      <c r="B63" s="181"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="45" t="s">
         <v>341</v>
       </c>
-      <c r="B64" s="178"/>
+      <c r="B64" s="182"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="34" t="s">
         <v>605</v>
       </c>
-      <c r="B65" s="179" t="s">
+      <c r="B65" s="183" t="s">
         <v>606</v>
       </c>
     </row>
@@ -13043,26 +13039,26 @@
       <c r="A66" s="34" t="s">
         <v>281</v>
       </c>
-      <c r="B66" s="180"/>
+      <c r="B66" s="184"/>
       <c r="E66" s="46"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="39" t="s">
         <v>300</v>
       </c>
-      <c r="B67" s="180"/>
+      <c r="B67" s="184"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="B68" s="181"/>
+      <c r="B68" s="185"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="47" t="s">
         <v>306</v>
       </c>
-      <c r="B69" s="176" t="s">
+      <c r="B69" s="180" t="s">
         <v>15</v>
       </c>
     </row>
@@ -13070,37 +13066,37 @@
       <c r="A70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="B70" s="177"/>
+      <c r="B70" s="181"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="48" t="s">
         <v>308</v>
       </c>
-      <c r="B71" s="177"/>
+      <c r="B71" s="181"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="34" t="s">
         <v>309</v>
       </c>
-      <c r="B72" s="177"/>
+      <c r="B72" s="181"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="B73" s="177"/>
+      <c r="B73" s="181"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="34" t="s">
         <v>311</v>
       </c>
-      <c r="B74" s="178"/>
+      <c r="B74" s="182"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="47" t="s">
         <v>313</v>
       </c>
-      <c r="B75" s="176" t="s">
+      <c r="B75" s="180" t="s">
         <v>16</v>
       </c>
     </row>
@@ -13108,139 +13104,139 @@
       <c r="A76" s="34" t="s">
         <v>314</v>
       </c>
-      <c r="B76" s="177"/>
+      <c r="B76" s="181"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="34" t="s">
         <v>315</v>
       </c>
-      <c r="B77" s="177"/>
+      <c r="B77" s="181"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="34" t="s">
         <v>316</v>
       </c>
-      <c r="B78" s="177"/>
+      <c r="B78" s="181"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="B79" s="177"/>
+      <c r="B79" s="181"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="B80" s="177"/>
+      <c r="B80" s="181"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="B81" s="177"/>
+      <c r="B81" s="181"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="B82" s="177"/>
+      <c r="B82" s="181"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="34" t="s">
         <v>322</v>
       </c>
-      <c r="B83" s="177"/>
+      <c r="B83" s="181"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="34" t="s">
         <v>323</v>
       </c>
-      <c r="B84" s="177"/>
+      <c r="B84" s="181"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="34" t="s">
         <v>324</v>
       </c>
-      <c r="B85" s="177"/>
+      <c r="B85" s="181"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="49" t="s">
         <v>325</v>
       </c>
-      <c r="B86" s="177"/>
+      <c r="B86" s="181"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="B87" s="177"/>
+      <c r="B87" s="181"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="34" t="s">
         <v>327</v>
       </c>
-      <c r="B88" s="177"/>
+      <c r="B88" s="181"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="34" t="s">
         <v>328</v>
       </c>
-      <c r="B89" s="177"/>
+      <c r="B89" s="181"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="B90" s="177"/>
+      <c r="B90" s="181"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="B91" s="177"/>
+      <c r="B91" s="181"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="34" t="s">
         <v>331</v>
       </c>
-      <c r="B92" s="177"/>
+      <c r="B92" s="181"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="34" t="s">
         <v>332</v>
       </c>
-      <c r="B93" s="177"/>
+      <c r="B93" s="181"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="49" t="s">
         <v>333</v>
       </c>
-      <c r="B94" s="177"/>
+      <c r="B94" s="181"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="49" t="s">
         <v>334</v>
       </c>
-      <c r="B95" s="177"/>
+      <c r="B95" s="181"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="49" t="s">
         <v>335</v>
       </c>
-      <c r="B96" s="177"/>
+      <c r="B96" s="181"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="34" t="s">
         <v>336</v>
       </c>
-      <c r="B97" s="177"/>
+      <c r="B97" s="181"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="50" t="s">
         <v>345</v>
       </c>
-      <c r="B98" s="170" t="s">
+      <c r="B98" s="177" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13248,37 +13244,37 @@
       <c r="A99" s="51" t="s">
         <v>346</v>
       </c>
-      <c r="B99" s="171"/>
+      <c r="B99" s="178"/>
     </row>
     <row r="100" spans="1:2" s="29" customFormat="1">
       <c r="A100" s="51" t="s">
         <v>347</v>
       </c>
-      <c r="B100" s="171"/>
+      <c r="B100" s="178"/>
     </row>
     <row r="101" spans="1:2" s="29" customFormat="1">
       <c r="A101" s="51" t="s">
         <v>348</v>
       </c>
-      <c r="B101" s="171"/>
+      <c r="B101" s="178"/>
     </row>
     <row r="102" spans="1:2" s="29" customFormat="1">
       <c r="A102" s="51" t="s">
         <v>349</v>
       </c>
-      <c r="B102" s="171"/>
+      <c r="B102" s="178"/>
     </row>
     <row r="103" spans="1:2" s="29" customFormat="1">
       <c r="A103" s="51" t="s">
         <v>350</v>
       </c>
-      <c r="B103" s="171"/>
+      <c r="B103" s="178"/>
     </row>
     <row r="104" spans="1:2" s="29" customFormat="1">
       <c r="A104" s="45" t="s">
         <v>351</v>
       </c>
-      <c r="B104" s="172"/>
+      <c r="B104" s="179"/>
     </row>
     <row r="105" spans="1:2" s="29" customFormat="1">
       <c r="A105" s="52" t="s">
@@ -13290,22 +13286,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="36" type="noConversion"/>
   <hyperlinks>
@@ -13340,12 +13336,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IV240"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18" style="10" customWidth="1"/>
-    <col min="2" max="2" width="35.453125" style="23" customWidth="1"/>
-    <col min="3" max="256" width="9.08984375" style="10"/>
-    <col min="257" max="16384" width="9.08984375" style="1"/>
+    <col min="2" max="2" width="35.5" style="23" customWidth="1"/>
+    <col min="3" max="256" width="9.125" style="10"/>
+    <col min="257" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27" customHeight="1">
@@ -15280,10 +15276,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B179"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18" style="16" customWidth="1"/>
-    <col min="2" max="2" width="35.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16729,10 +16725,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="103.7265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="103.75" style="2" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16760,7 +16756,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28">
+    <row r="4" spans="1:2" ht="27">
       <c r="B4" s="2" t="s">
         <v>1446</v>
       </c>
@@ -16770,9 +16766,9 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="84">
+    <row r="6" spans="1:2" ht="67.5">
       <c r="B6" s="2" t="s">
-        <v>1448</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -16780,7 +16776,7 @@
         <v>1441</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -16796,62 +16792,62 @@
         <v>1444</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="B13" s="7" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="27">
+      <c r="B14" s="7" t="s">
         <v>1451</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="28">
-      <c r="B14" s="7" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" s="7" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" s="7" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="B17" s="7" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="40.5">
+      <c r="B18" s="7" t="s">
         <v>1455</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="42">
-      <c r="B18" s="7" t="s">
-        <v>1456</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="B19" s="7" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="B20" s="7" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="B21" s="7" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="B22" s="7" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="27">
+      <c r="B23" s="7" t="s">
         <v>1460</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="28">
-      <c r="B23" s="7" t="s">
-        <v>1461</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -16862,7 +16858,7 @@
         <v>1441</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -16873,12 +16869,12 @@
         <v>43245</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="84">
+    <row r="28" spans="1:2" ht="67.5">
       <c r="A28" s="9" t="s">
         <v>1444</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -16889,7 +16885,7 @@
         <v>1441</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -16900,12 +16896,12 @@
         <v>43126</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="322">
+    <row r="32" spans="1:2" ht="297">
       <c r="A32" s="9" t="s">
         <v>1444</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -16916,7 +16912,7 @@
         <v>1441</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -16932,7 +16928,7 @@
         <v>1444</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -16940,7 +16936,7 @@
         <v>1441</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -16956,7 +16952,7 @@
         <v>1444</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -16965,7 +16961,7 @@
     <row r="42" spans="1:2">
       <c r="A42" s="189"/>
       <c r="B42" s="11" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -16975,7 +16971,7 @@
     <row r="44" spans="1:2">
       <c r="A44" s="189"/>
       <c r="B44" s="11" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -16985,7 +16981,7 @@
     <row r="46" spans="1:2">
       <c r="A46" s="189"/>
       <c r="B46" s="11" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -16995,7 +16991,7 @@
     <row r="48" spans="1:2">
       <c r="A48" s="189"/>
       <c r="B48" s="11" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -17005,7 +17001,7 @@
     <row r="50" spans="1:2">
       <c r="A50" s="189"/>
       <c r="B50" s="11" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -17015,17 +17011,17 @@
     <row r="52" spans="1:2">
       <c r="A52" s="189"/>
       <c r="B52" s="11" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="189"/>
       <c r="B53" s="11"/>
     </row>
-    <row r="54" spans="1:2" ht="28">
+    <row r="54" spans="1:2" ht="27">
       <c r="A54" s="189"/>
       <c r="B54" s="11" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -17035,27 +17031,27 @@
     <row r="56" spans="1:2">
       <c r="A56" s="189"/>
       <c r="B56" s="11" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="189"/>
       <c r="B57" s="11"/>
     </row>
-    <row r="58" spans="1:2" ht="28">
+    <row r="58" spans="1:2" ht="27">
       <c r="A58" s="189"/>
       <c r="B58" s="11" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="189"/>
       <c r="B59" s="11"/>
     </row>
-    <row r="60" spans="1:2" ht="28">
+    <row r="60" spans="1:2" ht="27">
       <c r="A60" s="189"/>
       <c r="B60" s="11" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -17065,7 +17061,7 @@
     <row r="62" spans="1:2">
       <c r="A62" s="189"/>
       <c r="B62" s="11" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -17075,7 +17071,7 @@
     <row r="64" spans="1:2">
       <c r="A64" s="189"/>
       <c r="B64" s="11" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -17087,7 +17083,7 @@
         <v>1441</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -17098,12 +17094,12 @@
         <v>42685</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="112">
+    <row r="68" spans="1:2" ht="108">
       <c r="A68" s="10" t="s">
         <v>1444</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -17111,7 +17107,7 @@
         <v>1441</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="30.75" customHeight="1">
@@ -17119,67 +17115,67 @@
         <v>1444</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="30.75" customHeight="1">
       <c r="B72" s="15" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="33.75" customHeight="1">
       <c r="B73" s="14" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="33.75" customHeight="1">
       <c r="B74" s="15" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="33.75" customHeight="1">
       <c r="B75" s="14" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="33.75" customHeight="1">
       <c r="B76" s="15" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="48.75" customHeight="1">
       <c r="B77" s="14" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="48.75" customHeight="1">
       <c r="B78" s="15" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="26.25" customHeight="1">
       <c r="B79" s="14" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="30" customHeight="1">
       <c r="B80" s="15" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="48.75" customHeight="1">
       <c r="B81" s="14" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="32.25" customHeight="1">
       <c r="B82" s="15" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="14.25" customHeight="1">
       <c r="B83" s="14" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -17187,15 +17183,15 @@
         <v>1441</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>1498</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" ht="56">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="54">
       <c r="A86" s="10" t="s">
         <v>1444</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -17203,7 +17199,7 @@
         <v>1441</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -17211,32 +17207,32 @@
         <v>1444</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="B90" s="2" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="B91" s="2" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="B92" s="2" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="B93" s="2" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="B94" s="2" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
   </sheetData>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetInfoRegist.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetInfoRegist.xlsx
@@ -1,13 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitHome\2.1.7\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760" firstSheet="2" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
   </bookViews>
   <sheets>
-    <sheet name="资产要素登记" sheetId="1" r:id="rId1"/>
+    <sheet name="资产负债登记要素" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
     <sheet name="各要素值域输入规则" sheetId="3" r:id="rId3"/>
     <sheet name="各类资产应填要素列说明" sheetId="4" r:id="rId4"/>
@@ -19,7 +24,7 @@
     <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
-    <definedName name="bd" localSheetId="0">资产要素登记!#REF!</definedName>
+    <definedName name="bd" localSheetId="0">资产负债登记要素!#REF!</definedName>
     <definedName name="bd">[1]资产要素登记!#REF!</definedName>
   </definedNames>
   <calcPr calcId="144525" concurrentCalc="0"/>
@@ -191,6 +196,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>份额面值</t>
@@ -203,6 +209,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -213,6 +220,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>*</t>
@@ -223,6 +231,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>起息日</t>
@@ -439,6 +448,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -449,6 +459,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>*</t>
@@ -459,6 +470,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>股票</t>
@@ -469,6 +481,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>/</t>
@@ -479,6 +492,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>企业名称</t>
@@ -563,6 +577,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>票面利率</t>
@@ -573,6 +588,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>%</t>
@@ -621,6 +637,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -631,6 +648,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>*资管计划名称</t>
@@ -661,6 +679,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -671,6 +690,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>*</t>
@@ -681,6 +701,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>资金运用方式</t>
@@ -693,6 +714,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -703,6 +725,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>*</t>
@@ -713,6 +736,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>资金运用行业</t>
@@ -758,6 +782,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -768,6 +793,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>*</t>
@@ -778,6 +804,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>其他合计费率%</t>
@@ -796,6 +823,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 资产收益率</t>
@@ -806,6 +834,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>%</t>
@@ -824,6 +853,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>项目收益率（利率）</t>
@@ -833,6 +863,7 @@
         <b/>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>%</t>
@@ -845,6 +876,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>*付息频率（个月</t>
@@ -854,6 +886,7 @@
         <b/>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>/</t>
@@ -863,6 +896,7 @@
         <b/>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>次）</t>
@@ -983,6 +1017,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 利率</t>
@@ -993,6 +1028,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>%</t>
@@ -1028,6 +1064,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1.为使导入成功，所有单元格都必须保持模板原有的格式，如须粘贴数据请使用</t>
@@ -1037,6 +1074,7 @@
         <sz val="12"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“选择性粘贴”</t>
@@ -1046,6 +1084,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>并只</t>
@@ -1055,6 +1094,7 @@
         <sz val="12"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“粘贴数值”</t>
@@ -1063,6 +1103,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>。</t>
@@ -1077,6 +1118,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>3</t>
@@ -1086,6 +1128,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>.“资产</t>
@@ -1095,6 +1138,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>/</t>
@@ -1104,6 +1148,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>负债类别”、“基准利率种类”、“所属国家或地区”、“发行机构所属行业”、“资金运用行业”、“用款项目所属行业”的填写内容请参照“</t>
@@ -1113,6 +1158,7 @@
         <sz val="12"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>各要素值域输入规则</t>
@@ -1122,6 +1168,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>”页。</t>
@@ -1133,6 +1180,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>4.A-E列为所有资产/负债均需要填写的要素</t>
@@ -1142,6 +1190,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>，其余列根据所属“资产/负债类别”填写对应的列，具体请参照“</t>
@@ -1151,6 +1200,7 @@
         <sz val="12"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>各类资产应填要素列说明</t>
@@ -1160,6 +1210,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>”页。</t>
@@ -1171,6 +1222,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>5.“融资人所属地区”参照附件《</t>
@@ -1180,6 +1232,7 @@
         <sz val="12"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>中国行政区划划分</t>
@@ -1189,6 +1242,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>》按照省（市）、地（市）、县（市）三级方式填报，该附件可在理财系统的“模板下载”模块中下载。</t>
@@ -1204,6 +1258,7 @@
         <sz val="18"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>资产类别</t>
@@ -1213,6 +1268,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">输入规则：   </t>
@@ -1222,6 +1278,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">                                                   </t>
@@ -1232,6 +1289,7 @@
         <sz val="16"/>
         <color indexed="60"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>左侧列对应一级分类；右侧列对应其下二级分类</t>
@@ -1241,6 +1299,7 @@
         <sz val="11"/>
         <color indexed="60"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">  </t>
@@ -1250,6 +1309,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">                                       </t>
@@ -1259,6 +1319,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">        </t>
@@ -1268,6 +1329,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">  </t>
@@ -1348,6 +1410,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>2</t>
@@ -1357,6 +1420,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">201 </t>
@@ -1366,6 +1430,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>信贷资产收益权转让</t>
@@ -1380,6 +1445,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>2299</t>
@@ -1389,6 +1455,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 其他新增可投资资产</t>
@@ -1406,6 +1473,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -1415,6 +1483,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">210 </t>
@@ -1424,6 +1493,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>信用证</t>
@@ -1456,6 +1526,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -1465,6 +1536,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>209 债权融资类产品</t>
@@ -1476,6 +1548,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1299</t>
@@ -1485,6 +1558,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 其他非标准化债权类投资</t>
@@ -1502,6 +1576,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1305</t>
@@ -1511,6 +1586,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 股票</t>
@@ -1520,6 +1596,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>(</t>
@@ -1529,6 +1606,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>一级市场</t>
@@ -1538,6 +1616,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>)</t>
@@ -1576,6 +1655,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1499</t>
@@ -1585,6 +1665,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 其他金融衍生品</t>
@@ -1597,6 +1678,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -1607,6 +1689,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>0</t>
@@ -1617,6 +1700,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>、代客境外理财投资QDII</t>
@@ -1652,6 +1736,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1503 QDII</t>
@@ -1661,6 +1746,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>结构性票据</t>
@@ -1672,6 +1758,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1599</t>
@@ -1681,6 +1768,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 其他代客境外理财投资QDII</t>
@@ -1693,6 +1781,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -1703,6 +1792,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -1713,6 +1803,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>、商品类资产</t>
@@ -1734,6 +1825,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -1744,6 +1836,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>2</t>
@@ -1754,6 +1847,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>、另类资产</t>
@@ -1784,6 +1878,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -1794,6 +1889,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>3</t>
@@ -1804,6 +1900,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>、公募基金</t>
@@ -1834,6 +1931,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -1844,6 +1942,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>4</t>
@@ -1854,6 +1953,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>、私募基金</t>
@@ -1938,6 +2038,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -1948,6 +2049,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>6</t>
@@ -1958,6 +2060,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>、委外投资——协议方式</t>
@@ -1991,6 +2094,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -2001,6 +2105,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>7、同业拆入及卖出回购</t>
@@ -2015,6 +2120,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1902</t>
@@ -2024,6 +2130,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 卖出回购</t>
@@ -2036,6 +2143,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -2046,6 +2154,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>8</t>
@@ -2056,6 +2165,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>、其他（负债）</t>
@@ -2067,6 +2177,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>2000 其他</t>
@@ -2076,6 +2187,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>(</t>
@@ -2085,6 +2197,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>负债</t>
@@ -2094,6 +2207,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>)</t>
@@ -2106,6 +2220,7 @@
         <sz val="18"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>基准利率种类</t>
@@ -2115,6 +2230,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>输入规则：</t>
@@ -2207,6 +2323,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>9</t>
@@ -2216,6 +2333,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>9</t>
@@ -2225,6 +2343,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 其他</t>
@@ -2237,6 +2356,7 @@
         <sz val="18"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">发行机构所属行业、
@@ -2249,6 +2369,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>输入规则：按照《国家统计局行业》分类，细化到二级分类</t>
@@ -2609,6 +2730,7 @@
         <sz val="18"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">融资人所属地区
@@ -2619,6 +2741,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>输入规则：参照附件《中国行政区划划分》按照省（市）、地（市）、县（市）三级方式填报</t>
@@ -2631,6 +2754,7 @@
         <sz val="18"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>结构性存款挂钩标的类别</t>
@@ -2641,6 +2765,7 @@
         <sz val="18"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">/标的类别
@@ -2651,6 +2776,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>输入规则：可多选，用逗号分隔；
@@ -2661,6 +2787,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">03 </t>
@@ -2670,6 +2797,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>股票，</t>
@@ -2679,6 +2807,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">08 </t>
@@ -2688,6 +2817,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>指数</t>
@@ -2745,6 +2875,7 @@
         <sz val="18"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>具体类别</t>
@@ -2754,6 +2885,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">输入规则：  </t>
@@ -2853,6 +2985,7 @@
         <sz val="18"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>主体评级</t>
@@ -2862,6 +2995,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">输入规则：  </t>
@@ -2984,6 +3118,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>111</t>
@@ -2993,6 +3128,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>6</t>
@@ -3002,6 +3138,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 资产支持证券</t>
@@ -3013,6 +3150,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>111</t>
@@ -3022,6 +3160,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>7</t>
@@ -3031,6 +3170,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 外国债券</t>
@@ -3060,6 +3200,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -3069,6 +3210,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>210 信用证</t>
@@ -3113,6 +3255,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>2</t>
@@ -3122,6 +3265,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -3131,6 +3275,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 其他(负债)</t>
@@ -3143,6 +3288,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>所属国家或地区</t>
@@ -3152,6 +3298,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>填写规则：下边列表中的一个（</t>
@@ -3161,6 +3308,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>例如：AFG 或者AFG 阿富汗</t>
@@ -3170,6 +3318,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
@@ -5713,6 +5862,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>6、对于“其他非标准化债权投资”二级分类的资产，新增“担保方式”</t>
@@ -5722,6 +5872,7 @@
         <sz val="11"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“担保情况说明”</t>
@@ -5731,6 +5882,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>要素；</t>
@@ -5768,6 +5920,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1.0.1</t>
@@ -5777,6 +5930,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>4</t>
@@ -5788,6 +5942,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
@@ -5799,6 +5954,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">2.对于类别为“买入返售”的资产、“卖出回购”的负债必填的“回购标的类别”要素,“02 股票”删除。
@@ -5815,6 +5971,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>9.</t>
@@ -5824,6 +5981,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“资金实际投向”要素的值域做调整</t>
@@ -5833,6 +5991,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>:</t>
@@ -5842,6 +6001,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>不得再选择“</t>
@@ -5851,6 +6011,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">02 </t>
@@ -5860,6 +6021,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>货币市场工具类”、“</t>
@@ -5869,6 +6031,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">14 </t>
@@ -5878,6 +6041,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>私募基金类”和“</t>
@@ -5887,6 +6051,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">15 </t>
@@ -5896,6 +6061,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>产业基金类”，增加“</t>
@@ -5905,6 +6071,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">18 </t>
@@ -5914,6 +6081,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>同业存单类”和“</t>
@@ -5923,6 +6091,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">19 </t>
@@ -5932,6 +6101,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">拆放同业及买入返售类”
@@ -5942,6 +6112,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">10.币种的值域去掉可选形式，依照币种填写规则填写币种代码
@@ -5952,6 +6123,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>11.所属国家或地区代码变更。</t>
@@ -5975,6 +6147,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>2.在“拆出/</t>
@@ -5984,6 +6157,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>逆回购资产</t>
@@ -5993,6 +6167,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>||</t>
@@ -6002,6 +6177,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>拆入</t>
@@ -6011,6 +6187,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>/</t>
@@ -6020,6 +6197,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>正回购资产”下增加对“年利率”、“回购标的金额”的数据验证：不能输入负数；</t>
@@ -6029,6 +6207,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">           </t>
@@ -6043,6 +6222,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>4.</t>
@@ -6052,6 +6232,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>在“票据类</t>
@@ -6061,6 +6242,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>/</t>
@@ -6070,6 +6252,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>信用证类资产”下增加对“合计金额”、“贴现利率”的数据验证：不能输入负数；</t>
@@ -6093,6 +6276,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>9.在“贵金属/</t>
@@ -6102,6 +6286,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>商品”下增加对“期限（天）”、“资产价值”的数据验证：不能输入负数；</t>
@@ -6113,6 +6298,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>10</t>
@@ -6122,6 +6308,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>.在“资产管理计划”下增加对“金额”、“预期最高收益率”“管理费率</t>
@@ -6131,6 +6318,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>%</t>
@@ -6140,6 +6328,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>”、“托管费率</t>
@@ -6149,6 +6338,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>%</t>
@@ -6158,6 +6348,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>”、“交易相关合计费率”、“中介服务机构合计费率”、“其他合计费率”的数据验证：不能输入负数；</t>
@@ -6169,6 +6360,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>11</t>
@@ -6178,6 +6370,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>.在“其他债券及货币市场工具</t>
@@ -6187,6 +6380,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>/</t>
@@ -6196,6 +6390,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>非标准化债权类</t>
@@ -6205,6 +6400,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>/</t>
@@ -6214,6 +6410,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>权益类</t>
@@ -6223,6 +6420,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>/</t>
@@ -6232,6 +6430,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>代客境外理财投资</t>
@@ -6241,6 +6440,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>QDII/</t>
@@ -6250,6 +6450,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>理财直接融资工具</t>
@@ -6259,6 +6460,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>/</t>
@@ -6268,6 +6470,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>信贷资产流转项目”下增加对“金额”的数据验证：不能输入负数；</t>
@@ -6279,6 +6482,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>12</t>
@@ -6288,6 +6492,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>.在“另类资产”下增加对“资产价值”的数据验证：不能输入负数；</t>
@@ -6299,6 +6504,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>13</t>
@@ -6308,6 +6514,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>.在“其他（负债）类资产”下增加对“期限（天）”、“负债规模”、“利率”的数据验证：不能输入负数；</t>
@@ -6347,6 +6554,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>5.票据类/信用证类资产中</t>
@@ -6356,6 +6564,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>增加“是否属于买入返售”要素</t>
@@ -6401,6 +6610,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1.0.</t>
@@ -6410,6 +6620,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>8</t>
@@ -6462,18 +6673,21 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6481,6 +6695,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6488,6 +6703,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -6496,6 +6712,7 @@
       <sz val="18"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6503,6 +6720,7 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6510,6 +6728,7 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6517,11 +6736,13 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -6530,12 +6751,14 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6543,6 +6766,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -6550,6 +6774,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -6558,6 +6783,7 @@
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6565,6 +6791,7 @@
       <sz val="18"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -6572,6 +6799,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -6580,6 +6808,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -6588,12 +6817,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -6601,6 +6832,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -6609,6 +6841,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -6616,12 +6849,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6629,12 +6864,14 @@
       <sz val="16"/>
       <color indexed="60"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="60"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6642,6 +6879,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6649,6 +6887,7 @@
       <sz val="11"/>
       <color indexed="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6656,29 +6895,34 @@
       <sz val="18"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -6686,17 +6930,20 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -7633,28 +7880,58 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -7665,35 +7942,59 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7716,58 +8017,40 @@
     <xf numFmtId="49" fontId="16" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7776,47 +8059,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8163,533 +8410,533 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:JM11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="44.5" style="75" customWidth="1"/>
-    <col min="2" max="2" width="15.375" style="76"/>
-    <col min="3" max="3" width="22.75" style="76" customWidth="1"/>
-    <col min="4" max="4" width="18.5" style="76" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="77" customWidth="1"/>
-    <col min="6" max="6" width="14.125" style="75"/>
-    <col min="7" max="7" width="10.75" style="78" customWidth="1"/>
-    <col min="8" max="8" width="10.375" style="79" customWidth="1"/>
-    <col min="9" max="9" width="9.5" style="79"/>
-    <col min="10" max="10" width="11.25" style="80" customWidth="1"/>
-    <col min="11" max="11" width="11.625" style="76" customWidth="1"/>
-    <col min="12" max="12" width="19.75" style="76"/>
-    <col min="13" max="13" width="25.25" style="76"/>
-    <col min="14" max="14" width="20.75" style="77"/>
-    <col min="15" max="15" width="12.75" style="81" customWidth="1"/>
-    <col min="16" max="17" width="12.25" style="82" customWidth="1"/>
-    <col min="18" max="18" width="15.375" style="82"/>
-    <col min="19" max="19" width="10.875" style="82"/>
-    <col min="20" max="20" width="30.875" style="82"/>
-    <col min="21" max="22" width="35.375" style="82"/>
-    <col min="23" max="23" width="22.25" style="82" customWidth="1"/>
-    <col min="24" max="24" width="22.375" style="82" customWidth="1"/>
-    <col min="25" max="25" width="19.875" style="82" customWidth="1"/>
-    <col min="26" max="26" width="9.5" style="75"/>
-    <col min="27" max="27" width="9.5" style="76"/>
+    <col min="1" max="1" width="44.453125" style="75" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" style="76"/>
+    <col min="3" max="3" width="22.7265625" style="76" customWidth="1"/>
+    <col min="4" max="4" width="18.453125" style="76" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="77" customWidth="1"/>
+    <col min="6" max="6" width="14.08984375" style="75"/>
+    <col min="7" max="7" width="10.7265625" style="78" customWidth="1"/>
+    <col min="8" max="8" width="10.36328125" style="79" customWidth="1"/>
+    <col min="9" max="9" width="9.453125" style="79"/>
+    <col min="10" max="10" width="11.26953125" style="80" customWidth="1"/>
+    <col min="11" max="11" width="11.6328125" style="76" customWidth="1"/>
+    <col min="12" max="12" width="19.7265625" style="76"/>
+    <col min="13" max="13" width="25.26953125" style="76"/>
+    <col min="14" max="14" width="20.7265625" style="77"/>
+    <col min="15" max="15" width="12.7265625" style="81" customWidth="1"/>
+    <col min="16" max="17" width="12.26953125" style="82" customWidth="1"/>
+    <col min="18" max="18" width="15.36328125" style="82"/>
+    <col min="19" max="19" width="10.90625" style="82"/>
+    <col min="20" max="20" width="30.90625" style="82"/>
+    <col min="21" max="22" width="35.36328125" style="82"/>
+    <col min="23" max="23" width="22.26953125" style="82" customWidth="1"/>
+    <col min="24" max="24" width="22.36328125" style="82" customWidth="1"/>
+    <col min="25" max="25" width="19.90625" style="82" customWidth="1"/>
+    <col min="26" max="26" width="9.453125" style="75"/>
+    <col min="27" max="27" width="9.453125" style="76"/>
     <col min="28" max="28" width="9" style="76"/>
-    <col min="29" max="29" width="22.875" style="76" customWidth="1"/>
-    <col min="30" max="30" width="11.625" style="80" customWidth="1"/>
-    <col min="31" max="31" width="11.625" style="76" customWidth="1"/>
-    <col min="32" max="32" width="14.125" style="76"/>
+    <col min="29" max="29" width="22.90625" style="76" customWidth="1"/>
+    <col min="30" max="30" width="11.6328125" style="80" customWidth="1"/>
+    <col min="31" max="31" width="11.6328125" style="76" customWidth="1"/>
+    <col min="32" max="32" width="14.08984375" style="76"/>
     <col min="33" max="33" width="56" style="83"/>
-    <col min="34" max="34" width="18.125" style="75" customWidth="1"/>
-    <col min="35" max="35" width="19.75" style="76"/>
-    <col min="36" max="36" width="13.625" style="76" customWidth="1"/>
-    <col min="37" max="37" width="15.375" style="78" customWidth="1"/>
-    <col min="38" max="38" width="15.375" style="79" customWidth="1"/>
-    <col min="39" max="39" width="9.125" style="76" customWidth="1"/>
-    <col min="40" max="40" width="9.375" style="76" customWidth="1"/>
-    <col min="41" max="41" width="11.5" style="76" customWidth="1"/>
-    <col min="42" max="42" width="19.875" style="76" customWidth="1"/>
-    <col min="43" max="45" width="20.125" style="80"/>
-    <col min="46" max="47" width="21.875" style="84" customWidth="1"/>
-    <col min="48" max="48" width="18.875" style="76" customWidth="1"/>
-    <col min="49" max="49" width="11.875" style="76" customWidth="1"/>
-    <col min="50" max="51" width="24.25" style="76" customWidth="1"/>
-    <col min="52" max="52" width="15.5" style="80" customWidth="1"/>
-    <col min="53" max="55" width="13.25" style="80" customWidth="1"/>
-    <col min="56" max="57" width="19.5" style="80" customWidth="1"/>
-    <col min="58" max="58" width="23.875" style="80" customWidth="1"/>
+    <col min="34" max="34" width="18.08984375" style="75" customWidth="1"/>
+    <col min="35" max="35" width="19.7265625" style="76"/>
+    <col min="36" max="36" width="13.6328125" style="76" customWidth="1"/>
+    <col min="37" max="37" width="15.36328125" style="78" customWidth="1"/>
+    <col min="38" max="38" width="15.36328125" style="79" customWidth="1"/>
+    <col min="39" max="39" width="9.08984375" style="76" customWidth="1"/>
+    <col min="40" max="40" width="9.36328125" style="76" customWidth="1"/>
+    <col min="41" max="41" width="11.453125" style="76" customWidth="1"/>
+    <col min="42" max="42" width="19.90625" style="76" customWidth="1"/>
+    <col min="43" max="45" width="20.08984375" style="80"/>
+    <col min="46" max="47" width="21.90625" style="84" customWidth="1"/>
+    <col min="48" max="48" width="18.90625" style="76" customWidth="1"/>
+    <col min="49" max="49" width="11.90625" style="76" customWidth="1"/>
+    <col min="50" max="51" width="24.26953125" style="76" customWidth="1"/>
+    <col min="52" max="52" width="15.453125" style="80" customWidth="1"/>
+    <col min="53" max="55" width="13.26953125" style="80" customWidth="1"/>
+    <col min="56" max="57" width="19.453125" style="80" customWidth="1"/>
+    <col min="58" max="58" width="23.90625" style="80" customWidth="1"/>
     <col min="59" max="59" width="9" style="76"/>
-    <col min="60" max="60" width="22.75" style="76" customWidth="1"/>
-    <col min="61" max="61" width="36.125" style="76" customWidth="1"/>
-    <col min="62" max="62" width="28.625" style="76"/>
-    <col min="63" max="64" width="33.125" style="76"/>
-    <col min="65" max="65" width="12.375" style="76" customWidth="1"/>
-    <col min="66" max="66" width="22.875" style="76" customWidth="1"/>
-    <col min="67" max="67" width="35.375" style="76"/>
-    <col min="68" max="68" width="25.25" style="76"/>
-    <col min="69" max="69" width="29.625" style="76"/>
-    <col min="70" max="71" width="15.375" style="76" customWidth="1"/>
-    <col min="72" max="72" width="20.875" style="76" customWidth="1"/>
-    <col min="73" max="73" width="15.375" style="76" customWidth="1"/>
-    <col min="74" max="74" width="20.75" style="76" customWidth="1"/>
-    <col min="75" max="75" width="16.625" style="76" customWidth="1"/>
-    <col min="76" max="76" width="15.75" style="76" customWidth="1"/>
-    <col min="77" max="77" width="19.375" style="76" customWidth="1"/>
-    <col min="78" max="79" width="14.5" style="76" customWidth="1"/>
-    <col min="80" max="85" width="16.625" style="76" customWidth="1"/>
-    <col min="86" max="90" width="19.5" style="76" customWidth="1"/>
-    <col min="91" max="91" width="19.5" style="85" customWidth="1"/>
+    <col min="60" max="60" width="22.7265625" style="76" customWidth="1"/>
+    <col min="61" max="61" width="36.08984375" style="76" customWidth="1"/>
+    <col min="62" max="62" width="28.6328125" style="76"/>
+    <col min="63" max="64" width="33.08984375" style="76"/>
+    <col min="65" max="65" width="12.36328125" style="76" customWidth="1"/>
+    <col min="66" max="66" width="22.90625" style="76" customWidth="1"/>
+    <col min="67" max="67" width="35.36328125" style="76"/>
+    <col min="68" max="68" width="25.26953125" style="76"/>
+    <col min="69" max="69" width="29.6328125" style="76"/>
+    <col min="70" max="71" width="15.36328125" style="76" customWidth="1"/>
+    <col min="72" max="72" width="20.90625" style="76" customWidth="1"/>
+    <col min="73" max="73" width="15.36328125" style="76" customWidth="1"/>
+    <col min="74" max="74" width="20.7265625" style="76" customWidth="1"/>
+    <col min="75" max="75" width="16.6328125" style="76" customWidth="1"/>
+    <col min="76" max="76" width="15.7265625" style="76" customWidth="1"/>
+    <col min="77" max="77" width="19.36328125" style="76" customWidth="1"/>
+    <col min="78" max="79" width="14.453125" style="76" customWidth="1"/>
+    <col min="80" max="85" width="16.6328125" style="76" customWidth="1"/>
+    <col min="86" max="90" width="19.453125" style="76" customWidth="1"/>
+    <col min="91" max="91" width="19.453125" style="85" customWidth="1"/>
     <col min="92" max="92" width="14" style="76" customWidth="1"/>
-    <col min="93" max="93" width="14.375" style="76" customWidth="1"/>
+    <col min="93" max="93" width="14.36328125" style="76" customWidth="1"/>
     <col min="94" max="97" width="19" style="76" customWidth="1"/>
-    <col min="98" max="98" width="14.875" style="80" customWidth="1"/>
-    <col min="99" max="99" width="19.75" style="77"/>
-    <col min="100" max="100" width="17.625" style="76" customWidth="1"/>
-    <col min="101" max="101" width="19.75" style="76"/>
-    <col min="102" max="102" width="16.375" style="76" customWidth="1"/>
-    <col min="103" max="103" width="13.5" style="84" customWidth="1"/>
-    <col min="104" max="104" width="14.625" style="78" customWidth="1"/>
+    <col min="98" max="98" width="14.90625" style="80" customWidth="1"/>
+    <col min="99" max="99" width="19.7265625" style="77"/>
+    <col min="100" max="100" width="17.6328125" style="76" customWidth="1"/>
+    <col min="101" max="101" width="19.7265625" style="76"/>
+    <col min="102" max="102" width="16.36328125" style="76" customWidth="1"/>
+    <col min="103" max="103" width="13.453125" style="84" customWidth="1"/>
+    <col min="104" max="104" width="14.6328125" style="78" customWidth="1"/>
     <col min="105" max="105" width="22" style="124"/>
     <col min="106" max="106" width="22" style="84"/>
     <col min="107" max="107" width="22" style="84" customWidth="1"/>
     <col min="108" max="108" width="22" style="79" customWidth="1"/>
-    <col min="109" max="109" width="13.875" style="79" customWidth="1"/>
-    <col min="110" max="110" width="16.5" style="76" customWidth="1"/>
-    <col min="111" max="111" width="16.125" style="80" customWidth="1"/>
-    <col min="112" max="112" width="16.875" style="75" customWidth="1"/>
-    <col min="113" max="113" width="17.875" style="76"/>
-    <col min="114" max="114" width="9.75" style="76"/>
-    <col min="115" max="117" width="17.875" style="76" customWidth="1"/>
-    <col min="118" max="118" width="26.5" style="76"/>
-    <col min="119" max="120" width="30.875" style="76"/>
-    <col min="121" max="122" width="26.5" style="76" customWidth="1"/>
+    <col min="109" max="109" width="13.90625" style="79" customWidth="1"/>
+    <col min="110" max="110" width="16.453125" style="76" customWidth="1"/>
+    <col min="111" max="111" width="16.08984375" style="80" customWidth="1"/>
+    <col min="112" max="112" width="16.90625" style="75" customWidth="1"/>
+    <col min="113" max="113" width="17.90625" style="76"/>
+    <col min="114" max="114" width="9.7265625" style="76"/>
+    <col min="115" max="117" width="17.90625" style="76" customWidth="1"/>
+    <col min="118" max="118" width="26.453125" style="76"/>
+    <col min="119" max="120" width="30.90625" style="76"/>
+    <col min="121" max="122" width="26.453125" style="76" customWidth="1"/>
     <col min="123" max="123" width="9" style="75"/>
-    <col min="124" max="124" width="13.875" style="78"/>
-    <col min="125" max="126" width="11.5" style="76" customWidth="1"/>
-    <col min="127" max="127" width="19.375" style="75" customWidth="1"/>
-    <col min="128" max="128" width="10.625" style="76" customWidth="1"/>
-    <col min="129" max="129" width="10.125" style="82" customWidth="1"/>
+    <col min="124" max="124" width="13.90625" style="78"/>
+    <col min="125" max="126" width="11.453125" style="76" customWidth="1"/>
+    <col min="127" max="127" width="19.36328125" style="75" customWidth="1"/>
+    <col min="128" max="128" width="10.6328125" style="76" customWidth="1"/>
+    <col min="129" max="129" width="10.08984375" style="82" customWidth="1"/>
     <col min="130" max="130" width="11" style="82" customWidth="1"/>
-    <col min="131" max="131" width="21.5" style="82" customWidth="1"/>
+    <col min="131" max="131" width="21.453125" style="82" customWidth="1"/>
     <col min="132" max="133" width="10" style="82" customWidth="1"/>
-    <col min="134" max="134" width="11.875" style="86" customWidth="1"/>
-    <col min="135" max="135" width="21.75" style="82" customWidth="1"/>
-    <col min="136" max="136" width="14.375" style="82" customWidth="1"/>
-    <col min="137" max="137" width="11.875" style="87" customWidth="1"/>
-    <col min="138" max="138" width="21.125" style="86" customWidth="1"/>
-    <col min="139" max="139" width="14.625" style="82" customWidth="1"/>
-    <col min="140" max="140" width="28.5" style="76" customWidth="1"/>
-    <col min="141" max="141" width="16.875" style="75" customWidth="1"/>
-    <col min="142" max="143" width="9.5" style="76"/>
+    <col min="134" max="134" width="11.90625" style="86" customWidth="1"/>
+    <col min="135" max="135" width="21.7265625" style="82" customWidth="1"/>
+    <col min="136" max="136" width="14.36328125" style="82" customWidth="1"/>
+    <col min="137" max="137" width="11.90625" style="87" customWidth="1"/>
+    <col min="138" max="138" width="21.08984375" style="86" customWidth="1"/>
+    <col min="139" max="139" width="14.6328125" style="82" customWidth="1"/>
+    <col min="140" max="140" width="28.453125" style="76" customWidth="1"/>
+    <col min="141" max="141" width="16.90625" style="75" customWidth="1"/>
+    <col min="142" max="143" width="9.453125" style="76"/>
     <col min="144" max="144" width="9" style="76"/>
-    <col min="145" max="145" width="12.625" style="80" customWidth="1"/>
-    <col min="146" max="146" width="11.375" style="77" customWidth="1"/>
-    <col min="147" max="147" width="16.25" style="75" customWidth="1"/>
-    <col min="148" max="148" width="16.125" style="76" customWidth="1"/>
-    <col min="149" max="149" width="15.875" style="76" customWidth="1"/>
-    <col min="150" max="150" width="11.25" style="76" customWidth="1"/>
-    <col min="151" max="151" width="23.75" style="77"/>
-    <col min="152" max="152" width="16.25" style="75" customWidth="1"/>
-    <col min="153" max="155" width="10.25" style="76" customWidth="1"/>
-    <col min="156" max="156" width="10.875" style="80" customWidth="1"/>
-    <col min="157" max="157" width="20.75" style="84" customWidth="1"/>
+    <col min="145" max="145" width="12.6328125" style="80" customWidth="1"/>
+    <col min="146" max="146" width="11.36328125" style="77" customWidth="1"/>
+    <col min="147" max="147" width="16.26953125" style="75" customWidth="1"/>
+    <col min="148" max="148" width="16.08984375" style="76" customWidth="1"/>
+    <col min="149" max="149" width="15.90625" style="76" customWidth="1"/>
+    <col min="150" max="150" width="11.26953125" style="76" customWidth="1"/>
+    <col min="151" max="151" width="23.7265625" style="77"/>
+    <col min="152" max="152" width="16.26953125" style="75" customWidth="1"/>
+    <col min="153" max="155" width="10.26953125" style="76" customWidth="1"/>
+    <col min="156" max="156" width="10.90625" style="80" customWidth="1"/>
+    <col min="157" max="157" width="20.7265625" style="84" customWidth="1"/>
     <col min="158" max="159" width="28" style="80"/>
-    <col min="160" max="160" width="26.5" style="76" customWidth="1"/>
-    <col min="161" max="161" width="29.125" style="76" customWidth="1"/>
-    <col min="162" max="162" width="14.75" style="76" customWidth="1"/>
+    <col min="160" max="160" width="26.453125" style="76" customWidth="1"/>
+    <col min="161" max="161" width="29.08984375" style="76" customWidth="1"/>
+    <col min="162" max="162" width="14.7265625" style="76" customWidth="1"/>
     <col min="163" max="163" width="15" style="76" customWidth="1"/>
-    <col min="164" max="164" width="22.875" style="80" customWidth="1"/>
-    <col min="165" max="165" width="23.625" style="80" customWidth="1"/>
-    <col min="166" max="166" width="21.625" style="78" customWidth="1"/>
-    <col min="167" max="167" width="24.75" style="78" customWidth="1"/>
-    <col min="168" max="168" width="12.25" style="121" customWidth="1"/>
-    <col min="169" max="169" width="15.25" style="82" customWidth="1"/>
-    <col min="170" max="170" width="28.375" style="82" customWidth="1"/>
-    <col min="171" max="171" width="25.25" style="82" customWidth="1"/>
-    <col min="172" max="172" width="17.75" style="82" customWidth="1"/>
-    <col min="173" max="173" width="9.75" style="82" customWidth="1"/>
+    <col min="164" max="164" width="22.90625" style="80" customWidth="1"/>
+    <col min="165" max="165" width="23.6328125" style="80" customWidth="1"/>
+    <col min="166" max="166" width="21.6328125" style="78" customWidth="1"/>
+    <col min="167" max="167" width="24.7265625" style="78" customWidth="1"/>
+    <col min="168" max="168" width="12.26953125" style="121" customWidth="1"/>
+    <col min="169" max="169" width="15.26953125" style="82" customWidth="1"/>
+    <col min="170" max="170" width="28.36328125" style="82" customWidth="1"/>
+    <col min="171" max="171" width="25.26953125" style="82" customWidth="1"/>
+    <col min="172" max="172" width="17.7265625" style="82" customWidth="1"/>
+    <col min="173" max="173" width="9.7265625" style="82" customWidth="1"/>
     <col min="174" max="174" width="11" style="82" customWidth="1"/>
-    <col min="175" max="175" width="19.375" style="88"/>
-    <col min="176" max="176" width="17.5" style="82" customWidth="1"/>
-    <col min="177" max="177" width="17.625" style="82" customWidth="1"/>
-    <col min="178" max="178" width="17.5" style="82" customWidth="1"/>
-    <col min="179" max="179" width="18.5" style="82" customWidth="1"/>
-    <col min="180" max="180" width="18.25" style="82" customWidth="1"/>
-    <col min="181" max="181" width="15.375" style="82"/>
-    <col min="182" max="182" width="17.5" style="82" customWidth="1"/>
-    <col min="183" max="183" width="17.125" style="87" customWidth="1"/>
-    <col min="184" max="184" width="16.5" style="87" customWidth="1"/>
-    <col min="185" max="185" width="12.75" style="82" customWidth="1"/>
-    <col min="186" max="186" width="12.875" style="82" customWidth="1"/>
-    <col min="187" max="188" width="14.25" style="87" customWidth="1"/>
+    <col min="175" max="175" width="19.36328125" style="88"/>
+    <col min="176" max="176" width="17.453125" style="82" customWidth="1"/>
+    <col min="177" max="177" width="17.6328125" style="82" customWidth="1"/>
+    <col min="178" max="178" width="17.453125" style="82" customWidth="1"/>
+    <col min="179" max="179" width="18.453125" style="82" customWidth="1"/>
+    <col min="180" max="180" width="18.26953125" style="82" customWidth="1"/>
+    <col min="181" max="181" width="15.36328125" style="82"/>
+    <col min="182" max="182" width="17.453125" style="82" customWidth="1"/>
+    <col min="183" max="183" width="17.08984375" style="87" customWidth="1"/>
+    <col min="184" max="184" width="16.453125" style="87" customWidth="1"/>
+    <col min="185" max="185" width="12.7265625" style="82" customWidth="1"/>
+    <col min="186" max="186" width="12.90625" style="82" customWidth="1"/>
+    <col min="187" max="188" width="14.26953125" style="87" customWidth="1"/>
     <col min="189" max="189" width="21" style="87"/>
-    <col min="190" max="190" width="25.5" style="87"/>
-    <col min="191" max="191" width="17.875" style="87"/>
-    <col min="192" max="192" width="16.25" style="75" customWidth="1"/>
+    <col min="190" max="190" width="25.453125" style="87"/>
+    <col min="191" max="191" width="17.90625" style="87"/>
+    <col min="192" max="192" width="16.26953125" style="75" customWidth="1"/>
     <col min="193" max="193" width="9" style="76"/>
-    <col min="194" max="194" width="12.5" style="84" customWidth="1"/>
+    <col min="194" max="194" width="12.453125" style="84" customWidth="1"/>
     <col min="195" max="195" width="11" style="78" customWidth="1"/>
-    <col min="196" max="196" width="13.125" style="89" customWidth="1"/>
+    <col min="196" max="196" width="13.08984375" style="89" customWidth="1"/>
     <col min="197" max="197" width="20" style="76" customWidth="1"/>
-    <col min="198" max="198" width="15.375" style="76"/>
-    <col min="199" max="199" width="17.5" style="76"/>
-    <col min="200" max="200" width="11.625" style="78" customWidth="1"/>
-    <col min="201" max="202" width="11.625" style="76" customWidth="1"/>
-    <col min="203" max="203" width="17.625" style="76"/>
-    <col min="204" max="204" width="19.75" style="76"/>
-    <col min="205" max="205" width="23.25" style="80"/>
-    <col min="206" max="206" width="23.25" style="90"/>
-    <col min="207" max="207" width="11.625" style="76" customWidth="1"/>
-    <col min="208" max="208" width="35.375" style="76"/>
-    <col min="209" max="209" width="38.5" style="76"/>
-    <col min="210" max="210" width="28.625" style="76"/>
-    <col min="211" max="212" width="33.125" style="76"/>
-    <col min="213" max="213" width="11.625" style="76" customWidth="1"/>
-    <col min="214" max="214" width="16.375" style="76"/>
-    <col min="215" max="215" width="19.75" style="76"/>
-    <col min="216" max="216" width="35.375" style="76"/>
-    <col min="217" max="217" width="25.25" style="76"/>
-    <col min="218" max="218" width="29.625" style="76"/>
-    <col min="219" max="224" width="18.625" style="76"/>
-    <col min="225" max="225" width="16.625" style="76" customWidth="1"/>
-    <col min="226" max="226" width="18.625" style="76"/>
-    <col min="227" max="227" width="17.625" style="75"/>
-    <col min="228" max="230" width="13.125" style="76" customWidth="1"/>
-    <col min="231" max="231" width="13.125" style="78" customWidth="1"/>
-    <col min="232" max="232" width="14.75" style="89" customWidth="1"/>
-    <col min="233" max="233" width="16.125" style="75" customWidth="1"/>
-    <col min="234" max="236" width="16.125" style="76" customWidth="1"/>
-    <col min="237" max="237" width="21.75" style="76"/>
-    <col min="238" max="238" width="17.5" style="76"/>
-    <col min="239" max="239" width="27.625" style="76" customWidth="1"/>
+    <col min="198" max="198" width="15.36328125" style="76"/>
+    <col min="199" max="199" width="17.453125" style="76"/>
+    <col min="200" max="200" width="11.6328125" style="78" customWidth="1"/>
+    <col min="201" max="202" width="11.6328125" style="76" customWidth="1"/>
+    <col min="203" max="203" width="17.6328125" style="76"/>
+    <col min="204" max="204" width="19.7265625" style="76"/>
+    <col min="205" max="205" width="23.26953125" style="80"/>
+    <col min="206" max="206" width="23.26953125" style="90"/>
+    <col min="207" max="207" width="11.6328125" style="76" customWidth="1"/>
+    <col min="208" max="208" width="35.36328125" style="76"/>
+    <col min="209" max="209" width="38.453125" style="76"/>
+    <col min="210" max="210" width="28.6328125" style="76"/>
+    <col min="211" max="212" width="33.08984375" style="76"/>
+    <col min="213" max="213" width="11.6328125" style="76" customWidth="1"/>
+    <col min="214" max="214" width="16.36328125" style="76"/>
+    <col min="215" max="215" width="19.7265625" style="76"/>
+    <col min="216" max="216" width="35.36328125" style="76"/>
+    <col min="217" max="217" width="25.26953125" style="76"/>
+    <col min="218" max="218" width="29.6328125" style="76"/>
+    <col min="219" max="224" width="18.6328125" style="76"/>
+    <col min="225" max="225" width="16.6328125" style="76" customWidth="1"/>
+    <col min="226" max="226" width="18.6328125" style="76"/>
+    <col min="227" max="227" width="17.6328125" style="75"/>
+    <col min="228" max="230" width="13.08984375" style="76" customWidth="1"/>
+    <col min="231" max="231" width="13.08984375" style="78" customWidth="1"/>
+    <col min="232" max="232" width="14.7265625" style="89" customWidth="1"/>
+    <col min="233" max="233" width="16.08984375" style="75" customWidth="1"/>
+    <col min="234" max="236" width="16.08984375" style="76" customWidth="1"/>
+    <col min="237" max="237" width="21.7265625" style="76"/>
+    <col min="238" max="238" width="17.453125" style="76"/>
+    <col min="239" max="239" width="27.6328125" style="76" customWidth="1"/>
     <col min="240" max="240" width="23" style="76"/>
-    <col min="241" max="242" width="19.75" style="76"/>
-    <col min="243" max="243" width="19.75" style="76" customWidth="1"/>
-    <col min="244" max="244" width="29.625" style="76"/>
-    <col min="245" max="245" width="34.125" style="76"/>
-    <col min="246" max="246" width="34.125" style="76" customWidth="1"/>
-    <col min="247" max="247" width="34.125" style="77" customWidth="1"/>
-    <col min="248" max="252" width="34.125" style="76" customWidth="1"/>
-    <col min="253" max="253" width="34.125" style="91" customWidth="1"/>
-    <col min="254" max="260" width="34.125" style="76" customWidth="1"/>
-    <col min="261" max="261" width="34.125" style="92" customWidth="1"/>
-    <col min="262" max="267" width="34.125" style="74" customWidth="1"/>
-    <col min="268" max="268" width="15.75" style="82" customWidth="1"/>
+    <col min="241" max="242" width="19.7265625" style="76"/>
+    <col min="243" max="243" width="19.7265625" style="76" customWidth="1"/>
+    <col min="244" max="244" width="29.6328125" style="76"/>
+    <col min="245" max="245" width="34.08984375" style="76"/>
+    <col min="246" max="246" width="34.08984375" style="76" customWidth="1"/>
+    <col min="247" max="247" width="34.08984375" style="77" customWidth="1"/>
+    <col min="248" max="252" width="34.08984375" style="76" customWidth="1"/>
+    <col min="253" max="253" width="34.08984375" style="91" customWidth="1"/>
+    <col min="254" max="260" width="34.08984375" style="76" customWidth="1"/>
+    <col min="261" max="261" width="34.08984375" style="92" customWidth="1"/>
+    <col min="262" max="267" width="34.08984375" style="74" customWidth="1"/>
+    <col min="268" max="268" width="15.7265625" style="82" customWidth="1"/>
     <col min="269" max="269" width="9" style="82"/>
-    <col min="270" max="270" width="12.5" style="86" customWidth="1"/>
+    <col min="270" max="270" width="12.453125" style="86" customWidth="1"/>
     <col min="271" max="271" width="11" style="88" customWidth="1"/>
-    <col min="272" max="272" width="13.125" style="87" customWidth="1"/>
-    <col min="273" max="273" width="16.5" style="75" customWidth="1"/>
+    <col min="272" max="272" width="13.08984375" style="87" customWidth="1"/>
+    <col min="273" max="273" width="16.453125" style="75" customWidth="1"/>
     <col min="274" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:273" s="72" customFormat="1">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="128" t="s">
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="125" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="130"/>
-      <c r="L1" s="129"/>
-      <c r="M1" s="129"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="132" t="s">
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="126"/>
+      <c r="M1" s="126"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
-      <c r="R1" s="132"/>
-      <c r="S1" s="132"/>
-      <c r="T1" s="132"/>
-      <c r="U1" s="132"/>
-      <c r="V1" s="132"/>
-      <c r="W1" s="132"/>
-      <c r="X1" s="132"/>
-      <c r="Y1" s="132"/>
-      <c r="Z1" s="128" t="s">
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="137"/>
+      <c r="Y1" s="137"/>
+      <c r="Z1" s="125" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="129"/>
-      <c r="AB1" s="129"/>
-      <c r="AC1" s="129"/>
-      <c r="AD1" s="129"/>
-      <c r="AE1" s="129"/>
-      <c r="AF1" s="129"/>
-      <c r="AG1" s="131"/>
-      <c r="AH1" s="125" t="s">
+      <c r="AA1" s="126"/>
+      <c r="AB1" s="126"/>
+      <c r="AC1" s="126"/>
+      <c r="AD1" s="126"/>
+      <c r="AE1" s="126"/>
+      <c r="AF1" s="126"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="141" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="126"/>
-      <c r="AJ1" s="126"/>
-      <c r="AK1" s="126"/>
-      <c r="AL1" s="126"/>
-      <c r="AM1" s="126"/>
-      <c r="AN1" s="126"/>
-      <c r="AO1" s="126"/>
-      <c r="AP1" s="126"/>
-      <c r="AQ1" s="126"/>
-      <c r="AR1" s="126"/>
-      <c r="AS1" s="126"/>
-      <c r="AT1" s="126"/>
-      <c r="AU1" s="126"/>
-      <c r="AV1" s="126"/>
-      <c r="AW1" s="126"/>
-      <c r="AX1" s="126"/>
-      <c r="AY1" s="126"/>
-      <c r="AZ1" s="126"/>
-      <c r="BA1" s="126"/>
-      <c r="BB1" s="126"/>
-      <c r="BC1" s="126"/>
-      <c r="BD1" s="126"/>
-      <c r="BE1" s="126"/>
-      <c r="BF1" s="126"/>
-      <c r="BG1" s="126"/>
-      <c r="BH1" s="126"/>
-      <c r="BI1" s="126"/>
-      <c r="BJ1" s="126"/>
-      <c r="BK1" s="126"/>
-      <c r="BL1" s="126"/>
-      <c r="BM1" s="126"/>
-      <c r="BN1" s="126"/>
-      <c r="BO1" s="126"/>
-      <c r="BP1" s="126"/>
-      <c r="BQ1" s="126"/>
-      <c r="BR1" s="126"/>
-      <c r="BS1" s="126"/>
-      <c r="BT1" s="126"/>
-      <c r="BU1" s="126"/>
-      <c r="BV1" s="126"/>
-      <c r="BW1" s="126"/>
-      <c r="BX1" s="126"/>
-      <c r="BY1" s="126"/>
-      <c r="BZ1" s="126"/>
-      <c r="CA1" s="126"/>
-      <c r="CB1" s="133"/>
-      <c r="CC1" s="133"/>
-      <c r="CD1" s="133"/>
-      <c r="CE1" s="133"/>
-      <c r="CF1" s="133"/>
-      <c r="CG1" s="133"/>
-      <c r="CH1" s="133"/>
-      <c r="CI1" s="133"/>
-      <c r="CJ1" s="133"/>
-      <c r="CK1" s="133"/>
-      <c r="CL1" s="133"/>
-      <c r="CM1" s="134"/>
-      <c r="CN1" s="126"/>
-      <c r="CO1" s="126"/>
-      <c r="CP1" s="126"/>
-      <c r="CQ1" s="126"/>
-      <c r="CR1" s="126"/>
-      <c r="CS1" s="126"/>
-      <c r="CT1" s="126"/>
-      <c r="CU1" s="127"/>
-      <c r="CV1" s="135" t="s">
+      <c r="AI1" s="135"/>
+      <c r="AJ1" s="135"/>
+      <c r="AK1" s="135"/>
+      <c r="AL1" s="135"/>
+      <c r="AM1" s="135"/>
+      <c r="AN1" s="135"/>
+      <c r="AO1" s="135"/>
+      <c r="AP1" s="135"/>
+      <c r="AQ1" s="135"/>
+      <c r="AR1" s="135"/>
+      <c r="AS1" s="135"/>
+      <c r="AT1" s="135"/>
+      <c r="AU1" s="135"/>
+      <c r="AV1" s="135"/>
+      <c r="AW1" s="135"/>
+      <c r="AX1" s="135"/>
+      <c r="AY1" s="135"/>
+      <c r="AZ1" s="135"/>
+      <c r="BA1" s="135"/>
+      <c r="BB1" s="135"/>
+      <c r="BC1" s="135"/>
+      <c r="BD1" s="135"/>
+      <c r="BE1" s="135"/>
+      <c r="BF1" s="135"/>
+      <c r="BG1" s="135"/>
+      <c r="BH1" s="135"/>
+      <c r="BI1" s="135"/>
+      <c r="BJ1" s="135"/>
+      <c r="BK1" s="135"/>
+      <c r="BL1" s="135"/>
+      <c r="BM1" s="135"/>
+      <c r="BN1" s="135"/>
+      <c r="BO1" s="135"/>
+      <c r="BP1" s="135"/>
+      <c r="BQ1" s="135"/>
+      <c r="BR1" s="135"/>
+      <c r="BS1" s="135"/>
+      <c r="BT1" s="135"/>
+      <c r="BU1" s="135"/>
+      <c r="BV1" s="135"/>
+      <c r="BW1" s="135"/>
+      <c r="BX1" s="135"/>
+      <c r="BY1" s="135"/>
+      <c r="BZ1" s="135"/>
+      <c r="CA1" s="135"/>
+      <c r="CB1" s="143"/>
+      <c r="CC1" s="143"/>
+      <c r="CD1" s="143"/>
+      <c r="CE1" s="143"/>
+      <c r="CF1" s="143"/>
+      <c r="CG1" s="143"/>
+      <c r="CH1" s="143"/>
+      <c r="CI1" s="143"/>
+      <c r="CJ1" s="143"/>
+      <c r="CK1" s="143"/>
+      <c r="CL1" s="143"/>
+      <c r="CM1" s="144"/>
+      <c r="CN1" s="135"/>
+      <c r="CO1" s="135"/>
+      <c r="CP1" s="135"/>
+      <c r="CQ1" s="135"/>
+      <c r="CR1" s="135"/>
+      <c r="CS1" s="135"/>
+      <c r="CT1" s="135"/>
+      <c r="CU1" s="142"/>
+      <c r="CV1" s="136" t="s">
         <v>5</v>
       </c>
-      <c r="CW1" s="132"/>
-      <c r="CX1" s="132"/>
-      <c r="CY1" s="132"/>
-      <c r="CZ1" s="132"/>
-      <c r="DA1" s="132"/>
-      <c r="DB1" s="132"/>
-      <c r="DC1" s="132"/>
-      <c r="DD1" s="132"/>
-      <c r="DE1" s="132"/>
-      <c r="DF1" s="132"/>
-      <c r="DG1" s="136"/>
-      <c r="DH1" s="137" t="s">
+      <c r="CW1" s="137"/>
+      <c r="CX1" s="137"/>
+      <c r="CY1" s="137"/>
+      <c r="CZ1" s="137"/>
+      <c r="DA1" s="137"/>
+      <c r="DB1" s="137"/>
+      <c r="DC1" s="137"/>
+      <c r="DD1" s="137"/>
+      <c r="DE1" s="137"/>
+      <c r="DF1" s="137"/>
+      <c r="DG1" s="138"/>
+      <c r="DH1" s="131" t="s">
         <v>6</v>
       </c>
-      <c r="DI1" s="138"/>
-      <c r="DJ1" s="138"/>
-      <c r="DK1" s="138"/>
-      <c r="DL1" s="138"/>
-      <c r="DM1" s="138"/>
-      <c r="DN1" s="138"/>
-      <c r="DO1" s="138"/>
-      <c r="DP1" s="138"/>
-      <c r="DQ1" s="138"/>
-      <c r="DR1" s="138"/>
+      <c r="DI1" s="132"/>
+      <c r="DJ1" s="132"/>
+      <c r="DK1" s="132"/>
+      <c r="DL1" s="132"/>
+      <c r="DM1" s="132"/>
+      <c r="DN1" s="132"/>
+      <c r="DO1" s="132"/>
+      <c r="DP1" s="132"/>
+      <c r="DQ1" s="132"/>
+      <c r="DR1" s="132"/>
       <c r="DS1" s="139" t="s">
         <v>7</v>
       </c>
       <c r="DT1" s="140"/>
       <c r="DU1" s="140"/>
       <c r="DV1" s="140"/>
-      <c r="DW1" s="141" t="s">
+      <c r="DW1" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="DX1" s="130"/>
-      <c r="DY1" s="142"/>
-      <c r="DZ1" s="142"/>
-      <c r="EA1" s="142"/>
-      <c r="EB1" s="142"/>
-      <c r="EC1" s="142"/>
-      <c r="ED1" s="142"/>
-      <c r="EE1" s="142"/>
-      <c r="EF1" s="142"/>
-      <c r="EG1" s="142"/>
-      <c r="EH1" s="142"/>
-      <c r="EI1" s="142"/>
-      <c r="EJ1" s="143"/>
-      <c r="EK1" s="137" t="s">
+      <c r="DX1" s="134"/>
+      <c r="DY1" s="129"/>
+      <c r="DZ1" s="129"/>
+      <c r="EA1" s="129"/>
+      <c r="EB1" s="129"/>
+      <c r="EC1" s="129"/>
+      <c r="ED1" s="129"/>
+      <c r="EE1" s="129"/>
+      <c r="EF1" s="129"/>
+      <c r="EG1" s="129"/>
+      <c r="EH1" s="129"/>
+      <c r="EI1" s="129"/>
+      <c r="EJ1" s="130"/>
+      <c r="EK1" s="131" t="s">
         <v>9</v>
       </c>
-      <c r="EL1" s="138"/>
-      <c r="EM1" s="138"/>
-      <c r="EN1" s="138"/>
-      <c r="EO1" s="138"/>
-      <c r="EP1" s="144"/>
-      <c r="EQ1" s="137" t="s">
+      <c r="EL1" s="132"/>
+      <c r="EM1" s="132"/>
+      <c r="EN1" s="132"/>
+      <c r="EO1" s="132"/>
+      <c r="EP1" s="133"/>
+      <c r="EQ1" s="131" t="s">
         <v>10</v>
       </c>
-      <c r="ER1" s="138"/>
-      <c r="ES1" s="138"/>
-      <c r="ET1" s="138"/>
-      <c r="EU1" s="144"/>
-      <c r="EV1" s="137" t="s">
+      <c r="ER1" s="132"/>
+      <c r="ES1" s="132"/>
+      <c r="ET1" s="132"/>
+      <c r="EU1" s="133"/>
+      <c r="EV1" s="131" t="s">
         <v>11</v>
       </c>
-      <c r="EW1" s="138"/>
-      <c r="EX1" s="138"/>
-      <c r="EY1" s="138"/>
-      <c r="EZ1" s="138"/>
-      <c r="FA1" s="138"/>
-      <c r="FB1" s="138"/>
-      <c r="FC1" s="138"/>
-      <c r="FD1" s="138"/>
-      <c r="FE1" s="138"/>
-      <c r="FF1" s="138"/>
-      <c r="FG1" s="138"/>
-      <c r="FH1" s="138"/>
-      <c r="FI1" s="138"/>
-      <c r="FJ1" s="138"/>
-      <c r="FK1" s="138"/>
-      <c r="FL1" s="144"/>
-      <c r="FM1" s="130" t="s">
+      <c r="EW1" s="132"/>
+      <c r="EX1" s="132"/>
+      <c r="EY1" s="132"/>
+      <c r="EZ1" s="132"/>
+      <c r="FA1" s="132"/>
+      <c r="FB1" s="132"/>
+      <c r="FC1" s="132"/>
+      <c r="FD1" s="132"/>
+      <c r="FE1" s="132"/>
+      <c r="FF1" s="132"/>
+      <c r="FG1" s="132"/>
+      <c r="FH1" s="132"/>
+      <c r="FI1" s="132"/>
+      <c r="FJ1" s="132"/>
+      <c r="FK1" s="132"/>
+      <c r="FL1" s="133"/>
+      <c r="FM1" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="FN1" s="130"/>
-      <c r="FO1" s="130"/>
-      <c r="FP1" s="130"/>
-      <c r="FQ1" s="130"/>
-      <c r="FR1" s="130"/>
-      <c r="FS1" s="130"/>
-      <c r="FT1" s="130"/>
-      <c r="FU1" s="130"/>
-      <c r="FV1" s="130"/>
-      <c r="FW1" s="130"/>
-      <c r="FX1" s="130"/>
-      <c r="FY1" s="130"/>
-      <c r="FZ1" s="130"/>
-      <c r="GA1" s="130"/>
-      <c r="GB1" s="130"/>
-      <c r="GC1" s="130"/>
-      <c r="GD1" s="130"/>
-      <c r="GE1" s="130"/>
-      <c r="GF1" s="130"/>
-      <c r="GG1" s="130"/>
-      <c r="GH1" s="130"/>
-      <c r="GI1" s="130"/>
-      <c r="GJ1" s="137" t="s">
+      <c r="FN1" s="134"/>
+      <c r="FO1" s="134"/>
+      <c r="FP1" s="134"/>
+      <c r="FQ1" s="134"/>
+      <c r="FR1" s="134"/>
+      <c r="FS1" s="134"/>
+      <c r="FT1" s="134"/>
+      <c r="FU1" s="134"/>
+      <c r="FV1" s="134"/>
+      <c r="FW1" s="134"/>
+      <c r="FX1" s="134"/>
+      <c r="FY1" s="134"/>
+      <c r="FZ1" s="134"/>
+      <c r="GA1" s="134"/>
+      <c r="GB1" s="134"/>
+      <c r="GC1" s="134"/>
+      <c r="GD1" s="134"/>
+      <c r="GE1" s="134"/>
+      <c r="GF1" s="134"/>
+      <c r="GG1" s="134"/>
+      <c r="GH1" s="134"/>
+      <c r="GI1" s="134"/>
+      <c r="GJ1" s="131" t="s">
         <v>13</v>
       </c>
-      <c r="GK1" s="138"/>
-      <c r="GL1" s="138"/>
-      <c r="GM1" s="138"/>
-      <c r="GN1" s="144"/>
-      <c r="GO1" s="128" t="s">
+      <c r="GK1" s="132"/>
+      <c r="GL1" s="132"/>
+      <c r="GM1" s="132"/>
+      <c r="GN1" s="133"/>
+      <c r="GO1" s="125" t="s">
         <v>14</v>
       </c>
-      <c r="GP1" s="129"/>
-      <c r="GQ1" s="129"/>
-      <c r="GR1" s="129"/>
-      <c r="GS1" s="129"/>
-      <c r="GT1" s="129"/>
-      <c r="GU1" s="129"/>
-      <c r="GV1" s="129"/>
-      <c r="GW1" s="129"/>
-      <c r="GX1" s="129"/>
-      <c r="GY1" s="129"/>
-      <c r="GZ1" s="129"/>
-      <c r="HA1" s="129"/>
-      <c r="HB1" s="129"/>
-      <c r="HC1" s="129"/>
-      <c r="HD1" s="129"/>
-      <c r="HE1" s="129"/>
-      <c r="HF1" s="129"/>
-      <c r="HG1" s="129"/>
-      <c r="HH1" s="129"/>
-      <c r="HI1" s="129"/>
-      <c r="HJ1" s="129"/>
-      <c r="HK1" s="129"/>
-      <c r="HL1" s="129"/>
-      <c r="HM1" s="129"/>
-      <c r="HN1" s="129"/>
-      <c r="HO1" s="129"/>
-      <c r="HP1" s="129"/>
-      <c r="HQ1" s="126"/>
-      <c r="HR1" s="129"/>
-      <c r="HS1" s="128" t="s">
+      <c r="GP1" s="126"/>
+      <c r="GQ1" s="126"/>
+      <c r="GR1" s="126"/>
+      <c r="GS1" s="126"/>
+      <c r="GT1" s="126"/>
+      <c r="GU1" s="126"/>
+      <c r="GV1" s="126"/>
+      <c r="GW1" s="126"/>
+      <c r="GX1" s="126"/>
+      <c r="GY1" s="126"/>
+      <c r="GZ1" s="126"/>
+      <c r="HA1" s="126"/>
+      <c r="HB1" s="126"/>
+      <c r="HC1" s="126"/>
+      <c r="HD1" s="126"/>
+      <c r="HE1" s="126"/>
+      <c r="HF1" s="126"/>
+      <c r="HG1" s="126"/>
+      <c r="HH1" s="126"/>
+      <c r="HI1" s="126"/>
+      <c r="HJ1" s="126"/>
+      <c r="HK1" s="126"/>
+      <c r="HL1" s="126"/>
+      <c r="HM1" s="126"/>
+      <c r="HN1" s="126"/>
+      <c r="HO1" s="126"/>
+      <c r="HP1" s="126"/>
+      <c r="HQ1" s="135"/>
+      <c r="HR1" s="126"/>
+      <c r="HS1" s="125" t="s">
         <v>15</v>
       </c>
-      <c r="HT1" s="129"/>
-      <c r="HU1" s="129"/>
-      <c r="HV1" s="129"/>
-      <c r="HW1" s="129"/>
-      <c r="HX1" s="131"/>
-      <c r="HY1" s="128" t="s">
+      <c r="HT1" s="126"/>
+      <c r="HU1" s="126"/>
+      <c r="HV1" s="126"/>
+      <c r="HW1" s="126"/>
+      <c r="HX1" s="127"/>
+      <c r="HY1" s="125" t="s">
         <v>16</v>
       </c>
-      <c r="HZ1" s="129"/>
-      <c r="IA1" s="129"/>
-      <c r="IB1" s="129"/>
-      <c r="IC1" s="129"/>
-      <c r="ID1" s="129"/>
-      <c r="IE1" s="129"/>
-      <c r="IF1" s="129"/>
-      <c r="IG1" s="129"/>
-      <c r="IH1" s="129"/>
-      <c r="II1" s="129"/>
-      <c r="IJ1" s="129"/>
-      <c r="IK1" s="129"/>
-      <c r="IL1" s="129"/>
-      <c r="IM1" s="131"/>
-      <c r="IN1" s="141" t="s">
+      <c r="HZ1" s="126"/>
+      <c r="IA1" s="126"/>
+      <c r="IB1" s="126"/>
+      <c r="IC1" s="126"/>
+      <c r="ID1" s="126"/>
+      <c r="IE1" s="126"/>
+      <c r="IF1" s="126"/>
+      <c r="IG1" s="126"/>
+      <c r="IH1" s="126"/>
+      <c r="II1" s="126"/>
+      <c r="IJ1" s="126"/>
+      <c r="IK1" s="126"/>
+      <c r="IL1" s="126"/>
+      <c r="IM1" s="127"/>
+      <c r="IN1" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="IO1" s="142"/>
-      <c r="IP1" s="142"/>
-      <c r="IQ1" s="142"/>
-      <c r="IR1" s="142"/>
-      <c r="IS1" s="142"/>
-      <c r="IT1" s="142"/>
-      <c r="IU1" s="142"/>
-      <c r="IV1" s="142"/>
-      <c r="IW1" s="142"/>
-      <c r="IX1" s="142"/>
-      <c r="IY1" s="142"/>
-      <c r="IZ1" s="142"/>
-      <c r="JA1" s="142"/>
-      <c r="JB1" s="142"/>
-      <c r="JC1" s="142"/>
-      <c r="JD1" s="142"/>
-      <c r="JE1" s="142"/>
-      <c r="JF1" s="142"/>
-      <c r="JG1" s="143"/>
-      <c r="JH1" s="141" t="s">
+      <c r="IO1" s="129"/>
+      <c r="IP1" s="129"/>
+      <c r="IQ1" s="129"/>
+      <c r="IR1" s="129"/>
+      <c r="IS1" s="129"/>
+      <c r="IT1" s="129"/>
+      <c r="IU1" s="129"/>
+      <c r="IV1" s="129"/>
+      <c r="IW1" s="129"/>
+      <c r="IX1" s="129"/>
+      <c r="IY1" s="129"/>
+      <c r="IZ1" s="129"/>
+      <c r="JA1" s="129"/>
+      <c r="JB1" s="129"/>
+      <c r="JC1" s="129"/>
+      <c r="JD1" s="129"/>
+      <c r="JE1" s="129"/>
+      <c r="JF1" s="129"/>
+      <c r="JG1" s="130"/>
+      <c r="JH1" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="JI1" s="142"/>
-      <c r="JJ1" s="142"/>
-      <c r="JK1" s="142"/>
-      <c r="JL1" s="142"/>
+      <c r="JI1" s="129"/>
+      <c r="JJ1" s="129"/>
+      <c r="JK1" s="129"/>
+      <c r="JL1" s="129"/>
       <c r="JM1" s="117"/>
     </row>
     <row r="2" spans="1:273" s="73" customFormat="1">
@@ -10091,6 +10338,16 @@
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="19">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:N1"/>
+    <mergeCell ref="O1:Y1"/>
+    <mergeCell ref="Z1:AG1"/>
+    <mergeCell ref="AH1:CU1"/>
+    <mergeCell ref="CV1:DG1"/>
+    <mergeCell ref="DH1:DR1"/>
+    <mergeCell ref="DS1:DV1"/>
+    <mergeCell ref="DW1:EJ1"/>
+    <mergeCell ref="EK1:EP1"/>
     <mergeCell ref="HS1:HX1"/>
     <mergeCell ref="HY1:IM1"/>
     <mergeCell ref="IN1:JG1"/>
@@ -10100,16 +10357,6 @@
     <mergeCell ref="FM1:GI1"/>
     <mergeCell ref="GJ1:GN1"/>
     <mergeCell ref="GO1:HR1"/>
-    <mergeCell ref="CV1:DG1"/>
-    <mergeCell ref="DH1:DR1"/>
-    <mergeCell ref="DS1:DV1"/>
-    <mergeCell ref="DW1:EJ1"/>
-    <mergeCell ref="EK1:EP1"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:N1"/>
-    <mergeCell ref="O1:Y1"/>
-    <mergeCell ref="Z1:AG1"/>
-    <mergeCell ref="AH1:CU1"/>
   </mergeCells>
   <phoneticPr fontId="36" type="noConversion"/>
   <dataValidations count="130">
@@ -10549,9 +10796,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="95.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="95.08984375" style="1" customWidth="1"/>
     <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -10601,22 +10848,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IV319"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="32.25" style="30" customWidth="1"/>
-    <col min="2" max="2" width="44.75" style="30" customWidth="1"/>
+    <col min="1" max="1" width="32.26953125" style="30" customWidth="1"/>
+    <col min="2" max="2" width="44.7265625" style="30" customWidth="1"/>
     <col min="3" max="256" width="9" style="30"/>
     <col min="257" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="163" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="146"/>
+      <c r="B1" s="164"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="154" t="s">
         <v>239</v>
       </c>
       <c r="B2" s="42" t="s">
@@ -10624,25 +10871,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="160"/>
+      <c r="A3" s="155"/>
       <c r="B3" s="39" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="160"/>
+      <c r="A4" s="155"/>
       <c r="B4" s="39" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="161"/>
+      <c r="A5" s="156"/>
       <c r="B5" s="37" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="30" customFormat="1">
-      <c r="A6" s="162" t="s">
+      <c r="A6" s="157" t="s">
         <v>241</v>
       </c>
       <c r="B6" s="42" t="s">
@@ -10650,13 +10897,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="30" customFormat="1">
-      <c r="A7" s="163"/>
+      <c r="A7" s="158"/>
       <c r="B7" s="36" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="30" customFormat="1">
-      <c r="A8" s="164" t="s">
+      <c r="A8" s="159" t="s">
         <v>244</v>
       </c>
       <c r="B8" s="35" t="s">
@@ -10664,13 +10911,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="30" customFormat="1">
-      <c r="A9" s="163"/>
+      <c r="A9" s="158"/>
       <c r="B9" s="36" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="152" t="s">
+      <c r="A10" s="160" t="s">
         <v>247</v>
       </c>
       <c r="B10" s="39" t="s">
@@ -10678,61 +10925,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="165"/>
+      <c r="A11" s="161"/>
       <c r="B11" s="39" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="165"/>
+      <c r="A12" s="161"/>
       <c r="B12" s="39" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="165"/>
+      <c r="A13" s="161"/>
       <c r="B13" s="39" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="165"/>
+      <c r="A14" s="161"/>
       <c r="B14" s="39" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="165"/>
+      <c r="A15" s="161"/>
       <c r="B15" s="39" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="165"/>
+      <c r="A16" s="161"/>
       <c r="B16" s="39" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="165"/>
+      <c r="A17" s="161"/>
       <c r="B17" s="39" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="165"/>
+      <c r="A18" s="161"/>
       <c r="B18" s="39" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="165"/>
+      <c r="A19" s="161"/>
       <c r="B19" s="39" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="165"/>
+      <c r="A20" s="161"/>
       <c r="B20" s="39" t="s">
         <v>258</v>
       </c>
@@ -10746,7 +10993,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="152" t="s">
+      <c r="A22" s="160" t="s">
         <v>261</v>
       </c>
       <c r="B22" s="42" t="s">
@@ -10754,19 +11001,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="165"/>
+      <c r="A23" s="161"/>
       <c r="B23" s="39" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="153"/>
+      <c r="A24" s="162"/>
       <c r="B24" s="37" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="152" t="s">
+      <c r="A25" s="160" t="s">
         <v>265</v>
       </c>
       <c r="B25" s="39" t="s">
@@ -10774,67 +11021,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="165"/>
+      <c r="A26" s="161"/>
       <c r="B26" s="39" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="165"/>
+      <c r="A27" s="161"/>
       <c r="B27" s="34" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="165"/>
+      <c r="A28" s="161"/>
       <c r="B28" s="34" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="165"/>
+      <c r="A29" s="161"/>
       <c r="B29" s="34" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="165"/>
+      <c r="A30" s="161"/>
       <c r="B30" s="34" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="165"/>
+      <c r="A31" s="161"/>
       <c r="B31" s="34" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="165"/>
+      <c r="A32" s="161"/>
       <c r="B32" s="34" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="165"/>
+      <c r="A33" s="161"/>
       <c r="B33" s="34" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="165"/>
+      <c r="A34" s="161"/>
       <c r="B34" s="34" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="153"/>
+      <c r="A35" s="162"/>
       <c r="B35" s="55" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="152" t="s">
+      <c r="A36" s="160" t="s">
         <v>277</v>
       </c>
       <c r="B36" s="34" t="s">
@@ -10842,25 +11089,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="165"/>
+      <c r="A37" s="161"/>
       <c r="B37" s="39" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="165"/>
+      <c r="A38" s="161"/>
       <c r="B38" s="34" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="153"/>
+      <c r="A39" s="162"/>
       <c r="B39" s="34" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="152" t="s">
+      <c r="A40" s="160" t="s">
         <v>282</v>
       </c>
       <c r="B40" s="33" t="s">
@@ -10868,43 +11115,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="165"/>
+      <c r="A41" s="161"/>
       <c r="B41" s="34" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="165"/>
+      <c r="A42" s="161"/>
       <c r="B42" s="34" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="165"/>
+      <c r="A43" s="161"/>
       <c r="B43" s="34" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="165"/>
+      <c r="A44" s="161"/>
       <c r="B44" s="34" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="165"/>
+      <c r="A45" s="161"/>
       <c r="B45" s="34" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="153"/>
+      <c r="A46" s="162"/>
       <c r="B46" s="37" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="152" t="s">
+      <c r="A47" s="160" t="s">
         <v>290</v>
       </c>
       <c r="B47" s="42" t="s">
@@ -10912,61 +11159,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="165"/>
+      <c r="A48" s="161"/>
       <c r="B48" s="34" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="165"/>
+      <c r="A49" s="161"/>
       <c r="B49" s="34" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="165"/>
+      <c r="A50" s="161"/>
       <c r="B50" s="34" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="165"/>
+      <c r="A51" s="161"/>
       <c r="B51" s="34" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="165"/>
+      <c r="A52" s="161"/>
       <c r="B52" s="34" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="165"/>
+      <c r="A53" s="161"/>
       <c r="B53" s="39" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="165"/>
+      <c r="A54" s="161"/>
       <c r="B54" s="34" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="165"/>
+      <c r="A55" s="161"/>
       <c r="B55" s="39" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="153"/>
+      <c r="A56" s="162"/>
       <c r="B56" s="37" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="152" t="s">
+      <c r="A57" s="160" t="s">
         <v>301</v>
       </c>
       <c r="B57" s="33" t="s">
@@ -10974,19 +11221,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="165"/>
+      <c r="A58" s="161"/>
       <c r="B58" s="34" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="153"/>
+      <c r="A59" s="162"/>
       <c r="B59" s="37" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="152" t="s">
+      <c r="A60" s="160" t="s">
         <v>305</v>
       </c>
       <c r="B60" s="47" t="s">
@@ -10994,37 +11241,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="165"/>
+      <c r="A61" s="161"/>
       <c r="B61" s="34" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="165"/>
+      <c r="A62" s="161"/>
       <c r="B62" s="48" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="165"/>
+      <c r="A63" s="161"/>
       <c r="B63" s="34" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="165"/>
+      <c r="A64" s="161"/>
       <c r="B64" s="34" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="153"/>
+      <c r="A65" s="162"/>
       <c r="B65" s="41" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="152" t="s">
+      <c r="A66" s="160" t="s">
         <v>312</v>
       </c>
       <c r="B66" s="47" t="s">
@@ -11032,37 +11279,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="165"/>
+      <c r="A67" s="161"/>
       <c r="B67" s="34" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="165"/>
+      <c r="A68" s="161"/>
       <c r="B68" s="34" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="165"/>
+      <c r="A69" s="161"/>
       <c r="B69" s="34" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="165"/>
+      <c r="A70" s="161"/>
       <c r="B70" s="34" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="153"/>
+      <c r="A71" s="162"/>
       <c r="B71" s="41" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="30" customFormat="1">
-      <c r="A72" s="152" t="s">
+      <c r="A72" s="160" t="s">
         <v>319</v>
       </c>
       <c r="B72" s="34" t="s">
@@ -11070,103 +11317,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="30" customFormat="1">
-      <c r="A73" s="165"/>
+      <c r="A73" s="161"/>
       <c r="B73" s="34" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="30" customFormat="1">
-      <c r="A74" s="165"/>
+      <c r="A74" s="161"/>
       <c r="B74" s="34" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="30" customFormat="1">
-      <c r="A75" s="165"/>
+      <c r="A75" s="161"/>
       <c r="B75" s="34" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="30" customFormat="1">
-      <c r="A76" s="165"/>
+      <c r="A76" s="161"/>
       <c r="B76" s="34" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="30" customFormat="1">
-      <c r="A77" s="165"/>
+      <c r="A77" s="161"/>
       <c r="B77" s="49" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="30" customFormat="1">
-      <c r="A78" s="165"/>
+      <c r="A78" s="161"/>
       <c r="B78" s="34" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="30" customFormat="1">
-      <c r="A79" s="165"/>
+      <c r="A79" s="161"/>
       <c r="B79" s="34" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="30" customFormat="1">
-      <c r="A80" s="165"/>
+      <c r="A80" s="161"/>
       <c r="B80" s="34" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="30" customFormat="1">
-      <c r="A81" s="165"/>
+      <c r="A81" s="161"/>
       <c r="B81" s="49" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="30" customFormat="1">
-      <c r="A82" s="165"/>
+      <c r="A82" s="161"/>
       <c r="B82" s="34" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="30" customFormat="1">
-      <c r="A83" s="165"/>
+      <c r="A83" s="161"/>
       <c r="B83" s="34" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="30" customFormat="1">
-      <c r="A84" s="165"/>
+      <c r="A84" s="161"/>
       <c r="B84" s="34" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="30" customFormat="1">
-      <c r="A85" s="165"/>
+      <c r="A85" s="161"/>
       <c r="B85" s="49" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="30" customFormat="1">
-      <c r="A86" s="165"/>
+      <c r="A86" s="161"/>
       <c r="B86" s="49" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="30" customFormat="1">
-      <c r="A87" s="165"/>
+      <c r="A87" s="161"/>
       <c r="B87" s="49" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="30" customFormat="1">
-      <c r="A88" s="153"/>
+      <c r="A88" s="162"/>
       <c r="B88" s="37" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="30" customFormat="1">
-      <c r="A89" s="152" t="s">
+      <c r="A89" s="160" t="s">
         <v>337</v>
       </c>
       <c r="B89" s="39" t="s">
@@ -11174,38 +11421,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="30" customFormat="1">
-      <c r="A90" s="165"/>
+      <c r="A90" s="161"/>
       <c r="B90" s="39" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="30" customFormat="1">
-      <c r="A91" s="165"/>
+      <c r="A91" s="161"/>
       <c r="B91" s="39" t="s">
         <v>340</v>
       </c>
       <c r="F91" s="56"/>
     </row>
     <row r="92" spans="1:6" s="30" customFormat="1">
-      <c r="A92" s="165"/>
+      <c r="A92" s="161"/>
       <c r="B92" s="57" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="30" customFormat="1">
-      <c r="A93" s="165"/>
+      <c r="A93" s="161"/>
       <c r="B93" s="39" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="30" customFormat="1">
-      <c r="A94" s="153"/>
+      <c r="A94" s="162"/>
       <c r="B94" s="37" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="30" customFormat="1">
-      <c r="A95" s="152" t="s">
+      <c r="A95" s="160" t="s">
         <v>344</v>
       </c>
       <c r="B95" s="50" t="s">
@@ -11213,43 +11460,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="30" customFormat="1">
-      <c r="A96" s="165"/>
+      <c r="A96" s="161"/>
       <c r="B96" s="51" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="30" customFormat="1">
-      <c r="A97" s="165"/>
+      <c r="A97" s="161"/>
       <c r="B97" s="51" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="30" customFormat="1">
-      <c r="A98" s="165"/>
+      <c r="A98" s="161"/>
       <c r="B98" s="51" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="30" customFormat="1">
-      <c r="A99" s="165"/>
+      <c r="A99" s="161"/>
       <c r="B99" s="51" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="30" customFormat="1">
-      <c r="A100" s="165"/>
+      <c r="A100" s="161"/>
       <c r="B100" s="51" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="30" customFormat="1">
-      <c r="A101" s="153"/>
+      <c r="A101" s="162"/>
       <c r="B101" s="45" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="30" customFormat="1">
-      <c r="A102" s="152" t="s">
+      <c r="A102" s="160" t="s">
         <v>352</v>
       </c>
       <c r="B102" s="33" t="s">
@@ -11257,7 +11504,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="30" customFormat="1">
-      <c r="A103" s="153"/>
+      <c r="A103" s="162"/>
       <c r="B103" s="37" t="s">
         <v>354</v>
       </c>
@@ -11275,10 +11522,10 @@
       <c r="B105" s="40"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="147" t="s">
+      <c r="A107" s="165" t="s">
         <v>357</v>
       </c>
-      <c r="B107" s="146"/>
+      <c r="B107" s="164"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="61"/>
@@ -11449,17 +11696,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="166" t="s">
+      <c r="A137" s="148" t="s">
         <v>386</v>
       </c>
-      <c r="B137" s="167"/>
+      <c r="B137" s="149"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="168"/>
-      <c r="B138" s="169"/>
+      <c r="A138" s="150"/>
+      <c r="B138" s="151"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="154" t="s">
+      <c r="A139" s="145" t="s">
         <v>387</v>
       </c>
       <c r="B139" s="63" t="s">
@@ -11467,31 +11714,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="155"/>
+      <c r="A140" s="146"/>
       <c r="B140" s="64" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="155"/>
+      <c r="A141" s="146"/>
       <c r="B141" s="64" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="155"/>
+      <c r="A142" s="146"/>
       <c r="B142" s="64" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="156"/>
+      <c r="A143" s="147"/>
       <c r="B143" s="66" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="154" t="s">
+      <c r="A144" s="145" t="s">
         <v>393</v>
       </c>
       <c r="B144" s="63" t="s">
@@ -11499,43 +11746,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="155"/>
+      <c r="A145" s="146"/>
       <c r="B145" s="64" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="155"/>
+      <c r="A146" s="146"/>
       <c r="B146" s="64" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="155"/>
+      <c r="A147" s="146"/>
       <c r="B147" s="64" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="155"/>
+      <c r="A148" s="146"/>
       <c r="B148" s="64" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="155"/>
+      <c r="A149" s="146"/>
       <c r="B149" s="64" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="156"/>
+      <c r="A150" s="147"/>
       <c r="B150" s="66" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="154" t="s">
+      <c r="A151" s="145" t="s">
         <v>401</v>
       </c>
       <c r="B151" s="63" t="s">
@@ -11543,187 +11790,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="155"/>
+      <c r="A152" s="146"/>
       <c r="B152" s="64" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="155"/>
+      <c r="A153" s="146"/>
       <c r="B153" s="64" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="155"/>
+      <c r="A154" s="146"/>
       <c r="B154" s="64" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="155"/>
+      <c r="A155" s="146"/>
       <c r="B155" s="64" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="155"/>
+      <c r="A156" s="146"/>
       <c r="B156" s="64" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="155"/>
+      <c r="A157" s="146"/>
       <c r="B157" s="64" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="155"/>
+      <c r="A158" s="146"/>
       <c r="B158" s="64" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="155"/>
+      <c r="A159" s="146"/>
       <c r="B159" s="64" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="155"/>
+      <c r="A160" s="146"/>
       <c r="B160" s="64" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="155"/>
+      <c r="A161" s="146"/>
       <c r="B161" s="64" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="155"/>
+      <c r="A162" s="146"/>
       <c r="B162" s="64" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="155"/>
+      <c r="A163" s="146"/>
       <c r="B163" s="64" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="155"/>
+      <c r="A164" s="146"/>
       <c r="B164" s="64" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="155"/>
+      <c r="A165" s="146"/>
       <c r="B165" s="64" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="155"/>
+      <c r="A166" s="146"/>
       <c r="B166" s="64" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="155"/>
+      <c r="A167" s="146"/>
       <c r="B167" s="64" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="155"/>
+      <c r="A168" s="146"/>
       <c r="B168" s="64" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="155"/>
+      <c r="A169" s="146"/>
       <c r="B169" s="64" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="155"/>
+      <c r="A170" s="146"/>
       <c r="B170" s="64" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="155"/>
+      <c r="A171" s="146"/>
       <c r="B171" s="64" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="155"/>
+      <c r="A172" s="146"/>
       <c r="B172" s="64" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="155"/>
+      <c r="A173" s="146"/>
       <c r="B173" s="64" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="155"/>
+      <c r="A174" s="146"/>
       <c r="B174" s="64" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="155"/>
+      <c r="A175" s="146"/>
       <c r="B175" s="64" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="155"/>
+      <c r="A176" s="146"/>
       <c r="B176" s="64" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="155"/>
+      <c r="A177" s="146"/>
       <c r="B177" s="64" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="155"/>
+      <c r="A178" s="146"/>
       <c r="B178" s="64" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="155"/>
+      <c r="A179" s="146"/>
       <c r="B179" s="64" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="155"/>
+      <c r="A180" s="146"/>
       <c r="B180" s="64" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="156"/>
+      <c r="A181" s="147"/>
       <c r="B181" s="66" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="154" t="s">
+      <c r="A182" s="145" t="s">
         <v>433</v>
       </c>
       <c r="B182" s="63" t="s">
@@ -11731,19 +11978,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="155"/>
+      <c r="A183" s="146"/>
       <c r="B183" s="64" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="156"/>
+      <c r="A184" s="147"/>
       <c r="B184" s="66" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="154" t="s">
+      <c r="A185" s="145" t="s">
         <v>437</v>
       </c>
       <c r="B185" s="63" t="s">
@@ -11751,25 +11998,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="155"/>
+      <c r="A186" s="146"/>
       <c r="B186" s="64" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="155"/>
+      <c r="A187" s="146"/>
       <c r="B187" s="64" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="156"/>
+      <c r="A188" s="147"/>
       <c r="B188" s="66" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="154" t="s">
+      <c r="A189" s="145" t="s">
         <v>442</v>
       </c>
       <c r="B189" s="63" t="s">
@@ -11777,13 +12024,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="156"/>
+      <c r="A190" s="147"/>
       <c r="B190" s="66" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="154" t="s">
+      <c r="A191" s="145" t="s">
         <v>445</v>
       </c>
       <c r="B191" s="63" t="s">
@@ -11791,49 +12038,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="155"/>
+      <c r="A192" s="146"/>
       <c r="B192" s="64" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="155"/>
+      <c r="A193" s="146"/>
       <c r="B193" s="64" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="155"/>
+      <c r="A194" s="146"/>
       <c r="B194" s="64" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="155"/>
+      <c r="A195" s="146"/>
       <c r="B195" s="64" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="155"/>
+      <c r="A196" s="146"/>
       <c r="B196" s="64" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="155"/>
+      <c r="A197" s="146"/>
       <c r="B197" s="64" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="156"/>
+      <c r="A198" s="147"/>
       <c r="B198" s="66" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="154" t="s">
+      <c r="A199" s="145" t="s">
         <v>454</v>
       </c>
       <c r="B199" s="63" t="s">
@@ -11841,13 +12088,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="156"/>
+      <c r="A200" s="147"/>
       <c r="B200" s="66" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="154" t="s">
+      <c r="A201" s="145" t="s">
         <v>457</v>
       </c>
       <c r="B201" s="63" t="s">
@@ -11855,19 +12102,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="155"/>
+      <c r="A202" s="146"/>
       <c r="B202" s="64" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="156"/>
+      <c r="A203" s="147"/>
       <c r="B203" s="66" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="154" t="s">
+      <c r="A204" s="145" t="s">
         <v>461</v>
       </c>
       <c r="B204" s="63" t="s">
@@ -11875,19 +12122,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="155"/>
+      <c r="A205" s="146"/>
       <c r="B205" s="64" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="155"/>
+      <c r="A206" s="146"/>
       <c r="B206" s="64" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="156"/>
+      <c r="A207" s="147"/>
       <c r="B207" s="66" t="s">
         <v>465</v>
       </c>
@@ -11901,7 +12148,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="154" t="s">
+      <c r="A209" s="145" t="s">
         <v>468</v>
       </c>
       <c r="B209" s="63" t="s">
@@ -11909,13 +12156,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="156"/>
+      <c r="A210" s="147"/>
       <c r="B210" s="66" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="154" t="s">
+      <c r="A211" s="145" t="s">
         <v>471</v>
       </c>
       <c r="B211" s="63" t="s">
@@ -11923,19 +12170,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="155"/>
+      <c r="A212" s="146"/>
       <c r="B212" s="64" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="156"/>
+      <c r="A213" s="147"/>
       <c r="B213" s="66" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="154" t="s">
+      <c r="A214" s="145" t="s">
         <v>475</v>
       </c>
       <c r="B214" s="63" t="s">
@@ -11943,19 +12190,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="155"/>
+      <c r="A215" s="146"/>
       <c r="B215" s="64" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="156"/>
+      <c r="A216" s="147"/>
       <c r="B216" s="66" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="154" t="s">
+      <c r="A217" s="145" t="s">
         <v>479</v>
       </c>
       <c r="B217" s="63" t="s">
@@ -11963,13 +12210,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="155"/>
+      <c r="A218" s="146"/>
       <c r="B218" s="64" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="156"/>
+      <c r="A219" s="147"/>
       <c r="B219" s="66" t="s">
         <v>482</v>
       </c>
@@ -11983,7 +12230,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="154" t="s">
+      <c r="A221" s="145" t="s">
         <v>485</v>
       </c>
       <c r="B221" s="63" t="s">
@@ -11991,13 +12238,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="156"/>
+      <c r="A222" s="147"/>
       <c r="B222" s="66" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="154" t="s">
+      <c r="A223" s="145" t="s">
         <v>488</v>
       </c>
       <c r="B223" s="63" t="s">
@@ -12005,31 +12252,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="155"/>
+      <c r="A224" s="146"/>
       <c r="B224" s="64" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="155"/>
+      <c r="A225" s="146"/>
       <c r="B225" s="64" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="155"/>
+      <c r="A226" s="146"/>
       <c r="B226" s="64" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="156"/>
+      <c r="A227" s="147"/>
       <c r="B227" s="66" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="154" t="s">
+      <c r="A228" s="145" t="s">
         <v>494</v>
       </c>
       <c r="B228" s="63" t="s">
@@ -12037,31 +12284,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="155"/>
+      <c r="A229" s="146"/>
       <c r="B229" s="64" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="155"/>
+      <c r="A230" s="146"/>
       <c r="B230" s="64" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="155"/>
+      <c r="A231" s="146"/>
       <c r="B231" s="64" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="155"/>
+      <c r="A232" s="146"/>
       <c r="B232" s="64" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="156"/>
+      <c r="A233" s="147"/>
       <c r="B233" s="66" t="s">
         <v>500</v>
       </c>
@@ -12075,16 +12322,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="148" t="s">
+      <c r="A236" s="166" t="s">
         <v>503</v>
       </c>
-      <c r="B236" s="149"/>
+      <c r="B236" s="167"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="147" t="s">
+      <c r="A239" s="165" t="s">
         <v>504</v>
       </c>
-      <c r="B239" s="146"/>
+      <c r="B239" s="164"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="61"/>
@@ -12183,10 +12430,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="150" t="s">
+      <c r="A257" s="168" t="s">
         <v>520</v>
       </c>
-      <c r="B257" s="151"/>
+      <c r="B257" s="169"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="61"/>
@@ -12362,11 +12609,11 @@
         <v>549</v>
       </c>
     </row>
-    <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="157" t="s">
+    <row r="288" spans="1:2" ht="23">
+      <c r="A288" s="152" t="s">
         <v>550</v>
       </c>
-      <c r="B288" s="158"/>
+      <c r="B288" s="153"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="69"/>
@@ -12557,14 +12804,22 @@
   </sheetData>
   <sheetProtection password="EC2B" sheet="1" objects="1"/>
   <mergeCells count="40">
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A236:B236"/>
+    <mergeCell ref="A239:B239"/>
+    <mergeCell ref="A257:B257"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A139:A143"/>
+    <mergeCell ref="A144:A150"/>
+    <mergeCell ref="A151:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A188"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="A191:A198"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A201:A203"/>
+    <mergeCell ref="A204:A207"/>
     <mergeCell ref="A288:B288"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -12581,22 +12836,14 @@
     <mergeCell ref="A72:A88"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A236:B236"/>
-    <mergeCell ref="A239:B239"/>
-    <mergeCell ref="A257:B257"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A139:A143"/>
-    <mergeCell ref="A144:A150"/>
-    <mergeCell ref="A151:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="A191:A198"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A201:A203"/>
-    <mergeCell ref="A204:A207"/>
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="36" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12607,21 +12854,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IV105"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="38.125" style="30" customWidth="1"/>
-    <col min="2" max="2" width="76.625" style="30" customWidth="1"/>
+    <col min="1" max="1" width="38.08984375" style="30" customWidth="1"/>
+    <col min="2" max="2" width="76.6328125" style="30" customWidth="1"/>
     <col min="3" max="256" width="9" style="30"/>
     <col min="257" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="182" t="s">
         <v>582</v>
       </c>
-      <c r="B1" s="171"/>
-    </row>
-    <row r="2" spans="1:2" s="28" customFormat="1" ht="14.25">
+      <c r="B1" s="183"/>
+    </row>
+    <row r="2" spans="1:2" s="28" customFormat="1" ht="15">
       <c r="A2" s="31" t="s">
         <v>583</v>
       </c>
@@ -12633,7 +12880,7 @@
       <c r="A3" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="B3" s="172" t="s">
+      <c r="B3" s="173" t="s">
         <v>1</v>
       </c>
     </row>
@@ -12641,25 +12888,25 @@
       <c r="A4" s="34" t="s">
         <v>585</v>
       </c>
-      <c r="B4" s="173"/>
+      <c r="B4" s="174"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="B5" s="173"/>
+      <c r="B5" s="174"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="B6" s="174"/>
+      <c r="B6" s="175"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="35" t="s">
         <v>245</v>
       </c>
-      <c r="B7" s="172" t="s">
+      <c r="B7" s="173" t="s">
         <v>586</v>
       </c>
     </row>
@@ -12667,25 +12914,25 @@
       <c r="A8" s="36" t="s">
         <v>246</v>
       </c>
-      <c r="B8" s="173"/>
+      <c r="B8" s="174"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="33" t="s">
         <v>353</v>
       </c>
-      <c r="B9" s="173"/>
+      <c r="B9" s="174"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="37" t="s">
         <v>354</v>
       </c>
-      <c r="B10" s="174"/>
+      <c r="B10" s="175"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="B11" s="172" t="s">
+      <c r="B11" s="173" t="s">
         <v>2</v>
       </c>
     </row>
@@ -12693,85 +12940,85 @@
       <c r="A12" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="B12" s="173"/>
+      <c r="B12" s="174"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="38" t="s">
         <v>250</v>
       </c>
-      <c r="B13" s="173"/>
+      <c r="B13" s="174"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="34" t="s">
         <v>251</v>
       </c>
-      <c r="B14" s="173"/>
+      <c r="B14" s="174"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="B15" s="173"/>
+      <c r="B15" s="174"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="B16" s="173"/>
+      <c r="B16" s="174"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="B17" s="173"/>
+      <c r="B17" s="174"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="34" t="s">
         <v>587</v>
       </c>
-      <c r="B18" s="173"/>
+      <c r="B18" s="174"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="B19" s="173"/>
+      <c r="B19" s="174"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="34" t="s">
         <v>588</v>
       </c>
-      <c r="B20" s="173"/>
+      <c r="B20" s="174"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="39" t="s">
         <v>589</v>
       </c>
-      <c r="B21" s="173"/>
+      <c r="B21" s="174"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="39" t="s">
         <v>260</v>
       </c>
-      <c r="B22" s="173"/>
+      <c r="B22" s="174"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="40" t="s">
         <v>242</v>
       </c>
-      <c r="B23" s="175"/>
+      <c r="B23" s="184"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="B24" s="176"/>
+      <c r="B24" s="185"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="33" t="s">
         <v>590</v>
       </c>
-      <c r="B25" s="172" t="s">
+      <c r="B25" s="173" t="s">
         <v>4</v>
       </c>
     </row>
@@ -12779,61 +13026,61 @@
       <c r="A26" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="B26" s="173"/>
+      <c r="B26" s="174"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="34" t="s">
         <v>270</v>
       </c>
-      <c r="B27" s="173"/>
+      <c r="B27" s="174"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="B28" s="173"/>
+      <c r="B28" s="174"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="34" t="s">
         <v>272</v>
       </c>
-      <c r="B29" s="173"/>
+      <c r="B29" s="174"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="34" t="s">
         <v>591</v>
       </c>
-      <c r="B30" s="173"/>
+      <c r="B30" s="174"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="B31" s="173"/>
+      <c r="B31" s="174"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="34" t="s">
         <v>592</v>
       </c>
-      <c r="B32" s="173"/>
+      <c r="B32" s="174"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="34" t="s">
         <v>593</v>
       </c>
-      <c r="B33" s="173"/>
+      <c r="B33" s="174"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="41" t="s">
         <v>263</v>
       </c>
-      <c r="B34" s="174"/>
+      <c r="B34" s="175"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="42" t="s">
         <v>594</v>
       </c>
-      <c r="B35" s="172" t="s">
+      <c r="B35" s="173" t="s">
         <v>595</v>
       </c>
     </row>
@@ -12841,13 +13088,13 @@
       <c r="A36" s="41" t="s">
         <v>596</v>
       </c>
-      <c r="B36" s="174"/>
+      <c r="B36" s="175"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="34" t="s">
         <v>278</v>
       </c>
-      <c r="B37" s="172" t="s">
+      <c r="B37" s="173" t="s">
         <v>6</v>
       </c>
     </row>
@@ -12855,19 +13102,19 @@
       <c r="A38" s="39" t="s">
         <v>279</v>
       </c>
-      <c r="B38" s="173"/>
+      <c r="B38" s="174"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="B39" s="173"/>
+      <c r="B39" s="174"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="33" t="s">
         <v>597</v>
       </c>
-      <c r="B40" s="172" t="s">
+      <c r="B40" s="173" t="s">
         <v>598</v>
       </c>
     </row>
@@ -12875,37 +13122,37 @@
       <c r="A41" s="34" t="s">
         <v>599</v>
       </c>
-      <c r="B41" s="173"/>
+      <c r="B41" s="174"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="B42" s="173"/>
+      <c r="B42" s="174"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="34" t="s">
         <v>600</v>
       </c>
-      <c r="B43" s="173"/>
+      <c r="B43" s="174"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="34" t="s">
         <v>601</v>
       </c>
-      <c r="B44" s="173"/>
+      <c r="B44" s="174"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="34" t="s">
         <v>288</v>
       </c>
-      <c r="B45" s="173"/>
+      <c r="B45" s="174"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="37" t="s">
         <v>289</v>
       </c>
-      <c r="B46" s="174"/>
+      <c r="B46" s="175"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="43" t="s">
@@ -12919,7 +13166,7 @@
       <c r="A48" s="34" t="s">
         <v>292</v>
       </c>
-      <c r="B48" s="172" t="s">
+      <c r="B48" s="173" t="s">
         <v>602</v>
       </c>
     </row>
@@ -12927,13 +13174,13 @@
       <c r="A49" s="34" t="s">
         <v>293</v>
       </c>
-      <c r="B49" s="174"/>
+      <c r="B49" s="175"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="B50" s="172" t="s">
+      <c r="B50" s="173" t="s">
         <v>10</v>
       </c>
     </row>
@@ -12941,25 +13188,25 @@
       <c r="A51" s="34" t="s">
         <v>297</v>
       </c>
-      <c r="B51" s="173"/>
+      <c r="B51" s="174"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="34" t="s">
         <v>294</v>
       </c>
-      <c r="B52" s="173"/>
+      <c r="B52" s="174"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="34" t="s">
         <v>295</v>
       </c>
-      <c r="B53" s="173"/>
+      <c r="B53" s="174"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="41" t="s">
         <v>296</v>
       </c>
-      <c r="B54" s="174"/>
+      <c r="B54" s="175"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="43" t="s">
@@ -12973,7 +13220,7 @@
       <c r="A56" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="B56" s="172" t="s">
+      <c r="B56" s="173" t="s">
         <v>13</v>
       </c>
     </row>
@@ -12981,19 +13228,19 @@
       <c r="A57" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="B57" s="173"/>
+      <c r="B57" s="174"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="37" t="s">
         <v>304</v>
       </c>
-      <c r="B58" s="174"/>
+      <c r="B58" s="175"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="34" t="s">
         <v>338</v>
       </c>
-      <c r="B59" s="180" t="s">
+      <c r="B59" s="176" t="s">
         <v>12</v>
       </c>
     </row>
@@ -13001,37 +13248,37 @@
       <c r="A60" s="34" t="s">
         <v>342</v>
       </c>
-      <c r="B60" s="181"/>
+      <c r="B60" s="177"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="34" t="s">
         <v>339</v>
       </c>
-      <c r="B61" s="181"/>
+      <c r="B61" s="177"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="B62" s="181"/>
+      <c r="B62" s="177"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="34" t="s">
         <v>343</v>
       </c>
-      <c r="B63" s="181"/>
+      <c r="B63" s="177"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="45" t="s">
         <v>341</v>
       </c>
-      <c r="B64" s="182"/>
+      <c r="B64" s="178"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="34" t="s">
         <v>605</v>
       </c>
-      <c r="B65" s="183" t="s">
+      <c r="B65" s="179" t="s">
         <v>606</v>
       </c>
     </row>
@@ -13039,26 +13286,26 @@
       <c r="A66" s="34" t="s">
         <v>281</v>
       </c>
-      <c r="B66" s="184"/>
+      <c r="B66" s="180"/>
       <c r="E66" s="46"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="39" t="s">
         <v>300</v>
       </c>
-      <c r="B67" s="184"/>
+      <c r="B67" s="180"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="B68" s="185"/>
+      <c r="B68" s="181"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="47" t="s">
         <v>306</v>
       </c>
-      <c r="B69" s="180" t="s">
+      <c r="B69" s="176" t="s">
         <v>15</v>
       </c>
     </row>
@@ -13066,37 +13313,37 @@
       <c r="A70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="B70" s="181"/>
+      <c r="B70" s="177"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="48" t="s">
         <v>308</v>
       </c>
-      <c r="B71" s="181"/>
+      <c r="B71" s="177"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="34" t="s">
         <v>309</v>
       </c>
-      <c r="B72" s="181"/>
+      <c r="B72" s="177"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="B73" s="181"/>
+      <c r="B73" s="177"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="34" t="s">
         <v>311</v>
       </c>
-      <c r="B74" s="182"/>
+      <c r="B74" s="178"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="47" t="s">
         <v>313</v>
       </c>
-      <c r="B75" s="180" t="s">
+      <c r="B75" s="176" t="s">
         <v>16</v>
       </c>
     </row>
@@ -13104,139 +13351,139 @@
       <c r="A76" s="34" t="s">
         <v>314</v>
       </c>
-      <c r="B76" s="181"/>
+      <c r="B76" s="177"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="34" t="s">
         <v>315</v>
       </c>
-      <c r="B77" s="181"/>
+      <c r="B77" s="177"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="34" t="s">
         <v>316</v>
       </c>
-      <c r="B78" s="181"/>
+      <c r="B78" s="177"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="B79" s="181"/>
+      <c r="B79" s="177"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="B80" s="181"/>
+      <c r="B80" s="177"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="B81" s="181"/>
+      <c r="B81" s="177"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="B82" s="181"/>
+      <c r="B82" s="177"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="34" t="s">
         <v>322</v>
       </c>
-      <c r="B83" s="181"/>
+      <c r="B83" s="177"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="34" t="s">
         <v>323</v>
       </c>
-      <c r="B84" s="181"/>
+      <c r="B84" s="177"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="34" t="s">
         <v>324</v>
       </c>
-      <c r="B85" s="181"/>
+      <c r="B85" s="177"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="49" t="s">
         <v>325</v>
       </c>
-      <c r="B86" s="181"/>
+      <c r="B86" s="177"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="B87" s="181"/>
+      <c r="B87" s="177"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="34" t="s">
         <v>327</v>
       </c>
-      <c r="B88" s="181"/>
+      <c r="B88" s="177"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="34" t="s">
         <v>328</v>
       </c>
-      <c r="B89" s="181"/>
+      <c r="B89" s="177"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="B90" s="181"/>
+      <c r="B90" s="177"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="B91" s="181"/>
+      <c r="B91" s="177"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="34" t="s">
         <v>331</v>
       </c>
-      <c r="B92" s="181"/>
+      <c r="B92" s="177"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="34" t="s">
         <v>332</v>
       </c>
-      <c r="B93" s="181"/>
+      <c r="B93" s="177"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="49" t="s">
         <v>333</v>
       </c>
-      <c r="B94" s="181"/>
+      <c r="B94" s="177"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="49" t="s">
         <v>334</v>
       </c>
-      <c r="B95" s="181"/>
+      <c r="B95" s="177"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="49" t="s">
         <v>335</v>
       </c>
-      <c r="B96" s="181"/>
+      <c r="B96" s="177"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="34" t="s">
         <v>336</v>
       </c>
-      <c r="B97" s="181"/>
+      <c r="B97" s="177"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="50" t="s">
         <v>345</v>
       </c>
-      <c r="B98" s="177" t="s">
+      <c r="B98" s="170" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13244,37 +13491,37 @@
       <c r="A99" s="51" t="s">
         <v>346</v>
       </c>
-      <c r="B99" s="178"/>
+      <c r="B99" s="171"/>
     </row>
     <row r="100" spans="1:2" s="29" customFormat="1">
       <c r="A100" s="51" t="s">
         <v>347</v>
       </c>
-      <c r="B100" s="178"/>
+      <c r="B100" s="171"/>
     </row>
     <row r="101" spans="1:2" s="29" customFormat="1">
       <c r="A101" s="51" t="s">
         <v>348</v>
       </c>
-      <c r="B101" s="178"/>
+      <c r="B101" s="171"/>
     </row>
     <row r="102" spans="1:2" s="29" customFormat="1">
       <c r="A102" s="51" t="s">
         <v>349</v>
       </c>
-      <c r="B102" s="178"/>
+      <c r="B102" s="171"/>
     </row>
     <row r="103" spans="1:2" s="29" customFormat="1">
       <c r="A103" s="51" t="s">
         <v>350</v>
       </c>
-      <c r="B103" s="178"/>
+      <c r="B103" s="171"/>
     </row>
     <row r="104" spans="1:2" s="29" customFormat="1">
       <c r="A104" s="45" t="s">
         <v>351</v>
       </c>
-      <c r="B104" s="179"/>
+      <c r="B104" s="172"/>
     </row>
     <row r="105" spans="1:2" s="29" customFormat="1">
       <c r="A105" s="52" t="s">
@@ -13286,22 +13533,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="36" type="noConversion"/>
   <hyperlinks>
@@ -13336,12 +13583,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IV240"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" style="10" customWidth="1"/>
-    <col min="2" max="2" width="35.5" style="23" customWidth="1"/>
-    <col min="3" max="256" width="9.125" style="10"/>
-    <col min="257" max="16384" width="9.125" style="1"/>
+    <col min="2" max="2" width="35.453125" style="23" customWidth="1"/>
+    <col min="3" max="256" width="9.08984375" style="10"/>
+    <col min="257" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27" customHeight="1">
@@ -15276,10 +15523,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B179"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" style="16" customWidth="1"/>
-    <col min="2" max="2" width="35.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.453125" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16725,10 +16972,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="103.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="103.7265625" style="2" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16756,7 +17003,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="27">
+    <row r="4" spans="1:2" ht="28">
       <c r="B4" s="2" t="s">
         <v>1446</v>
       </c>
@@ -16766,7 +17013,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="67.5">
+    <row r="6" spans="1:2" ht="84">
       <c r="B6" s="2" t="s">
         <v>1506</v>
       </c>
@@ -16800,7 +17047,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="27">
+    <row r="14" spans="1:2" ht="28">
       <c r="B14" s="7" t="s">
         <v>1451</v>
       </c>
@@ -16820,7 +17067,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="40.5">
+    <row r="18" spans="1:2" ht="42">
       <c r="B18" s="7" t="s">
         <v>1455</v>
       </c>
@@ -16845,7 +17092,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="27">
+    <row r="23" spans="1:2" ht="28">
       <c r="B23" s="7" t="s">
         <v>1460</v>
       </c>
@@ -16869,7 +17116,7 @@
         <v>43245</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="67.5">
+    <row r="28" spans="1:2" ht="84">
       <c r="A28" s="9" t="s">
         <v>1444</v>
       </c>
@@ -16896,7 +17143,7 @@
         <v>43126</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="297">
+    <row r="32" spans="1:2" ht="322">
       <c r="A32" s="9" t="s">
         <v>1444</v>
       </c>
@@ -17018,7 +17265,7 @@
       <c r="A53" s="189"/>
       <c r="B53" s="11"/>
     </row>
-    <row r="54" spans="1:2" ht="27">
+    <row r="54" spans="1:2" ht="28">
       <c r="A54" s="189"/>
       <c r="B54" s="11" t="s">
         <v>1475</v>
@@ -17038,7 +17285,7 @@
       <c r="A57" s="189"/>
       <c r="B57" s="11"/>
     </row>
-    <row r="58" spans="1:2" ht="27">
+    <row r="58" spans="1:2" ht="28">
       <c r="A58" s="189"/>
       <c r="B58" s="11" t="s">
         <v>1477</v>
@@ -17048,7 +17295,7 @@
       <c r="A59" s="189"/>
       <c r="B59" s="11"/>
     </row>
-    <row r="60" spans="1:2" ht="27">
+    <row r="60" spans="1:2" ht="28">
       <c r="A60" s="189"/>
       <c r="B60" s="11" t="s">
         <v>1478</v>
@@ -17094,7 +17341,7 @@
         <v>42685</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="108">
+    <row r="68" spans="1:2" ht="112">
       <c r="A68" s="10" t="s">
         <v>1444</v>
       </c>
@@ -17186,7 +17433,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="54">
+    <row r="86" spans="1:2" ht="56">
       <c r="A86" s="10" t="s">
         <v>1444</v>
       </c>
